--- a/data/glossary/ATK_mis.Gold_tables_v1.xlsx
+++ b/data/glossary/ATK_mis.Gold_tables_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448C0C79-90D2-4244-85E6-68C58DB562A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B18D03-6E4F-4781-BD63-72A1F9CCB8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26775" yWindow="1020" windowWidth="26490" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="712">
   <si>
     <t>BranchCode</t>
   </si>
@@ -2170,6 +2170,9 @@
   </si>
   <si>
     <t>АктыПередачиКредитныхДел Активность</t>
+  </si>
+  <si>
+    <t>CreditHistoryType</t>
   </si>
 </sst>
 </file>
@@ -2641,10 +2644,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
@@ -2936,7 +2939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E556"/>
+  <dimension ref="A1:E557"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.140625" customWidth="1"/>
@@ -3852,7 +3855,7 @@
       <c r="C68" s="27"/>
       <c r="D68" s="47"/>
       <c r="E68" s="41" t="str">
-        <f t="shared" ref="E68:E131" si="1">IF(C68&gt;0,IF(D68&gt;0,D68, C68)," ")</f>
+        <f t="shared" ref="E68:E132" si="1">IF(C68&gt;0,IF(D68&gt;0,D68, C68)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -4345,19 +4348,21 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="27"/>
+      <c r="B105" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C105" s="27" t="s">
+        <v>711</v>
+      </c>
       <c r="D105" s="47"/>
       <c r="E105" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>CreditHistoryType</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
-      <c r="B106" s="1" t="s">
-        <v>418</v>
-      </c>
+      <c r="B106" s="2"/>
       <c r="C106" s="27"/>
       <c r="D106" s="47"/>
       <c r="E106" s="41" t="str">
@@ -4367,33 +4372,33 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
-      <c r="B107" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C107" s="27" t="s">
-        <v>239</v>
-      </c>
+      <c r="B107" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C107" s="27"/>
       <c r="D107" s="47"/>
       <c r="E107" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>FinancialProductsMainGroup</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="27"/>
+      <c r="B108" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C108" s="27" t="s">
+        <v>239</v>
+      </c>
       <c r="D108" s="47"/>
       <c r="E108" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>FinancialProductsMainGroup</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
-      <c r="B109" s="1" t="s">
-        <v>419</v>
-      </c>
+      <c r="B109" s="2"/>
       <c r="C109" s="27"/>
       <c r="D109" s="47"/>
       <c r="E109" s="41" t="str">
@@ -4403,33 +4408,33 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
-      <c r="B110" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C110" s="27" t="s">
-        <v>241</v>
-      </c>
+      <c r="B110" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C110" s="27"/>
       <c r="D110" s="47"/>
       <c r="E110" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>IssuedCreditsStatus</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="27"/>
+      <c r="B111" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>241</v>
+      </c>
       <c r="D111" s="47"/>
       <c r="E111" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>IssuedCreditsStatus</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
-      <c r="B112" s="1" t="s">
-        <v>420</v>
-      </c>
+      <c r="B112" s="2"/>
       <c r="C112" s="27"/>
       <c r="D112" s="47"/>
       <c r="E112" s="41" t="str">
@@ -4439,47 +4444,47 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
-      <c r="B113" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C113" s="27" t="s">
-        <v>245</v>
-      </c>
+      <c r="B113" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C113" s="27"/>
       <c r="D113" s="47"/>
       <c r="E113" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>CreditApplicationPartnerID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="B114" s="2" t="s">
-        <v>389</v>
+        <v>244</v>
       </c>
       <c r="C114" s="27" t="s">
-        <v>390</v>
+        <v>245</v>
       </c>
       <c r="D114" s="47"/>
       <c r="E114" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>CreditPartnerName</v>
+        <v>CreditApplicationPartnerID</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="27"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="27" t="s">
+        <v>390</v>
+      </c>
       <c r="D115" s="47"/>
       <c r="E115" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>CreditPartnerName</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
-      <c r="B116" s="1" t="s">
-        <v>415</v>
-      </c>
+      <c r="B116" s="2"/>
       <c r="C116" s="27"/>
       <c r="D116" s="47"/>
       <c r="E116" s="41" t="str">
@@ -4489,47 +4494,47 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
-      <c r="B117" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C117" s="27" t="s">
-        <v>507</v>
-      </c>
+      <c r="B117" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C117" s="27"/>
       <c r="D117" s="47"/>
       <c r="E117" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>First_Filial_ID/Last_Filial_ID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C118" s="27" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D118" s="47"/>
       <c r="E118" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>First_Expert_ID/Last_Expert_ID</v>
+        <v>First_Filial_ID/Last_Filial_ID</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="27"/>
+      <c r="B119" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>508</v>
+      </c>
       <c r="D119" s="47"/>
       <c r="E119" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>First_Expert_ID/Last_Expert_ID</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
-      <c r="B120" s="1" t="s">
-        <v>415</v>
-      </c>
+      <c r="B120" s="2"/>
       <c r="C120" s="27"/>
       <c r="D120" s="47"/>
       <c r="E120" s="41" t="str">
@@ -4539,26 +4544,28 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
-      <c r="B121" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C121" s="27" t="s">
-        <v>414</v>
-      </c>
+      <c r="B121" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C121" s="27"/>
       <c r="D121" s="47"/>
       <c r="E121" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>FirstEmployeeID/LastEmployeeID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="27"/>
+      <c r="B122" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C122" s="27" t="s">
+        <v>414</v>
+      </c>
       <c r="D122" s="47"/>
       <c r="E122" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>FirstEmployeeID/LastEmployeeID</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -4573,9 +4580,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
-      <c r="B124" s="1" t="s">
-        <v>421</v>
-      </c>
+      <c r="B124" s="2"/>
       <c r="C124" s="27"/>
       <c r="D124" s="47"/>
       <c r="E124" s="41" t="str">
@@ -4585,47 +4590,47 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
-      <c r="B125" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C125" s="27" t="s">
-        <v>221</v>
-      </c>
+      <c r="B125" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C125" s="27"/>
       <c r="D125" s="47"/>
       <c r="E125" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>DealerID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
       <c r="B126" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C126" s="27" t="s">
-        <v>393</v>
+        <v>221</v>
       </c>
       <c r="D126" s="47"/>
       <c r="E126" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>Source</v>
+        <v>DealerID</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="27"/>
+      <c r="B127" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C127" s="27" t="s">
+        <v>393</v>
+      </c>
       <c r="D127" s="47"/>
       <c r="E127" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>Source</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
-      <c r="B128" s="1" t="s">
-        <v>422</v>
-      </c>
+      <c r="B128" s="2"/>
       <c r="C128" s="27"/>
       <c r="D128" s="47"/>
       <c r="E128" s="41" t="str">
@@ -4635,33 +4640,33 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
-      <c r="B129" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C129" s="27" t="s">
-        <v>246</v>
-      </c>
+      <c r="B129" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C129" s="27"/>
       <c r="D129" s="47"/>
       <c r="E129" s="41" t="str">
         <f t="shared" si="1"/>
-        <v>LatestOutstandingAmount</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="27"/>
+      <c r="B130" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C130" s="27" t="s">
+        <v>246</v>
+      </c>
       <c r="D130" s="47"/>
       <c r="E130" s="41" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
+        <v>LatestOutstandingAmount</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
-      <c r="B131" s="1" t="s">
-        <v>417</v>
-      </c>
+      <c r="B131" s="2"/>
       <c r="C131" s="27"/>
       <c r="D131" s="47"/>
       <c r="E131" s="41" t="str">
@@ -4671,33 +4676,33 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
-      <c r="B132" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C132" s="27" t="s">
-        <v>394</v>
-      </c>
+      <c r="B132" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C132" s="27"/>
       <c r="D132" s="47"/>
       <c r="E132" s="41" t="str">
-        <f t="shared" ref="E132:E206" si="2">IF(C132&gt;0,IF(D132&gt;0,D132, C132)," ")</f>
-        <v>SegmentRevenue</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="13"/>
-      <c r="B133" s="19"/>
-      <c r="C133" s="27"/>
+      <c r="A133" s="3"/>
+      <c r="B133" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C133" s="27" t="s">
+        <v>394</v>
+      </c>
       <c r="D133" s="47"/>
       <c r="E133" s="41" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" ref="E133:E207" si="2">IF(C133&gt;0,IF(D133&gt;0,D133, C133)," ")</f>
+        <v>SegmentRevenue</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="13"/>
-      <c r="B134" s="19" t="s">
-        <v>423</v>
-      </c>
+      <c r="B134" s="19"/>
       <c r="C134" s="27"/>
       <c r="D134" s="47"/>
       <c r="E134" s="41" t="str">
@@ -4707,61 +4712,61 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="13"/>
-      <c r="B135" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="C135" s="27" t="s">
-        <v>397</v>
-      </c>
+      <c r="B135" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="C135" s="27"/>
       <c r="D135" s="47"/>
       <c r="E135" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>GreenCredit</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="13"/>
       <c r="B136" s="15" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C136" s="27" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D136" s="47"/>
       <c r="E136" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>CommitteeProt_CrPurpose</v>
+        <v>GreenCredit</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="13"/>
       <c r="B137" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C137" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D137" s="47"/>
       <c r="E137" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>CommitteeProt_AMLRiskCat</v>
+        <v>CommitteeProt_CrPurpose</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="13"/>
-      <c r="B138" s="15"/>
-      <c r="C138" s="27"/>
+      <c r="B138" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C138" s="27" t="s">
+        <v>399</v>
+      </c>
       <c r="D138" s="47"/>
       <c r="E138" s="41" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>CommitteeProt_AMLRiskCat</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="13"/>
-      <c r="B139" s="19" t="s">
-        <v>416</v>
-      </c>
+      <c r="B139" s="15"/>
       <c r="C139" s="27"/>
       <c r="D139" s="47"/>
       <c r="E139" s="41" t="str">
@@ -4771,50 +4776,50 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="13"/>
-      <c r="B140" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="C140" s="27" t="s">
-        <v>400</v>
-      </c>
+      <c r="B140" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C140" s="27"/>
       <c r="D140" s="47"/>
       <c r="E140" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EconomicSectorEFSE</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="13"/>
       <c r="B141" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C141" s="27" t="s">
-        <v>94</v>
+        <v>400</v>
       </c>
       <c r="D141" s="47"/>
       <c r="E141" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EconomicSector</v>
+        <v>EconomicSectorEFSE</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="22" t="s">
-        <v>429</v>
-      </c>
-      <c r="B142" s="20"/>
-      <c r="C142" s="16"/>
+      <c r="A142" s="13"/>
+      <c r="B142" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C142" s="27" t="s">
+        <v>94</v>
+      </c>
       <c r="D142" s="47"/>
       <c r="E142" s="41" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>EconomicSector</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="13"/>
-      <c r="B143" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="C143" s="33"/>
+      <c r="A143" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="B143" s="20"/>
+      <c r="C143" s="16"/>
       <c r="D143" s="47"/>
       <c r="E143" s="41" t="str">
         <f t="shared" si="2"/>
@@ -4823,48 +4828,48 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="13"/>
-      <c r="B144" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="C144" s="27" t="s">
-        <v>424</v>
-      </c>
+      <c r="B144" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C144" s="33"/>
       <c r="D144" s="47"/>
       <c r="E144" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeePositionID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="13"/>
       <c r="B145" s="15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C145" s="27" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D145" s="47"/>
       <c r="E145" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeePosition</v>
+        <v>EmployeePositionID</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="13"/>
-      <c r="B146" s="15"/>
-      <c r="C146" s="33"/>
+      <c r="B146" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C146" s="27" t="s">
+        <v>425</v>
+      </c>
       <c r="D146" s="47"/>
       <c r="E146" s="41" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>EmployeePosition</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="B147" s="20"/>
-      <c r="C147" s="16"/>
+      <c r="A147" s="13"/>
+      <c r="B147" s="15"/>
+      <c r="C147" s="33"/>
       <c r="D147" s="47"/>
       <c r="E147" s="41" t="str">
         <f t="shared" si="2"/>
@@ -4872,11 +4877,11 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="13"/>
-      <c r="B148" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="C148" s="33"/>
+      <c r="A148" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="B148" s="20"/>
+      <c r="C148" s="16"/>
       <c r="D148" s="47"/>
       <c r="E148" s="41" t="str">
         <f t="shared" si="2"/>
@@ -4885,176 +4890,176 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="13"/>
-      <c r="B149" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="C149" s="27" t="s">
-        <v>431</v>
-      </c>
+      <c r="B149" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C149" s="33"/>
       <c r="D149" s="47"/>
       <c r="E149" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeeID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="13"/>
       <c r="B150" s="15" t="s">
-        <v>438</v>
+        <v>170</v>
       </c>
       <c r="C150" s="27" t="s">
-        <v>10</v>
+        <v>431</v>
       </c>
       <c r="D150" s="47"/>
       <c r="E150" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>BranchID</v>
+        <v>EmployeeID</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="13"/>
       <c r="B151" s="15" t="s">
-        <v>171</v>
+        <v>438</v>
       </c>
       <c r="C151" s="27" t="s">
-        <v>432</v>
+        <v>10</v>
       </c>
       <c r="D151" s="47"/>
       <c r="E151" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeeCode</v>
+        <v>BranchID</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="13"/>
       <c r="B152" s="15" t="s">
-        <v>426</v>
+        <v>171</v>
       </c>
       <c r="C152" s="27" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D152" s="47"/>
       <c r="E152" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeePositionID</v>
+        <v>EmployeeCode</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="13"/>
       <c r="B153" s="15" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="C153" s="27" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D153" s="47"/>
       <c r="E153" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeeName</v>
+        <v>EmployeePositionID</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="13"/>
       <c r="B154" s="15" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="C154" s="27" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D154" s="47"/>
       <c r="E154" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeePosition</v>
+        <v>EmployeeName</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="13"/>
       <c r="B155" s="15" t="s">
-        <v>172</v>
+        <v>427</v>
       </c>
       <c r="C155" s="27" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D155" s="47"/>
       <c r="E155" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>HireDate</v>
+        <v>EmployeePosition</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="13"/>
       <c r="B156" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C156" s="27" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D156" s="47"/>
       <c r="E156" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>BirthDate</v>
+        <v>HireDate</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="13"/>
       <c r="B157" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C157" s="27" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D157" s="47"/>
       <c r="E157" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>DismissalDate</v>
+        <v>BirthDate</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="13"/>
       <c r="B158" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D158" s="47"/>
       <c r="E158" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>TimesheetNumber</v>
+        <v>DismissalDate</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="13"/>
       <c r="B159" s="15" t="s">
-        <v>440</v>
+        <v>175</v>
       </c>
       <c r="C159" s="27" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D159" s="47"/>
       <c r="E159" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmploymentPositionType</v>
+        <v>TimesheetNumber</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="22" t="s">
-        <v>442</v>
-      </c>
-      <c r="B160" s="20"/>
-      <c r="C160" s="34"/>
+      <c r="A160" s="13"/>
+      <c r="B160" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C160" s="27" t="s">
+        <v>441</v>
+      </c>
       <c r="D160" s="47"/>
       <c r="E160" s="41" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>EmploymentPositionType</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="23"/>
-      <c r="B161" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="C161" s="26"/>
+      <c r="A161" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="B161" s="20"/>
+      <c r="C161" s="34"/>
       <c r="D161" s="47"/>
       <c r="E161" s="41" t="str">
         <f t="shared" si="2"/>
@@ -5062,163 +5067,163 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="13"/>
-      <c r="B162" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="C162" s="27" t="s">
-        <v>176</v>
-      </c>
+      <c r="A162" s="23"/>
+      <c r="B162" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="C162" s="26"/>
       <c r="D162" s="47"/>
       <c r="E162" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Period</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="13"/>
       <c r="B163" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C163" s="27" t="s">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="D163" s="47"/>
       <c r="E163" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>ID</v>
+        <v>Period</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="13"/>
       <c r="B164" s="15" t="s">
-        <v>188</v>
+        <v>446</v>
       </c>
       <c r="C164" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D164" s="47"/>
       <c r="E164" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>RowNumber</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="13"/>
       <c r="B165" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C165" s="27" t="s">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="D165" s="47"/>
       <c r="E165" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>IsActive</v>
+        <v>RowNumber</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="13"/>
       <c r="B166" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C166" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D166" s="47"/>
       <c r="E166" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Credit_ID</v>
+        <v>IsActive</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="13"/>
       <c r="B167" s="15" t="s">
-        <v>447</v>
+        <v>186</v>
       </c>
       <c r="C167" s="27" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="D167" s="47"/>
       <c r="E167" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Credit</v>
+        <v>Credit_ID</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="13"/>
       <c r="B168" s="15" t="s">
-        <v>62</v>
+        <v>447</v>
       </c>
       <c r="C168" s="27" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="D168" s="47"/>
       <c r="E168" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Filial_ID</v>
+        <v>Credit</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="13"/>
       <c r="B169" s="15" t="s">
-        <v>184</v>
+        <v>62</v>
       </c>
       <c r="C169" s="27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D169" s="47"/>
       <c r="E169" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Filial</v>
+        <v>Filial_ID</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="13"/>
       <c r="B170" s="15" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="C170" s="27" t="s">
-        <v>443</v>
+        <v>180</v>
       </c>
       <c r="D170" s="47"/>
       <c r="E170" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Employee_ID</v>
+        <v>Filial</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="13"/>
       <c r="B171" s="15" t="s">
-        <v>448</v>
+        <v>61</v>
       </c>
       <c r="C171" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D171" s="47"/>
       <c r="E171" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Employee</v>
+        <v>Employee_ID</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="22" t="s">
-        <v>451</v>
-      </c>
-      <c r="B172" s="20"/>
-      <c r="C172" s="34"/>
+      <c r="A172" s="13"/>
+      <c r="B172" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C172" s="27" t="s">
+        <v>444</v>
+      </c>
       <c r="D172" s="47"/>
       <c r="E172" s="41" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>Employee</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="13"/>
-      <c r="B173" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="C173" s="42"/>
+      <c r="A173" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="B173" s="20"/>
+      <c r="C173" s="34"/>
       <c r="D173" s="47"/>
       <c r="E173" s="41" t="str">
         <f t="shared" si="2"/>
@@ -5227,2354 +5232,2356 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="13"/>
-      <c r="B174" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="C174" s="27" t="s">
-        <v>452</v>
-      </c>
+      <c r="B174" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="C174" s="42"/>
       <c r="D174" s="47"/>
       <c r="E174" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Period</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="13"/>
       <c r="B175" s="15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C175" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D175" s="47"/>
       <c r="E175" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_ID</v>
+        <v>Event_Period</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="13"/>
       <c r="B176" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C176" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D176" s="47"/>
       <c r="E176" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_ClientID</v>
+        <v>Event_ID</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="13"/>
       <c r="B177" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C177" s="27" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D177" s="47"/>
       <c r="E177" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Status</v>
+        <v>Event_ClientID</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="13"/>
       <c r="B178" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C178" s="27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D178" s="47"/>
       <c r="E178" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Kind</v>
+        <v>Event_Status</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C179" s="27" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D179" s="47"/>
       <c r="E179" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Type</v>
+        <v>Event_Kind</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="13"/>
       <c r="B180" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C180" s="27" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D180" s="47"/>
       <c r="E180" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Project</v>
+        <v>Event_Type</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="13"/>
       <c r="B181" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C181" s="27" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D181" s="47"/>
       <c r="E181" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Content</v>
+        <v>Event_Project</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="13"/>
       <c r="B182" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C182" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D182" s="47"/>
       <c r="E182" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_ResponsibleID</v>
+        <v>Event_Content</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="13"/>
       <c r="B183" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C183" s="27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D183" s="47"/>
       <c r="E183" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Responsible</v>
+        <v>Event_ResponsibleID</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="13"/>
       <c r="B184" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C184" s="27" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D184" s="47"/>
       <c r="E184" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_NextDateEvent</v>
+        <v>Event_Responsible</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="13"/>
       <c r="B185" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C185" s="27" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D185" s="47"/>
       <c r="E185" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_NextKindEvent</v>
+        <v>Event_NextDateEvent</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="13"/>
       <c r="B186" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C186" s="27" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D186" s="47"/>
       <c r="E186" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_BranchID</v>
+        <v>Event_NextKindEvent</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="13"/>
       <c r="B187" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C187" s="27" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D187" s="47"/>
       <c r="E187" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>Event_Branch_Name</v>
+        <v>Event_BranchID</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="13"/>
       <c r="B188" s="15" t="s">
-        <v>427</v>
+        <v>480</v>
       </c>
       <c r="C188" s="27" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="D188" s="47"/>
       <c r="E188" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>EmployeePosition</v>
+        <v>Event_Branch_Name</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="13"/>
       <c r="B189" s="15" t="s">
-        <v>481</v>
+        <v>427</v>
       </c>
       <c r="C189" s="27" t="s">
-        <v>463</v>
+        <v>425</v>
       </c>
       <c r="D189" s="47"/>
       <c r="E189" s="41" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">EmployeeBranch </v>
+        <v>EmployeePosition</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="13"/>
-      <c r="B190" s="15"/>
-      <c r="C190" s="33"/>
+      <c r="B190" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C190" s="27" t="s">
+        <v>463</v>
+      </c>
       <c r="D190" s="47"/>
-      <c r="E190" s="41"/>
+      <c r="E190" s="41" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">EmployeeBranch </v>
+      </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="22" t="s">
+      <c r="A191" s="13"/>
+      <c r="B191" s="15"/>
+      <c r="C191" s="33"/>
+      <c r="D191" s="47"/>
+      <c r="E191" s="41"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="22" t="s">
         <v>483</v>
       </c>
-      <c r="B191" s="20"/>
-      <c r="C191" s="34"/>
-      <c r="D191" s="47"/>
-      <c r="E191" s="41" t="str">
-        <f t="shared" ref="E191:E205" si="3">IF(C191&gt;0,IF(D191&gt;0,D191, C191)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="13"/>
-      <c r="B192" s="19" t="s">
-        <v>501</v>
-      </c>
-      <c r="C192" s="42"/>
+      <c r="B192" s="20"/>
+      <c r="C192" s="34"/>
       <c r="D192" s="47"/>
       <c r="E192" s="41" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E192:E206" si="3">IF(C192&gt;0,IF(D192&gt;0,D192, C192)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="13"/>
-      <c r="B193" s="15" t="s">
-        <v>494</v>
-      </c>
-      <c r="C193" s="27" t="s">
-        <v>374</v>
-      </c>
+      <c r="B193" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="C193" s="42"/>
       <c r="D193" s="47"/>
       <c r="E193" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>GroupID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="13"/>
       <c r="B194" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C194" s="27" t="s">
-        <v>484</v>
+        <v>374</v>
       </c>
       <c r="D194" s="47"/>
       <c r="E194" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>PersonID</v>
+        <v>GroupID</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="13"/>
       <c r="B195" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C195" s="27" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D195" s="47"/>
       <c r="E195" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>PersonName</v>
+        <v>PersonID</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="13"/>
       <c r="B196" s="15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C196" s="27" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D196" s="47"/>
       <c r="E196" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>PeriodOriginal</v>
+        <v>PersonName</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="13"/>
       <c r="B197" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C197" s="27" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D197" s="47"/>
       <c r="E197" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>ActiveFlag</v>
+        <v>PeriodOriginal</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="13"/>
       <c r="B198" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C198" s="27" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D198" s="47"/>
       <c r="E198" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>ExcludedFlag</v>
+        <v>ActiveFlag</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="13"/>
       <c r="B199" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C199" s="27" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D199" s="47"/>
       <c r="E199" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>GroupName</v>
+        <v>ExcludedFlag</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="13"/>
-      <c r="B200" s="15"/>
-      <c r="C200" s="27"/>
+      <c r="B200" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="C200" s="27" t="s">
+        <v>489</v>
+      </c>
       <c r="D200" s="47"/>
-      <c r="E200" s="41"/>
+      <c r="E200" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v>GroupName</v>
+      </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="13"/>
-      <c r="B201" s="19" t="s">
-        <v>410</v>
-      </c>
+      <c r="B201" s="15"/>
       <c r="C201" s="27"/>
       <c r="D201" s="47"/>
       <c r="E201" s="41"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="13"/>
-      <c r="B202" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="C202" s="27" t="s">
-        <v>490</v>
-      </c>
+      <c r="B202" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="C202" s="27"/>
       <c r="D202" s="47"/>
-      <c r="E202" s="41" t="str">
-        <f t="shared" si="3"/>
-        <v>GroupOwner</v>
-      </c>
+      <c r="E202" s="41"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="13"/>
       <c r="B203" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C203" s="27" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D203" s="47"/>
       <c r="E203" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>GroupCode</v>
+        <v>GroupOwner</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="13"/>
       <c r="B204" s="15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C204" s="27" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D204" s="47"/>
       <c r="E204" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>GroupNameFull</v>
+        <v>GroupCode</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="13"/>
       <c r="B205" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C205" s="27" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D205" s="47"/>
       <c r="E205" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>GroupOwnerTax</v>
+        <v>GroupNameFull</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="13"/>
-      <c r="B206" s="15"/>
-      <c r="C206" s="33"/>
+      <c r="B206" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="C206" s="27" t="s">
+        <v>493</v>
+      </c>
       <c r="D206" s="47"/>
       <c r="E206" s="41" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="3"/>
+        <v>GroupOwnerTax</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" s="22" t="s">
-        <v>506</v>
-      </c>
-      <c r="B207" s="17"/>
-      <c r="C207" s="21"/>
+      <c r="A207" s="13"/>
+      <c r="B207" s="15"/>
+      <c r="C207" s="33"/>
       <c r="D207" s="47"/>
       <c r="E207" s="41" t="str">
-        <f>IF(C207&gt;0,IF(D207&gt;0,D207, C207)," ")</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" s="12"/>
-      <c r="B208" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C208" s="26"/>
+      <c r="A208" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="B208" s="17"/>
+      <c r="C208" s="21"/>
       <c r="D208" s="47"/>
       <c r="E208" s="41" t="str">
-        <f>IF(C208&gt;0,IF(D208&gt;0,D208, C208)," ")</f>
+        <f t="shared" ref="E208:E213" si="4">IF(C208&gt;0,IF(D208&gt;0,D208, C208)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="3"/>
-      <c r="B209" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C209" s="27" t="s">
-        <v>516</v>
-      </c>
+      <c r="A209" s="12"/>
+      <c r="B209" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C209" s="26"/>
       <c r="D209" s="47"/>
       <c r="E209" s="41" t="str">
-        <f>IF(C209&gt;0,IF(D209&gt;0,D209, C209)," ")</f>
-        <v>PartnerBranchID</v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
       <c r="B210" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C210" s="27" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D210" s="47"/>
       <c r="E210" s="41" t="str">
-        <f>IF(C210&gt;0,IF(D210&gt;0,D210, C210)," ")</f>
-        <v>PartnerBranchDeletedFlag</v>
+        <f t="shared" si="4"/>
+        <v>PartnerBranchID</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
       <c r="B211" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C211" s="27" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D211" s="47"/>
       <c r="E211" s="41" t="str">
-        <f>IF(C211&gt;0,IF(D211&gt;0,D211, C211)," ")</f>
-        <v>PartnerBranchOwner</v>
+        <f t="shared" si="4"/>
+        <v>PartnerBranchDeletedFlag</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="3"/>
       <c r="B212" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C212" s="27" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D212" s="47"/>
       <c r="E212" s="41" t="str">
-        <f>IF(C212&gt;0,IF(D212&gt;0,D212, C212)," ")</f>
-        <v>PartnerBranchCode</v>
+        <f t="shared" si="4"/>
+        <v>PartnerBranchOwner</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="3"/>
       <c r="B213" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C213" s="27" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D213" s="47"/>
       <c r="E213" s="41" t="str">
-        <f t="shared" ref="E213:E358" si="4">IF(C213&gt;0,IF(D213&gt;0,D213, C213)," ")</f>
-        <v>PartnerBranchName</v>
+        <f t="shared" si="4"/>
+        <v>PartnerBranchCode</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="3"/>
       <c r="B214" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C214" s="27" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D214" s="47"/>
       <c r="E214" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>PartnerBranchAddress</v>
+        <f t="shared" ref="E214:E359" si="5">IF(C214&gt;0,IF(D214&gt;0,D214, C214)," ")</f>
+        <v>PartnerBranchName</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="3"/>
-      <c r="B215" s="2"/>
-      <c r="C215" s="27"/>
+      <c r="B215" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C215" s="27" t="s">
+        <v>511</v>
+      </c>
       <c r="D215" s="47"/>
       <c r="E215" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="5"/>
+        <v>PartnerBranchAddress</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="3"/>
-      <c r="B216" s="5" t="s">
-        <v>407</v>
-      </c>
+      <c r="B216" s="2"/>
       <c r="C216" s="27"/>
       <c r="D216" s="47"/>
       <c r="E216" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="3"/>
-      <c r="B217" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C217" s="27" t="s">
-        <v>510</v>
-      </c>
+      <c r="B217" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C217" s="27"/>
       <c r="D217" s="47"/>
       <c r="E217" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>PartnerOwnerName</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="3"/>
-      <c r="C218" s="27"/>
+      <c r="B218" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C218" s="27" t="s">
+        <v>510</v>
+      </c>
       <c r="D218" s="47"/>
       <c r="E218" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="5"/>
+        <v>PartnerOwnerName</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="3"/>
-      <c r="B219" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C219" s="27"/>
       <c r="D219" s="47"/>
       <c r="E219" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="3"/>
-      <c r="B220" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C220" s="27" t="s">
-        <v>221</v>
-      </c>
+      <c r="B220" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C220" s="27"/>
       <c r="D220" s="47"/>
       <c r="E220" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>DealerID</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="3"/>
       <c r="B221" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C221" s="27" t="s">
-        <v>522</v>
+        <v>221</v>
       </c>
       <c r="D221" s="47"/>
       <c r="E221" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>DealerDefaultEmployeeID</v>
+        <f t="shared" si="5"/>
+        <v>DealerID</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="3"/>
       <c r="B222" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C222" s="27" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D222" s="47"/>
       <c r="E222" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>DealerDefaultEmployeeName</v>
+        <f t="shared" si="5"/>
+        <v>DealerDefaultEmployeeID</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="3"/>
       <c r="B223" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C223" s="27" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D223" s="47"/>
       <c r="E223" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>DealerOrgRepID</v>
+        <f t="shared" si="5"/>
+        <v>DealerDefaultEmployeeName</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="3"/>
       <c r="B224" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C224" s="27" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D224" s="47"/>
       <c r="E224" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>DealerOrgRepName</v>
+        <f t="shared" si="5"/>
+        <v>DealerOrgRepID</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="3"/>
       <c r="B225" s="2" t="s">
-        <v>518</v>
+        <v>249</v>
       </c>
       <c r="C225" s="27" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D225" s="47"/>
       <c r="E225" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>DealerCabinetID</v>
+        <f t="shared" si="5"/>
+        <v>DealerOrgRepName</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="3"/>
       <c r="B226" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C226" s="27" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D226" s="47"/>
       <c r="E226" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>DealerCabinetType</v>
+        <f t="shared" si="5"/>
+        <v>DealerCabinetID</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="3"/>
       <c r="B227" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C227" s="27" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D227" s="47"/>
       <c r="E227" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>Contact_Info</v>
+        <f t="shared" si="5"/>
+        <v>DealerCabinetType</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="3"/>
-      <c r="B228" s="2"/>
-      <c r="C228" s="27"/>
+      <c r="B228" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C228" s="27" t="s">
+        <v>528</v>
+      </c>
       <c r="D228" s="47"/>
       <c r="E228" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="5"/>
+        <v>Contact_Info</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A229" s="22" t="s">
-        <v>521</v>
-      </c>
-      <c r="B229" s="20"/>
-      <c r="C229" s="16"/>
+      <c r="A229" s="3"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="27"/>
       <c r="D229" s="47"/>
       <c r="E229" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="12"/>
-      <c r="B230" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="C230" s="35"/>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="22" t="s">
+        <v>521</v>
+      </c>
+      <c r="B230" s="20"/>
+      <c r="C230" s="16"/>
       <c r="D230" s="47"/>
       <c r="E230" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="12"/>
-      <c r="B231" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="C231" s="27" t="s">
-        <v>529</v>
-      </c>
+      <c r="B231" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="C231" s="35"/>
       <c r="D231" s="47"/>
       <c r="E231" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12"/>
       <c r="B232" s="11" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C232" s="27" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D232" s="47"/>
       <c r="E232" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Deleted  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_ID  </v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="12"/>
       <c r="B233" s="11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C233" s="27" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D233" s="47"/>
       <c r="E233" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Date  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Deleted  </v>
       </c>
     </row>
     <row r="234" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12"/>
       <c r="B234" s="11" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C234" s="27" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D234" s="47"/>
       <c r="E234" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Number  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Date  </v>
       </c>
     </row>
     <row r="235" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="12"/>
       <c r="B235" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C235" s="27" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D235" s="47"/>
       <c r="E235" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Completed  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Number  </v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12"/>
       <c r="B236" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C236" s="27" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D236" s="47"/>
       <c r="E236" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Author_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Completed  </v>
       </c>
     </row>
     <row r="237" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="12"/>
       <c r="B237" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C237" s="27" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D237" s="47"/>
       <c r="E237" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Author  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Author_ID  </v>
       </c>
     </row>
     <row r="238" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12"/>
       <c r="B238" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C238" s="27" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D238" s="47"/>
       <c r="E238" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Branch_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Author  </v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="12"/>
       <c r="B239" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D239" s="47"/>
       <c r="E239" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Branch  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Branch_ID  </v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12"/>
       <c r="B240" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C240" s="27" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D240" s="47"/>
       <c r="E240" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Category_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Branch  </v>
       </c>
     </row>
     <row r="241" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12"/>
       <c r="B241" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C241" s="27" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D241" s="47"/>
       <c r="E241" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Category  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Category_ID  </v>
       </c>
     </row>
     <row r="242" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12"/>
       <c r="B242" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C242" s="27" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D242" s="47"/>
       <c r="E242" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Type_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Category  </v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="12"/>
       <c r="B243" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C243" s="27" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D243" s="47"/>
       <c r="E243" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Type  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Type_ID  </v>
       </c>
     </row>
     <row r="244" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12"/>
       <c r="B244" s="11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C244" s="27" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D244" s="47"/>
       <c r="E244" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Description  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Type  </v>
       </c>
     </row>
     <row r="245" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="12"/>
       <c r="B245" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C245" s="27" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D245" s="47"/>
       <c r="E245" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Base_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Description  </v>
       </c>
     </row>
     <row r="246" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12"/>
       <c r="B246" s="11" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C246" s="27" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D246" s="47"/>
       <c r="E246" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Source_Type  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Base_ID  </v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="12"/>
       <c r="B247" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C247" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D247" s="47"/>
       <c r="E247" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Source_View  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Source_Type  </v>
       </c>
     </row>
     <row r="248" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12"/>
       <c r="B248" s="11" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C248" s="27" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D248" s="47"/>
       <c r="E248" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Source_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Source_View  </v>
       </c>
     </row>
     <row r="249" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="12"/>
       <c r="B249" s="11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C249" s="27" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D249" s="47"/>
       <c r="E249" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Client_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Source_ID  </v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12"/>
       <c r="B250" s="11" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C250" s="27" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D250" s="47"/>
       <c r="E250" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Client  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Client_ID  </v>
       </c>
     </row>
     <row r="251" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="12"/>
       <c r="B251" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C251" s="27" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D251" s="47"/>
       <c r="E251" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Credit_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Client  </v>
       </c>
     </row>
     <row r="252" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12"/>
       <c r="B252" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C252" s="27" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D252" s="47"/>
       <c r="E252" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Credit  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Credit_ID  </v>
       </c>
     </row>
     <row r="253" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="12"/>
       <c r="B253" s="11" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C253" s="27" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D253" s="47"/>
       <c r="E253" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Limit_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Credit  </v>
       </c>
     </row>
     <row r="254" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12"/>
       <c r="B254" s="11" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C254" s="27" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D254" s="47"/>
       <c r="E254" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Limit  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Limit_ID  </v>
       </c>
     </row>
     <row r="255" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="12"/>
       <c r="B255" s="11" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C255" s="27" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D255" s="47"/>
       <c r="E255" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>AdminTask_CurrentStatus</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Limit  </v>
       </c>
     </row>
     <row r="256" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12"/>
       <c r="B256" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C256" s="27" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D256" s="47"/>
       <c r="E256" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_CurrentStatus_ID  </v>
+        <f t="shared" si="5"/>
+        <v>AdminTask_CurrentStatus</v>
       </c>
     </row>
     <row r="257" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="12"/>
       <c r="B257" s="11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C257" s="27" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D257" s="47"/>
       <c r="E257" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_CompletionDate  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_CurrentStatus_ID  </v>
       </c>
     </row>
     <row r="258" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12"/>
       <c r="B258" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C258" s="27" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D258" s="47"/>
       <c r="E258" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>AdminTask_CurrentComment</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_CompletionDate  </v>
       </c>
     </row>
     <row r="259" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="12"/>
       <c r="B259" s="11" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C259" s="27" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="D259" s="47"/>
       <c r="E259" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>AdminTask_TaskCount</v>
+        <f t="shared" si="5"/>
+        <v>AdminTask_CurrentComment</v>
       </c>
     </row>
     <row r="260" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
       <c r="B260" s="11" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C260" s="27" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D260" s="47"/>
       <c r="E260" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>AdminTask_Priority</v>
+        <f t="shared" si="5"/>
+        <v>AdminTask_TaskCount</v>
       </c>
     </row>
     <row r="261" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="12"/>
       <c r="B261" s="11" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C261" s="27" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="D261" s="47"/>
       <c r="E261" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Priority_ID  </v>
+        <f t="shared" si="5"/>
+        <v>AdminTask_Priority</v>
       </c>
     </row>
     <row r="262" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12"/>
       <c r="B262" s="11" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C262" s="27" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D262" s="47"/>
       <c r="E262" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AdminTask_Executor  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Priority_ID  </v>
       </c>
     </row>
     <row r="263" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12"/>
       <c r="B263" s="11" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C263" s="27" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="D263" s="47"/>
       <c r="E263" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">StatusHistory_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">AdminTask_Executor  </v>
       </c>
     </row>
     <row r="264" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12"/>
       <c r="B264" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C264" s="27" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="D264" s="47"/>
       <c r="E264" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>StatusHistory_RowNumber</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">StatusHistory_ID  </v>
       </c>
     </row>
     <row r="265" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12"/>
       <c r="B265" s="11" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="C265" s="27" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D265" s="47"/>
       <c r="E265" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>StatusHistory_Status</v>
+        <f t="shared" si="5"/>
+        <v>StatusHistory_RowNumber</v>
       </c>
     </row>
     <row r="266" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12"/>
       <c r="B266" s="11" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="C266" s="27" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="D266" s="47"/>
       <c r="E266" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">StatusHistory_UserID  </v>
+        <f t="shared" si="5"/>
+        <v>StatusHistory_Status</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12"/>
       <c r="B267" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C267" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D267" s="47"/>
       <c r="E267" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">StatusHistory_User  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">StatusHistory_UserID  </v>
       </c>
     </row>
     <row r="268" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12"/>
       <c r="B268" s="11" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C268" s="27" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D268" s="47"/>
       <c r="E268" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">StatusHistory_StartDate  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">StatusHistory_User  </v>
       </c>
     </row>
     <row r="269" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="12"/>
       <c r="B269" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C269" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D269" s="47"/>
       <c r="E269" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">StatusHistory_EndDate  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">StatusHistory_StartDate  </v>
       </c>
     </row>
     <row r="270" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12"/>
       <c r="B270" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C270" s="27" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="D270" s="47"/>
       <c r="E270" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>StatusHistory_Comment</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">StatusHistory_EndDate  </v>
       </c>
     </row>
     <row r="271" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="12"/>
       <c r="B271" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C271" s="27" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D271" s="47"/>
       <c r="E271" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>StatusHistory_Comment</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="12"/>
+      <c r="B272" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="C272" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="D272" s="47"/>
+      <c r="E272" s="41" t="str">
+        <f t="shared" si="5"/>
         <v>StatusHistory_Seconds</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="12"/>
-      <c r="B272" s="11"/>
-      <c r="C272" s="27"/>
-      <c r="D272" s="49"/>
-      <c r="E272" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="12"/>
-      <c r="B273" s="5" t="s">
-        <v>658</v>
-      </c>
+      <c r="B273" s="11"/>
       <c r="C273" s="27"/>
       <c r="D273" s="49"/>
       <c r="E273" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="12"/>
-      <c r="B274" s="11" t="s">
-        <v>623</v>
-      </c>
-      <c r="C274" s="27" t="s">
-        <v>557</v>
-      </c>
-      <c r="D274" s="47"/>
+      <c r="B274" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="C274" s="27"/>
+      <c r="D274" s="49"/>
       <c r="E274" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>AdminTask_SLA</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="275" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="12"/>
       <c r="B275" s="11" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C275" s="27" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="D275" s="47"/>
       <c r="E275" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>AdminTask_KPI</v>
+        <f t="shared" si="5"/>
+        <v>AdminTask_SLA</v>
       </c>
     </row>
     <row r="276" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12"/>
       <c r="B276" s="11" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="C276" s="27" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="D276" s="47"/>
       <c r="E276" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">TaskType_Deleted  </v>
+        <f t="shared" si="5"/>
+        <v>AdminTask_KPI</v>
       </c>
     </row>
     <row r="277" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="12"/>
       <c r="B277" s="11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C277" s="27" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D277" s="47"/>
       <c r="E277" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">TaskType_Parent_ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">TaskType_Deleted  </v>
       </c>
     </row>
     <row r="278" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12"/>
       <c r="B278" s="11" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="D278" s="47"/>
       <c r="E278" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>TaskType_IsGroup</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">TaskType_Parent_ID  </v>
       </c>
     </row>
     <row r="279" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="12"/>
       <c r="B279" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C279" s="27" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="D279" s="47"/>
       <c r="E279" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">TaskType_Code  </v>
+        <f t="shared" si="5"/>
+        <v>TaskType_IsGroup</v>
       </c>
     </row>
     <row r="280" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12"/>
       <c r="B280" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C280" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D280" s="47"/>
       <c r="E280" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">TaskType_Name  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">TaskType_Code  </v>
       </c>
     </row>
     <row r="281" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="12"/>
       <c r="B281" s="11" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C281" s="27" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="D281" s="47"/>
       <c r="E281" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>TaskType_Order</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">TaskType_Name  </v>
       </c>
     </row>
     <row r="282" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12"/>
       <c r="B282" s="11" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="C282" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D282" s="47"/>
       <c r="E282" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>TaskType_SLA</v>
+        <f t="shared" si="5"/>
+        <v>TaskType_Order</v>
       </c>
     </row>
     <row r="283" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="12"/>
       <c r="B283" s="11" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C283" s="27" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D283" s="47"/>
       <c r="E283" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>TaskType_KPI</v>
+        <f t="shared" si="5"/>
+        <v>TaskType_SLA</v>
       </c>
     </row>
     <row r="284" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12"/>
       <c r="B284" s="11" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C284" s="27" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D284" s="47"/>
       <c r="E284" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>TaskType_BlockEditCount</v>
+        <f t="shared" si="5"/>
+        <v>TaskType_KPI</v>
       </c>
     </row>
     <row r="285" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="12"/>
       <c r="B285" s="11" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C285" s="27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D285" s="47"/>
       <c r="E285" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>TaskType_BlockEditCount</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="12"/>
+      <c r="B286" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="C286" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="D286" s="47"/>
+      <c r="E286" s="41" t="str">
+        <f t="shared" si="5"/>
         <v>TaskType_MaxTime</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A286" s="12"/>
-      <c r="B286" s="11"/>
-      <c r="C286" s="27"/>
-      <c r="D286" s="49"/>
-      <c r="E286" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="12"/>
-      <c r="B287" s="5" t="s">
-        <v>659</v>
-      </c>
+      <c r="B287" s="11"/>
       <c r="C287" s="27"/>
       <c r="D287" s="49"/>
       <c r="E287" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="12"/>
-      <c r="B288" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="C288" s="35" t="s">
-        <v>569</v>
-      </c>
+      <c r="B288" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="C288" s="27"/>
       <c r="D288" s="49"/>
       <c r="E288" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Направление на Выплату ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="12"/>
       <c r="B289" s="11" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C289" s="35" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="D289" s="49"/>
       <c r="E289" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>СведенияОНаправленияхНаВыплату Направление на Выплату</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Направление на Выплату ID  </v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="12"/>
       <c r="B290" s="11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C290" s="35" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D290" s="49"/>
       <c r="E290" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>СведенияОНаправленияхНаВыплату SLA</v>
+        <f t="shared" si="5"/>
+        <v>СведенияОНаправленияхНаВыплату Направление на Выплату</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="12"/>
       <c r="B291" s="11" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C291" s="35" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D291" s="49"/>
       <c r="E291" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>СведенияОНаправленияхНаВыплату Максимальное Время Выполнения</v>
+        <f t="shared" si="5"/>
+        <v>СведенияОНаправленияхНаВыплату SLA</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="12"/>
       <c r="B292" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C292" s="35" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="D292" s="49"/>
       <c r="E292" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Создания  </v>
+        <f t="shared" si="5"/>
+        <v>СведенияОНаправленияхНаВыплату Максимальное Время Выполнения</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="12"/>
       <c r="B293" s="11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C293" s="35" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D293" s="49"/>
       <c r="E293" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Взятия в Работу  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Создания  </v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="12"/>
       <c r="B294" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C294" s="35" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D294" s="49"/>
       <c r="E294" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Утверждения  </v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Взятия в Работу  </v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="12"/>
       <c r="B295" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C295" s="35" t="s">
-        <v>573</v>
-      </c>
-      <c r="D295" s="47"/>
+        <v>572</v>
+      </c>
+      <c r="D295" s="49"/>
       <c r="E295" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Пометки Удаления  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Утверждения  </v>
       </c>
     </row>
     <row r="296" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12"/>
       <c r="B296" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C296" s="35" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D296" s="47"/>
       <c r="E296" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Тип Направления на Выплату ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Дата Пометки Удаления  </v>
       </c>
     </row>
     <row r="297" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="12"/>
       <c r="B297" s="11" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C297" s="35" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="D297" s="47"/>
       <c r="E297" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>СведенияОНаправленияхНаВыплату Тип Направления на Выплату</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">СведенияОНаправленияхНаВыплату Тип Направления на Выплату ID  </v>
       </c>
     </row>
     <row r="298" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12"/>
-      <c r="B298" s="11"/>
-      <c r="C298" s="35"/>
+      <c r="B298" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="C298" s="35" t="s">
+        <v>592</v>
+      </c>
       <c r="D298" s="47"/>
       <c r="E298" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="5"/>
+        <v>СведенияОНаправленияхНаВыплату Тип Направления на Выплату</v>
       </c>
     </row>
     <row r="299" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="12"/>
-      <c r="B299" s="5" t="s">
-        <v>660</v>
-      </c>
+      <c r="B299" s="11"/>
       <c r="C299" s="35"/>
       <c r="D299" s="47"/>
       <c r="E299" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="300" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12"/>
-      <c r="B300" s="11" t="s">
-        <v>656</v>
-      </c>
-      <c r="C300" s="35" t="s">
-        <v>575</v>
-      </c>
+      <c r="B300" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="C300" s="35"/>
       <c r="D300" s="47"/>
       <c r="E300" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">НаправлениеНаВыплату ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="301" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12"/>
       <c r="B301" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C301" s="35" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="D301" s="47"/>
       <c r="E301" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>НаправлениеНаВыплату Категория Риска AML</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">НаправлениеНаВыплату ID  </v>
       </c>
     </row>
     <row r="302" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="12"/>
-      <c r="B302" s="11"/>
-      <c r="C302" s="35"/>
+      <c r="B302" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="C302" s="35" t="s">
+        <v>593</v>
+      </c>
       <c r="D302" s="47"/>
       <c r="E302" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A303" s="22" t="s">
-        <v>661</v>
-      </c>
-      <c r="B303" s="20"/>
-      <c r="C303" s="16"/>
+        <f t="shared" si="5"/>
+        <v>НаправлениеНаВыплату Категория Риска AML</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="12"/>
+      <c r="B303" s="11"/>
+      <c r="C303" s="35"/>
       <c r="D303" s="47"/>
       <c r="E303" s="41" t="str">
-        <f t="shared" ref="E303" si="5">IF(C303&gt;0,IF(D303&gt;0,D303, C303)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="12"/>
-      <c r="B304" s="11"/>
-      <c r="C304" s="35"/>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="22" t="s">
+        <v>661</v>
+      </c>
+      <c r="B304" s="20"/>
+      <c r="C304" s="16"/>
       <c r="D304" s="47"/>
       <c r="E304" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E304" si="6">IF(C304&gt;0,IF(D304&gt;0,D304, C304)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="305" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12"/>
       <c r="B305" s="11"/>
-      <c r="C305" s="35" t="s">
-        <v>662</v>
-      </c>
+      <c r="C305" s="35"/>
       <c r="D305" s="47"/>
       <c r="E305" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>АктыПередачиКредитныхДел Период</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="306" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="12"/>
       <c r="B306" s="11"/>
       <c r="C306" s="35" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D306" s="47"/>
       <c r="E306" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел ID              </v>
+        <f t="shared" si="5"/>
+        <v>АктыПередачиКредитныхДел Период</v>
       </c>
     </row>
     <row r="307" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12"/>
       <c r="B307" s="11"/>
       <c r="C307" s="35" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D307" s="47"/>
       <c r="E307" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Номер Строки    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел ID              </v>
       </c>
     </row>
     <row r="308" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="12"/>
       <c r="B308" s="11"/>
       <c r="C308" s="35" t="s">
-        <v>710</v>
+        <v>664</v>
       </c>
       <c r="D308" s="47"/>
       <c r="E308" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>АктыПередачиКредитныхДел Активность</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Номер Строки    </v>
       </c>
     </row>
     <row r="309" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12"/>
       <c r="B309" s="11"/>
       <c r="C309" s="35" t="s">
-        <v>666</v>
+        <v>710</v>
       </c>
       <c r="D309" s="47"/>
       <c r="E309" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Кредит Tип      </v>
+        <f t="shared" si="5"/>
+        <v>АктыПередачиКредитныхДел Активность</v>
       </c>
     </row>
     <row r="310" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="12"/>
       <c r="B310" s="11"/>
       <c r="C310" s="35" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D310" s="47"/>
       <c r="E310" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Кредит Вид      </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Кредит Tип      </v>
       </c>
     </row>
     <row r="311" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12"/>
       <c r="B311" s="11"/>
       <c r="C311" s="35" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D311" s="47"/>
       <c r="E311" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Кредит ID       </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Кредит Вид      </v>
       </c>
     </row>
     <row r="312" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="12"/>
       <c r="B312" s="11"/>
       <c r="C312" s="35" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D312" s="47"/>
       <c r="E312" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Контрагент ID   </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Кредит ID       </v>
       </c>
     </row>
     <row r="313" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="12"/>
       <c r="B313" s="11"/>
       <c r="C313" s="35" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D313" s="47"/>
       <c r="E313" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Контрагент      </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Контрагент ID   </v>
       </c>
     </row>
     <row r="314" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="12"/>
       <c r="B314" s="11"/>
       <c r="C314" s="35" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D314" s="47"/>
       <c r="E314" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Акта        </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Контрагент      </v>
       </c>
     </row>
     <row r="315" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="12"/>
       <c r="B315" s="11"/>
       <c r="C315" s="35" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D315" s="47"/>
       <c r="E315" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Tип  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Акта        </v>
       </c>
     </row>
     <row r="316" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="12"/>
       <c r="B316" s="11"/>
       <c r="C316" s="35" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D316" s="47"/>
       <c r="E316" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Вид  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Tип  </v>
       </c>
     </row>
     <row r="317" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="12"/>
       <c r="B317" s="11"/>
       <c r="C317" s="35" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D317" s="47"/>
       <c r="E317" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Вид  </v>
       </c>
     </row>
     <row r="318" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="12"/>
       <c r="B318" s="11"/>
       <c r="C318" s="35" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D318" s="47"/>
       <c r="E318" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Документ Tип  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции ID  </v>
       </c>
     </row>
     <row r="319" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="12"/>
       <c r="B319" s="11"/>
       <c r="C319" s="35" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D319" s="47"/>
       <c r="E319" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Документ Вид  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Документ Tип  </v>
       </c>
     </row>
     <row r="320" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="12"/>
       <c r="B320" s="11"/>
       <c r="C320" s="35" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D320" s="47"/>
       <c r="E320" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Документ ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Документ Вид  </v>
       </c>
     </row>
     <row r="321" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="12"/>
       <c r="B321" s="11"/>
       <c r="C321" s="35" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D321" s="47"/>
       <c r="E321" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Акта Передачи Кредитных Дел  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Операции Документ ID  </v>
       </c>
     </row>
     <row r="322" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="12"/>
       <c r="B322" s="11"/>
       <c r="C322" s="35" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D322" s="47"/>
       <c r="E322" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Статус Досье  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Вид Акта Передачи Кредитных Дел  </v>
       </c>
     </row>
     <row r="323" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="12"/>
       <c r="B323" s="11"/>
       <c r="C323" s="35" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D323" s="47"/>
       <c r="E323" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Статус Акта  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Статус Досье  </v>
       </c>
     </row>
     <row r="324" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="12"/>
       <c r="B324" s="11"/>
       <c r="C324" s="35" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D324" s="47"/>
       <c r="E324" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Получатель Tип  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Статус Акта  </v>
       </c>
     </row>
     <row r="325" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="12"/>
       <c r="B325" s="11"/>
       <c r="C325" s="35" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D325" s="47"/>
       <c r="E325" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Получатель Вид  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Получатель Tип  </v>
       </c>
     </row>
     <row r="326" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="12"/>
       <c r="B326" s="11"/>
       <c r="C326" s="35" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D326" s="47"/>
       <c r="E326" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Получатель ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Получатель Вид  </v>
       </c>
     </row>
     <row r="327" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="12"/>
       <c r="B327" s="11"/>
       <c r="C327" s="35" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D327" s="47"/>
       <c r="E327" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Дата Получения  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Получатель ID  </v>
       </c>
     </row>
     <row r="328" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="12"/>
       <c r="B328" s="11"/>
       <c r="C328" s="35" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D328" s="47"/>
       <c r="E328" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Дата Проверки  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Дата Получения  </v>
       </c>
     </row>
     <row r="329" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="12"/>
       <c r="B329" s="11"/>
       <c r="C329" s="35" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D329" s="47"/>
       <c r="E329" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Комментарий  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Дата Проверки  </v>
       </c>
     </row>
     <row r="330" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="12"/>
       <c r="B330" s="11"/>
       <c r="C330" s="35" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D330" s="47"/>
       <c r="E330" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Автор ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Комментарий  </v>
       </c>
     </row>
     <row r="331" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="12"/>
       <c r="B331" s="11"/>
       <c r="C331" s="35" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D331" s="47"/>
       <c r="E331" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Автор  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Автор ID  </v>
       </c>
     </row>
     <row r="332" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="12"/>
       <c r="B332" s="11"/>
       <c r="C332" s="35" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D332" s="47"/>
       <c r="E332" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">АктыПередачиКредитныхДел Дедлайн  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Автор  </v>
       </c>
     </row>
     <row r="333" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="12"/>
       <c r="B333" s="11"/>
       <c r="C333" s="35" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D333" s="47"/>
       <c r="E333" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Период  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">АктыПередачиКредитныхДел Дедлайн  </v>
       </c>
     </row>
     <row r="334" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="12"/>
       <c r="B334" s="11"/>
       <c r="C334" s="35" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D334" s="47"/>
       <c r="E334" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Период  </v>
       </c>
     </row>
     <row r="335" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="12"/>
       <c r="B335" s="11"/>
       <c r="C335" s="35" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D335" s="47"/>
       <c r="E335" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Номер Строки  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам ID  </v>
       </c>
     </row>
     <row r="336" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="12"/>
       <c r="B336" s="11"/>
       <c r="C336" s="35" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D336" s="47"/>
       <c r="E336" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Активность  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Номер Строки  </v>
       </c>
     </row>
     <row r="337" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="12"/>
       <c r="B337" s="11"/>
       <c r="C337" s="35" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D337" s="47"/>
       <c r="E337" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Кредит Tип  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Активность  </v>
       </c>
     </row>
     <row r="338" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="12"/>
       <c r="B338" s="11"/>
       <c r="C338" s="35" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D338" s="47"/>
       <c r="E338" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Кредит Вид  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Кредит Tип  </v>
       </c>
     </row>
     <row r="339" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="12"/>
       <c r="B339" s="11"/>
       <c r="C339" s="35" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D339" s="47"/>
       <c r="E339" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Кредит ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Кредит Вид  </v>
       </c>
     </row>
     <row r="340" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="12"/>
       <c r="B340" s="11"/>
       <c r="C340" s="35" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D340" s="47"/>
       <c r="E340" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ответственный Tип  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Кредит ID  </v>
       </c>
     </row>
     <row r="341" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="12"/>
       <c r="B341" s="11"/>
       <c r="C341" s="35" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D341" s="47"/>
       <c r="E341" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ответственный Вид  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ответственный Tип  </v>
       </c>
     </row>
     <row r="342" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="12"/>
       <c r="B342" s="11"/>
       <c r="C342" s="35" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D342" s="47"/>
       <c r="E342" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ответственный ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ответственный Вид  </v>
       </c>
     </row>
     <row r="343" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="12"/>
       <c r="B343" s="11"/>
       <c r="C343" s="35" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D343" s="47"/>
       <c r="E343" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Дата Проверки  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ответственный ID  </v>
       </c>
     </row>
     <row r="344" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="12"/>
       <c r="B344" s="11"/>
       <c r="C344" s="35" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D344" s="47"/>
       <c r="E344" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Комментарий  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Дата Проверки  </v>
       </c>
     </row>
     <row r="345" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="12"/>
       <c r="B345" s="11"/>
       <c r="C345" s="35" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="D345" s="47"/>
       <c r="E345" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>ОтветственныеПоКредитнымДелам Телефон</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Комментарий  </v>
       </c>
     </row>
     <row r="346" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="12"/>
       <c r="B346" s="11"/>
       <c r="C346" s="35" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="D346" s="47"/>
       <c r="E346" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Филиал ID  </v>
+        <f t="shared" si="5"/>
+        <v>ОтветственныеПоКредитнымДелам Телефон</v>
       </c>
     </row>
     <row r="347" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="12"/>
       <c r="B347" s="11"/>
       <c r="C347" s="35" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D347" s="47"/>
       <c r="E347" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Филиал  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Филиал ID  </v>
       </c>
     </row>
     <row r="348" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="12"/>
       <c r="B348" s="11"/>
       <c r="C348" s="35" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D348" s="47"/>
       <c r="E348" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Вид Акта Передачи Кредитных Дел  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Филиал  </v>
       </c>
     </row>
     <row r="349" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="12"/>
       <c r="B349" s="11"/>
       <c r="C349" s="35" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D349" s="47"/>
       <c r="E349" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Отправитель ID  </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Вид Акта Передачи Кредитных Дел  </v>
       </c>
     </row>
     <row r="350" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="12"/>
       <c r="B350" s="11"/>
       <c r="C350" s="35" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D350" s="47"/>
       <c r="E350" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>ОтветственныеПоКредитнымДелам Отправитель</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Отправитель ID  </v>
       </c>
     </row>
     <row r="351" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="12"/>
       <c r="B351" s="11"/>
       <c r="C351" s="35" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D351" s="47"/>
       <c r="E351" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ссылка на Документ ID  </v>
+        <f t="shared" si="5"/>
+        <v>ОтветственныеПоКредитнымДелам Отправитель</v>
       </c>
     </row>
     <row r="352" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="12"/>
       <c r="B352" s="11"/>
       <c r="C352" s="35" t="s">
-        <v>665</v>
+        <v>707</v>
       </c>
       <c r="D352" s="47"/>
       <c r="E352" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v>ОтветственныеПоКредитнымДелам Ссылка на Документ</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Ссылка на Документ ID  </v>
       </c>
     </row>
     <row r="353" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="12"/>
       <c r="B353" s="11"/>
       <c r="C353" s="35" t="s">
-        <v>708</v>
+        <v>665</v>
       </c>
       <c r="D353" s="47"/>
       <c r="E353" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Статус Акта  </v>
+        <f t="shared" si="5"/>
+        <v>ОтветственныеПоКредитнымДелам Ссылка на Документ</v>
       </c>
     </row>
     <row r="354" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="3"/>
-      <c r="B354" s="2"/>
-      <c r="C354" s="35"/>
+      <c r="A354" s="12"/>
+      <c r="B354" s="11"/>
+      <c r="C354" s="35" t="s">
+        <v>708</v>
+      </c>
       <c r="D354" s="47"/>
       <c r="E354" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">ОтветственныеПоКредитнымДелам Статус Акта  </v>
       </c>
     </row>
     <row r="355" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7583,7 +7590,7 @@
       <c r="C355" s="35"/>
       <c r="D355" s="47"/>
       <c r="E355" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -7593,7 +7600,7 @@
       <c r="C356" s="35"/>
       <c r="D356" s="47"/>
       <c r="E356" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -7603,17 +7610,17 @@
       <c r="C357" s="35"/>
       <c r="D357" s="47"/>
       <c r="E357" s="41" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="3"/>
       <c r="B358" s="2"/>
-      <c r="C358" s="36"/>
+      <c r="C358" s="35"/>
       <c r="D358" s="47"/>
       <c r="E358" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -7623,7 +7630,7 @@
       <c r="C359" s="36"/>
       <c r="D359" s="47"/>
       <c r="E359" s="41" t="str">
-        <f t="shared" ref="E359:E367" si="6">IF(C359&gt;0,IF(D359&gt;0,D359, C359)," ")</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -7633,7 +7640,7 @@
       <c r="C360" s="36"/>
       <c r="D360" s="47"/>
       <c r="E360" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E360:E368" si="7">IF(C360&gt;0,IF(D360&gt;0,D360, C360)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -7643,7 +7650,7 @@
       <c r="C361" s="36"/>
       <c r="D361" s="47"/>
       <c r="E361" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -7653,7 +7660,7 @@
       <c r="C362" s="36"/>
       <c r="D362" s="47"/>
       <c r="E362" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -7663,2624 +7670,2634 @@
       <c r="C363" s="36"/>
       <c r="D363" s="47"/>
       <c r="E363" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A364" s="13"/>
-      <c r="B364" s="15"/>
+      <c r="A364" s="3"/>
+      <c r="B364" s="2"/>
       <c r="C364" s="36"/>
       <c r="D364" s="47"/>
       <c r="E364" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B365" s="20" t="s">
-        <v>247</v>
-      </c>
+      <c r="A365" s="13"/>
+      <c r="B365" s="15"/>
       <c r="C365" s="36"/>
       <c r="D365" s="47"/>
       <c r="E365" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" s="12"/>
-      <c r="B366" s="11" t="s">
-        <v>190</v>
+      <c r="A366" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B366" s="20" t="s">
+        <v>247</v>
       </c>
       <c r="C366" s="36"/>
       <c r="D366" s="47"/>
       <c r="E366" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" s="3"/>
-      <c r="B367" s="2" t="s">
-        <v>248</v>
+      <c r="A367" s="12"/>
+      <c r="B367" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="C367" s="36"/>
       <c r="D367" s="47"/>
       <c r="E367" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="B368" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C368" s="37"/>
+        <v>248</v>
+      </c>
+      <c r="C368" s="36"/>
       <c r="D368" s="47"/>
       <c r="E368" s="41" t="str">
-        <f t="shared" ref="E359:E422" si="7">IF(C368&gt;0,IF(D368&gt;0,D368, C368)," ")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="B369" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C369" s="16"/>
+        <v>189</v>
+      </c>
+      <c r="C369" s="37"/>
       <c r="D369" s="47"/>
       <c r="E369" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="E369:E423" si="8">IF(C369&gt;0,IF(D369&gt;0,D369, C369)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="3"/>
       <c r="B370" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C370" s="35" t="s">
-        <v>176</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C370" s="16"/>
       <c r="D370" s="47"/>
       <c r="E370" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Period</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="3"/>
       <c r="B371" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C371" s="36" t="s">
-        <v>224</v>
+        <v>187</v>
+      </c>
+      <c r="C371" s="35" t="s">
+        <v>176</v>
       </c>
       <c r="D371" s="47"/>
       <c r="E371" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Registrar_TRef</v>
+        <f t="shared" si="8"/>
+        <v>Period</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="3"/>
       <c r="B372" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C372" s="36" t="s">
-        <v>86</v>
+        <v>224</v>
       </c>
       <c r="D372" s="47"/>
       <c r="E372" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>ID</v>
+        <f t="shared" si="8"/>
+        <v>Registrar_TRef</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="3"/>
       <c r="B373" s="2" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="C373" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D373" s="47"/>
       <c r="E373" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>RowNumber</v>
+        <f t="shared" si="8"/>
+        <v>ID</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="3"/>
       <c r="B374" s="2" t="s">
-        <v>184</v>
+        <v>62</v>
       </c>
       <c r="C374" s="36" t="s">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="D374" s="47"/>
       <c r="E374" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>IsActive</v>
+        <f t="shared" si="8"/>
+        <v>RowNumber</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="3"/>
       <c r="B375" s="2" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="C375" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D375" s="47"/>
       <c r="E375" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Credit_ID</v>
+        <f t="shared" si="8"/>
+        <v>IsActive</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="3"/>
       <c r="B376" s="2" t="s">
-        <v>183</v>
+        <v>61</v>
       </c>
       <c r="C376" s="36" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="D376" s="47"/>
       <c r="E376" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Credit</v>
+        <f t="shared" si="8"/>
+        <v>Credit_ID</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="13"/>
-      <c r="B377" s="14"/>
+      <c r="A377" s="3"/>
+      <c r="B377" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="C377" s="36" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="D377" s="47"/>
       <c r="E377" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Filial_ID</v>
+        <f t="shared" si="8"/>
+        <v>Credit</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B378" s="20" t="s">
-        <v>38</v>
-      </c>
+      <c r="A378" s="13"/>
+      <c r="B378" s="14"/>
       <c r="C378" s="36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D378" s="47"/>
       <c r="E378" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Filial</v>
+        <f t="shared" si="8"/>
+        <v>Filial_ID</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="3"/>
-      <c r="B379" s="2" t="s">
-        <v>361</v>
+      <c r="A379" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B379" s="20" t="s">
+        <v>38</v>
       </c>
       <c r="C379" s="36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D379" s="47"/>
       <c r="E379" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Expert_ID</v>
+        <f t="shared" si="8"/>
+        <v>Filial</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="3"/>
       <c r="B380" s="2" t="s">
-        <v>192</v>
+        <v>361</v>
       </c>
       <c r="C380" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D380" s="47"/>
       <c r="E380" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>Expert</v>
+        <f t="shared" si="8"/>
+        <v>Expert_ID</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="3"/>
       <c r="B381" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C381" s="37"/>
+        <v>192</v>
+      </c>
+      <c r="C381" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D381" s="47"/>
       <c r="E381" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="8"/>
+        <v>Expert</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="3"/>
       <c r="B382" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C382" s="16"/>
+        <v>193</v>
+      </c>
+      <c r="C382" s="37"/>
       <c r="D382" s="47"/>
       <c r="E382" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="3"/>
       <c r="B383" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C383" s="38" t="s">
-        <v>361</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="C383" s="16"/>
       <c r="D383" s="47"/>
       <c r="E383" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам ID]</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="3"/>
       <c r="B384" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C384" s="38" t="s">
-        <v>192</v>
+        <v>361</v>
       </c>
       <c r="D384" s="47"/>
       <c r="E384" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Сотрудник]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам ID]</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="3"/>
       <c r="B385" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C385" s="38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D385" s="47"/>
       <c r="E385" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Сумма Выдано]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Сотрудник]</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="3"/>
       <c r="B386" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C386" s="38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D386" s="47"/>
       <c r="E386" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Сумма Портфель]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Сумма Выдано]</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="3"/>
       <c r="B387" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C387" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D387" s="47"/>
       <c r="E387" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Сумма Возмещено]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Сумма Портфель]</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="3"/>
       <c r="B388" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C388" s="38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D388" s="47"/>
       <c r="E388" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Сумма Оплачено]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Сумма Возмещено]</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="3"/>
       <c r="B389" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C389" s="38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D389" s="47"/>
       <c r="E389" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Количество Выдано]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Сумма Оплачено]</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="3"/>
       <c r="B390" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C390" s="38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D390" s="47"/>
       <c r="E390" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Количество Продвижений Визиты в День]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Количество Выдано]</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="3"/>
       <c r="B391" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C391" s="38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D391" s="47"/>
       <c r="E391" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Количество Продвижений Звонки в День]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Количество Продвижений Визиты в День]</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="3"/>
-      <c r="B392" s="1" t="s">
-        <v>39</v>
+      <c r="B392" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C392" s="38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D392" s="47"/>
       <c r="E392" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники PAR0]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Количество Продвижений Звонки в День]</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="3"/>
-      <c r="B393" s="2" t="s">
-        <v>204</v>
+      <c r="B393" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C393" s="38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D393" s="47"/>
       <c r="E393" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники PAR30]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники PAR0]</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="3"/>
       <c r="B394" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C394" s="38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D394" s="47"/>
       <c r="E394" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Финансовый Продукт ID]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники PAR30]</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="3"/>
       <c r="B395" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C395" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D395" s="47"/>
       <c r="E395" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам.Сотрудники Финансовый Продукт]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Финансовый Продукт ID]</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="3"/>
       <c r="B396" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C396" s="30" t="s">
-        <v>39</v>
+        <v>206</v>
+      </c>
+      <c r="C396" s="38" t="s">
+        <v>203</v>
       </c>
       <c r="D396" s="47"/>
       <c r="E396" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ATK].[dbo].[Документы.БюджетПоСотрудникам]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам.Сотрудники Финансовый Продукт]</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="3"/>
       <c r="B397" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C397" s="38" t="s">
-        <v>204</v>
+        <v>207</v>
+      </c>
+      <c r="C397" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="D397" s="47"/>
       <c r="E397" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Версия Данных]</v>
+        <f t="shared" si="8"/>
+        <v>[ATK].[dbo].[Документы.БюджетПоСотрудникам]</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="3"/>
       <c r="B398" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C398" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D398" s="47"/>
       <c r="E398" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Пометка Удаления]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Версия Данных]</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="3"/>
       <c r="B399" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C399" s="38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D399" s="47"/>
       <c r="E399" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Дата]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Пометка Удаления]</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="3"/>
       <c r="B400" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C400" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D400" s="47"/>
       <c r="E400" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Номер]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Дата]</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="3"/>
       <c r="B401" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C401" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D401" s="47"/>
       <c r="E401" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Проведен]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Номер]</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="3"/>
       <c r="B402" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C402" s="38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D402" s="47"/>
       <c r="E402" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Филиал ID]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Проведен]</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="3"/>
       <c r="B403" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C403" s="38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D403" s="47"/>
       <c r="E403" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Филиал]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Филиал ID]</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="3"/>
       <c r="B404" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C404" s="38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D404" s="47"/>
       <c r="E404" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Комментарий]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Филиал]</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="3"/>
       <c r="B405" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C405" s="38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D405" s="47"/>
       <c r="E405" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Организация]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Комментарий]</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="3"/>
       <c r="B406" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C406" s="38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D406" s="47"/>
       <c r="E406" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Сумма Выдано Итого]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Организация]</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="3"/>
       <c r="B407" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C407" s="38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D407" s="47"/>
       <c r="E407" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Сумма Портфель Итого]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Сумма Выдано Итого]</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="3"/>
       <c r="B408" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C408" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D408" s="47"/>
       <c r="E408" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Сумма Оплачено Итого]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Сумма Портфель Итого]</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="3"/>
       <c r="B409" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C409" s="38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D409" s="47"/>
       <c r="E409" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам Сумма Возмещено Итого]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Сумма Оплачено Итого]</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="13"/>
-      <c r="B410" s="14"/>
+      <c r="A410" s="3"/>
+      <c r="B410" s="2" t="s">
+        <v>191</v>
+      </c>
       <c r="C410" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D410" s="47"/>
       <c r="E410" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам PAR0]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам Сумма Возмещено Итого]</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B411" s="20" t="s">
-        <v>42</v>
-      </c>
+      <c r="A411" s="13"/>
+      <c r="B411" s="14"/>
       <c r="C411" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D411" s="47"/>
       <c r="E411" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам PAR30]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам PAR0]</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="12"/>
-      <c r="B412" s="11" t="s">
-        <v>220</v>
+      <c r="A412" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B412" s="20" t="s">
+        <v>42</v>
       </c>
       <c r="C412" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D412" s="47"/>
       <c r="E412" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам PAR0 Нон Бизнес]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам PAR30]</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A413" s="3"/>
-      <c r="B413" s="2" t="s">
-        <v>260</v>
+      <c r="A413" s="12"/>
+      <c r="B413" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="C413" s="38" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D413" s="47"/>
       <c r="E413" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[БюджетПоСотрудникам PAR30 Нон Бизнес]</v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам PAR0 Нон Бизнес]</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="3"/>
       <c r="B414" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C414" s="33"/>
+        <v>260</v>
+      </c>
+      <c r="C414" s="38" t="s">
+        <v>191</v>
+      </c>
       <c r="D414" s="47"/>
       <c r="E414" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="8"/>
+        <v>[БюджетПоСотрудникам PAR30 Нон Бизнес]</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="3"/>
       <c r="B415" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C415" s="16"/>
+        <v>261</v>
+      </c>
+      <c r="C415" s="33"/>
       <c r="D415" s="47"/>
       <c r="E415" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="3"/>
       <c r="B416" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C416" s="26" t="s">
-        <v>220</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C416" s="16"/>
       <c r="D416" s="47"/>
       <c r="E416" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ЗаявкаНаКредит ID]</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="3"/>
       <c r="B417" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C417" s="27" t="s">
-        <v>260</v>
+        <v>263</v>
+      </c>
+      <c r="C417" s="26" t="s">
+        <v>220</v>
       </c>
       <c r="D417" s="47"/>
       <c r="E417" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ЗаявкаНаКредит Дата]</v>
+        <f t="shared" si="8"/>
+        <v>[ЗаявкаНаКредит ID]</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="3"/>
       <c r="B418" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C418" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D418" s="47"/>
       <c r="E418" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ЗаявкаНаКредит Номер]</v>
+        <f t="shared" si="8"/>
+        <v>[ЗаявкаНаКредит Дата]</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="3"/>
       <c r="B419" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C419" s="27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D419" s="47"/>
       <c r="E419" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ЗаявкаНаКредит Проведен]</v>
+        <f t="shared" si="8"/>
+        <v>[ЗаявкаНаКредит Номер]</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="3"/>
       <c r="B420" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C420" s="27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D420" s="47"/>
       <c r="E420" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ЗаявкаНаКредит Автор]</v>
+        <f t="shared" si="8"/>
+        <v>[ЗаявкаНаКредит Проведен]</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="3"/>
       <c r="B421" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C421" s="27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D421" s="47"/>
       <c r="E421" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ЗаявкаНаКредит Агро]</v>
+        <f t="shared" si="8"/>
+        <v>[ЗаявкаНаКредит Автор]</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="3"/>
       <c r="B422" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C422" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D422" s="47"/>
       <c r="E422" s="41" t="str">
-        <f t="shared" si="7"/>
-        <v>[ЗаявкаНаКредит Альтернативный Сектор Экономики]</v>
+        <f t="shared" si="8"/>
+        <v>[ЗаявкаНаКредит Агро]</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="3"/>
       <c r="B423" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C423" s="27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D423" s="47"/>
       <c r="E423" s="41" t="str">
-        <f t="shared" ref="E423:E486" si="8">IF(C423&gt;0,IF(D423&gt;0,D423, C423)," ")</f>
-        <v>[ЗаявкаНаКредит Бизнес Организация]</v>
+        <f t="shared" si="8"/>
+        <v>[ЗаявкаНаКредит Альтернативный Сектор Экономики]</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="3"/>
       <c r="B424" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C424" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D424" s="47"/>
       <c r="E424" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Бизнес Сектор Экономики]</v>
+        <f t="shared" ref="E424:E487" si="9">IF(C424&gt;0,IF(D424&gt;0,D424, C424)," ")</f>
+        <v>[ЗаявкаНаКредит Бизнес Организация]</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="3"/>
       <c r="B425" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C425" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D425" s="47"/>
       <c r="E425" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Валюта]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Бизнес Сектор Экономики]</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="3"/>
       <c r="B426" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C426" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D426" s="47"/>
       <c r="E426" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Заявки]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Валюта]</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="3"/>
       <c r="B427" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C427" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D427" s="47"/>
       <c r="E427" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Кредитной Истории]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Вид Заявки]</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="3"/>
       <c r="B428" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C428" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D428" s="47"/>
       <c r="E428" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Обеспечения]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Вид Кредитной Истории]</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="3"/>
       <c r="B429" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C429" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D429" s="47"/>
       <c r="E429" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Отказа]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Вид Обеспечения]</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="3"/>
       <c r="B430" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C430" s="27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D430" s="47"/>
       <c r="E430" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Перечисления]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Вид Отказа]</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="3"/>
       <c r="B431" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C431" s="27" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D431" s="47"/>
       <c r="E431" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Реструктуризации Долга]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Вид Перечисления]</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="3"/>
       <c r="B432" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C432" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D432" s="47"/>
       <c r="E432" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Энергетической Эффективности]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Вид Реструктуризации Долга]</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="3"/>
       <c r="B433" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C433" s="27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D433" s="47"/>
       <c r="E433" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Дилер]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Вид Энергетической Эффективности]</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="3"/>
       <c r="B434" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C434" s="27" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D434" s="47"/>
       <c r="E434" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Заявка Клиента Интернет ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Дилер]</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="3"/>
       <c r="B435" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C435" s="27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D435" s="47"/>
       <c r="E435" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Заявка Клиента Интернет]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Заявка Клиента Интернет ID]</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="3"/>
       <c r="B436" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C436" s="27" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D436" s="47"/>
       <c r="E436" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Идентификатор]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Заявка Клиента Интернет]</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="3"/>
       <c r="B437" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C437" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D437" s="47"/>
       <c r="E437" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Имя Клиента]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Идентификатор]</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="3"/>
       <c r="B438" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C438" s="27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D438" s="47"/>
       <c r="E438" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Категория Цель Кредита]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Имя Клиента]</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="3"/>
       <c r="B439" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C439" s="27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D439" s="47"/>
       <c r="E439" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Категория Энергетической Эффективности]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Категория Цель Кредита]</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="3"/>
       <c r="B440" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C440" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D440" s="47"/>
       <c r="E440" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Клиент ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Категория Энергетической Эффективности]</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="3"/>
       <c r="B441" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C441" s="27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D441" s="47"/>
       <c r="E441" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Клиент]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Клиент ID]</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="3"/>
       <c r="B442" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C442" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D442" s="47"/>
       <c r="E442" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Количество Членов Семьи Итого]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Клиент]</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="3"/>
       <c r="B443" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C443" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D443" s="47"/>
       <c r="E443" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Количество Членов Семьи на Иждевении]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Количество Членов Семьи Итого]</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="3"/>
       <c r="B444" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C444" s="27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D444" s="47"/>
       <c r="E444" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Комитет ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Количество Членов Семьи на Иждевении]</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="3"/>
       <c r="B445" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C445" s="27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D445" s="47"/>
       <c r="E445" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Комитет]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Комитет ID]</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="3"/>
       <c r="B446" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C446" s="27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D446" s="47"/>
       <c r="E446" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Кредит ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Комитет]</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="3"/>
       <c r="B447" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C447" s="27" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D447" s="47"/>
       <c r="E447" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Кредитный Продукт ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Кредит ID]</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="3"/>
       <c r="B448" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C448" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D448" s="47"/>
       <c r="E448" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Кредитный Эксперт ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Кредитный Продукт ID]</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="3"/>
       <c r="B449" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C449" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D449" s="47"/>
       <c r="E449" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Кредитный Эксперт]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Кредитный Эксперт ID]</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="3"/>
       <c r="B450" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C450" s="27" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D450" s="47"/>
       <c r="E450" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Причина Отказа]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Кредитный Эксперт]</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="3"/>
       <c r="B451" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C451" s="27" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D451" s="47"/>
       <c r="E451" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Протокол Комитета ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Причина Отказа]</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="3"/>
       <c r="B452" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C452" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D452" s="47"/>
       <c r="E452" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Протокол Комитета]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Протокол Комитета ID]</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="3"/>
       <c r="B453" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C453" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D453" s="47"/>
       <c r="E453" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Решение Комитета]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Протокол Комитета]</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="3"/>
       <c r="B454" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C454" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D454" s="47"/>
       <c r="E454" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Сектор Экономики]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Решение Комитета]</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="3"/>
       <c r="B455" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C455" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D455" s="47"/>
       <c r="E455" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Скоринг Финальная Оценка]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Сектор Экономики]</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="3"/>
       <c r="B456" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C456" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D456" s="47"/>
       <c r="E456" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Состояние Заявки]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Скоринг Финальная Оценка]</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="3"/>
       <c r="B457" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C457" s="27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D457" s="47"/>
       <c r="E457" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Срок Кредита]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Состояние Заявки]</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="3"/>
       <c r="B458" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C458" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D458" s="47"/>
       <c r="E458" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Стаж Работы Общий]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Срок Кредита]</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="3"/>
       <c r="B459" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C459" s="27" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D459" s="47"/>
       <c r="E459" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Сумма Кредита]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Стаж Работы Общий]</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="3"/>
       <c r="B460" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C460" s="27" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D460" s="47"/>
       <c r="E460" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Уровень Финансового Риска]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Сумма Кредита]</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="3"/>
       <c r="B461" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C461" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D461" s="47"/>
       <c r="E461" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Филиал ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Уровень Финансового Риска]</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="3"/>
       <c r="B462" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C462" s="27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D462" s="47"/>
       <c r="E462" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Филиал Партнера]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Филиал ID]</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A463" s="13"/>
-      <c r="B463" s="15"/>
+      <c r="A463" s="3"/>
+      <c r="B463" s="2" t="s">
+        <v>309</v>
+      </c>
       <c r="C463" s="27" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D463" s="47"/>
       <c r="E463" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Финансовый Продукт ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Филиал Партнера]</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A464" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B464" s="20" t="s">
-        <v>336</v>
-      </c>
+      <c r="A464" s="13"/>
+      <c r="B464" s="15"/>
       <c r="C464" s="27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D464" s="47"/>
       <c r="E464" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Финансовый Продукт]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Финансовый Продукт ID]</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A465" s="12"/>
-      <c r="B465" s="11" t="s">
-        <v>310</v>
+      <c r="A465" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B465" s="20" t="s">
+        <v>336</v>
       </c>
       <c r="C465" s="27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D465" s="47"/>
       <c r="E465" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Цель Кредита]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Финансовый Продукт]</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A466" s="3"/>
-      <c r="B466" s="2" t="s">
-        <v>311</v>
+      <c r="A466" s="12"/>
+      <c r="B466" s="11" t="s">
+        <v>310</v>
       </c>
       <c r="C466" s="27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D466" s="47"/>
       <c r="E466" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Это Зеленый Кредит]</v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Цель Кредита]</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="3"/>
       <c r="B467" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C467" s="28"/>
+        <v>311</v>
+      </c>
+      <c r="C467" s="27" t="s">
+        <v>309</v>
+      </c>
       <c r="D467" s="47"/>
       <c r="E467" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v>[ЗаявкаНаКредит Это Зеленый Кредит]</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="3"/>
       <c r="B468" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C468" s="16"/>
+        <v>312</v>
+      </c>
+      <c r="C468" s="28"/>
       <c r="D468" s="47"/>
       <c r="E468" s="41" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="3"/>
       <c r="B469" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C469" s="26" t="s">
-        <v>310</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="C469" s="16"/>
       <c r="D469" s="47"/>
       <c r="E469" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка ID]</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="3"/>
       <c r="B470" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C470" s="27" t="s">
-        <v>311</v>
+        <v>314</v>
+      </c>
+      <c r="C470" s="26" t="s">
+        <v>310</v>
       </c>
       <c r="D470" s="47"/>
       <c r="E470" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Дата]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка ID]</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="3"/>
       <c r="B471" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C471" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D471" s="47"/>
       <c r="E471" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Номер]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Дата]</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="3"/>
       <c r="B472" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C472" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D472" s="47"/>
       <c r="E472" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Проведен]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Номер]</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="3"/>
       <c r="B473" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C473" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D473" s="47"/>
       <c r="E473" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Автор ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Проведен]</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="3"/>
       <c r="B474" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C474" s="27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D474" s="47"/>
       <c r="E474" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Автор]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Автор ID]</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="3"/>
       <c r="B475" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C475" s="27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D475" s="47"/>
       <c r="E475" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Вид Доходов Онлайн]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Автор]</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="3"/>
       <c r="B476" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C476" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D476" s="47"/>
       <c r="E476" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Вид Интернет Заявки]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Вид Доходов Онлайн]</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="3"/>
       <c r="B477" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C477" s="27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D477" s="47"/>
       <c r="E477" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Возраст]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Вид Интернет Заявки]</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="3"/>
       <c r="B478" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C478" s="27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D478" s="47"/>
       <c r="E478" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Дата Отправки на Рассмотрение]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Возраст]</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="3"/>
       <c r="B479" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C479" s="27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D479" s="47"/>
       <c r="E479" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Заявка на Кредит ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Дата Отправки на Рассмотрение]</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="3"/>
       <c r="B480" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C480" s="27" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D480" s="47"/>
       <c r="E480" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Заявка на Кредит]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Заявка на Кредит ID]</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="3"/>
       <c r="B481" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C481" s="27" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D481" s="47"/>
       <c r="E481" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Идентификатор]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Заявка на Кредит]</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="3"/>
       <c r="B482" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C482" s="27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D482" s="47"/>
       <c r="E482" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Компания Фиск Код]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Идентификатор]</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="3"/>
       <c r="B483" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C483" s="27" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D483" s="47"/>
       <c r="E483" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Консультант Партнера]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Компания Фиск Код]</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="3"/>
       <c r="B484" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C484" s="27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D484" s="47"/>
       <c r="E484" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Продукт WEB ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Консультант Партнера]</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="3"/>
       <c r="B485" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C485" s="27" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D485" s="47"/>
       <c r="E485" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Продукт WEB]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Продукт WEB ID]</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="3"/>
       <c r="B486" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C486" s="27" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D486" s="47"/>
       <c r="E486" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Эксперт ID]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Продукт WEB]</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="3"/>
       <c r="B487" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C487" s="27" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D487" s="47"/>
       <c r="E487" s="41" t="str">
-        <f t="shared" ref="E487:E550" si="9">IF(C487&gt;0,IF(D487&gt;0,D487, C487)," ")</f>
-        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Эксперт]</v>
+        <f t="shared" si="9"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Эксперт ID]</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A488" s="7"/>
+      <c r="A488" s="3"/>
       <c r="B488" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C488" s="27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D488" s="47"/>
       <c r="E488" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Номер Телефона Мобильный]</v>
+        <f t="shared" ref="E488:E551" si="10">IF(C488&gt;0,IF(D488&gt;0,D488, C488)," ")</f>
+        <v>[ОбъединеннаяИнтернетЗаявка Кредитный Эксперт]</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A489" s="3"/>
+      <c r="A489" s="7"/>
       <c r="B489" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C489" s="27" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D489" s="47"/>
       <c r="E489" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Отправлена на Рассмотрение]</v>
+        <f t="shared" si="10"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Номер Телефона Мобильный]</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="3"/>
       <c r="B490" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C490" s="27" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D490" s="47"/>
       <c r="E490" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Пол]</v>
+        <f t="shared" si="10"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Отправлена на Рассмотрение]</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="3"/>
-      <c r="B491" s="1" t="s">
-        <v>243</v>
+      <c r="B491" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="C491" s="27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D491" s="47"/>
       <c r="E491" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Состояние Заявки]</v>
+        <f t="shared" si="10"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Пол]</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="3"/>
-      <c r="B492" s="2" t="s">
-        <v>220</v>
+      <c r="B492" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C492" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D492" s="47"/>
       <c r="E492" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Срок Кредита]</v>
+        <f t="shared" si="10"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Состояние Заявки]</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A493" s="7"/>
+      <c r="A493" s="3"/>
       <c r="B493" s="2" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="C493" s="27" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D493" s="47"/>
       <c r="E493" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Сумма Кредита]</v>
+        <f t="shared" si="10"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Срок Кредита]</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A494" s="3"/>
+      <c r="A494" s="7"/>
       <c r="B494" s="2" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="C494" s="27" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D494" s="47"/>
       <c r="E494" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ОбъединеннаяИнтернетЗаявка Филиал ID]</v>
+        <f t="shared" si="10"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Сумма Кредита]</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="3"/>
       <c r="B495" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C495" s="30"/>
+        <v>299</v>
+      </c>
+      <c r="C495" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="D495" s="47"/>
       <c r="E495" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="10"/>
+        <v>[ОбъединеннаяИнтернетЗаявка Филиал ID]</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="3"/>
       <c r="B496" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C496" s="27" t="s">
-        <v>220</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C496" s="30"/>
       <c r="D496" s="47"/>
       <c r="E496" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит ID]</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A497" s="7"/>
+      <c r="A497" s="3"/>
       <c r="B497" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C497" s="27" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="D497" s="47"/>
       <c r="E497" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Дата]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит ID]</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A498" s="3"/>
+      <c r="A498" s="7"/>
       <c r="B498" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C498" s="27" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="D498" s="47"/>
       <c r="E498" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Состояние Заявки]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Дата]</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="3"/>
       <c r="B499" s="2" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="C499" s="27" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="D499" s="47"/>
       <c r="E499" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Проведен]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Состояние Заявки]</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="3"/>
       <c r="B500" s="2" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="C500" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D500" s="47"/>
       <c r="E500" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Бизнес Сектор Экономики]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Проведен]</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A501" s="7"/>
+      <c r="A501" s="3"/>
       <c r="B501" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C501" s="27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D501" s="47"/>
       <c r="E501" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Вид Заявки]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Бизнес Сектор Экономики]</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A502" s="3"/>
+      <c r="A502" s="7"/>
       <c r="B502" s="2" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="C502" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D502" s="47"/>
       <c r="E502" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Вид Кредитной Истории]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Вид Заявки]</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="3"/>
       <c r="B503" s="2" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="C503" s="27" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="D503" s="47"/>
       <c r="E503" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Кредит ID]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Вид Кредитной Истории]</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A504" s="13"/>
-      <c r="B504" s="15" t="s">
-        <v>362</v>
+      <c r="A504" s="3"/>
+      <c r="B504" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="C504" s="27" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="D504" s="47"/>
       <c r="E504" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Цель Кредита]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Кредит ID]</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="13"/>
-      <c r="B505" s="15"/>
+      <c r="B505" s="15" t="s">
+        <v>362</v>
+      </c>
       <c r="C505" s="27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D505" s="47"/>
       <c r="E505" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Это Зеленый Кредит]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Цель Кредита]</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A506" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B506" s="17"/>
+      <c r="A506" s="13"/>
+      <c r="B506" s="15"/>
       <c r="C506" s="27" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="D506" s="47"/>
       <c r="E506" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Клиент ID]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Это Зеленый Кредит]</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A507" s="12"/>
-      <c r="B507" s="5" t="s">
-        <v>225</v>
-      </c>
+      <c r="A507" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B507" s="17"/>
       <c r="C507" s="27" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D507" s="47"/>
       <c r="E507" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>[ЗаявкаНаКредит Сумма Кредита]</v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Клиент ID]</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A508" s="3"/>
-      <c r="B508" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C508" s="28" t="s">
-        <v>362</v>
+      <c r="A508" s="12"/>
+      <c r="B508" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C508" s="27" t="s">
+        <v>302</v>
       </c>
       <c r="D508" s="47"/>
       <c r="E508" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">[ЗаявкаНаКредит Причина Отказа] </v>
+        <f t="shared" si="10"/>
+        <v>[ЗаявкаНаКредит Сумма Кредита]</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="3"/>
       <c r="B509" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C509" s="28"/>
+        <v>78</v>
+      </c>
+      <c r="C509" s="28" t="s">
+        <v>362</v>
+      </c>
       <c r="D509" s="47"/>
       <c r="E509" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">[ЗаявкаНаКредит Причина Отказа] </v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="3"/>
       <c r="B510" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C510" s="21"/>
+        <v>223</v>
+      </c>
+      <c r="C510" s="28"/>
       <c r="D510" s="47"/>
       <c r="E510" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="3"/>
       <c r="B511" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C511" s="39"/>
+        <v>79</v>
+      </c>
+      <c r="C511" s="21"/>
       <c r="D511" s="47"/>
       <c r="E511" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="3"/>
       <c r="B512" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C512" s="27" t="s">
-        <v>176</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="C512" s="39"/>
       <c r="D512" s="47"/>
       <c r="E512" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>Period</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="3"/>
       <c r="B513" s="2" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C513" s="27" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D513" s="47"/>
       <c r="E513" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>Registrar_Tref</v>
+        <f t="shared" si="10"/>
+        <v>Period</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="3"/>
       <c r="B514" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C514" s="27" t="s">
-        <v>86</v>
+        <v>222</v>
       </c>
       <c r="D514" s="47"/>
       <c r="E514" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>ID</v>
+        <f t="shared" si="10"/>
+        <v>Registrar_Tref</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="3"/>
       <c r="B515" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C515" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D515" s="47"/>
       <c r="E515" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>RowNumber</v>
+        <f t="shared" si="10"/>
+        <v>ID</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="3"/>
       <c r="B516" s="2" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C516" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D516" s="47"/>
       <c r="E516" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>Active</v>
+        <f t="shared" si="10"/>
+        <v>RowNumber</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="3"/>
       <c r="B517" s="2" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C517" s="27" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D517" s="47"/>
       <c r="E517" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CreditID</v>
+        <f t="shared" si="10"/>
+        <v>Active</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="3"/>
       <c r="B518" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C518" s="27" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="D518" s="47"/>
       <c r="E518" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>Credit</v>
+        <f t="shared" si="10"/>
+        <v>CreditID</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A519" s="13"/>
-      <c r="B519" s="14"/>
+      <c r="A519" s="3"/>
+      <c r="B519" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="C519" s="27" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D519" s="47"/>
       <c r="E519" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>BranchID</v>
+        <f t="shared" si="10"/>
+        <v>Credit</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A520" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B520" s="17"/>
+      <c r="A520" s="13"/>
+      <c r="B520" s="14"/>
       <c r="C520" s="27" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D520" s="47"/>
       <c r="E520" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>Branch</v>
+        <f t="shared" si="10"/>
+        <v>BranchID</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A521" s="12"/>
-      <c r="B521" s="5" t="s">
-        <v>353</v>
-      </c>
+      <c r="A521" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B521" s="17"/>
       <c r="C521" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D521" s="47"/>
       <c r="E521" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CreditExpertID</v>
+        <f t="shared" si="10"/>
+        <v>Branch</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A522" s="3"/>
-      <c r="B522" s="2" t="s">
-        <v>73</v>
+      <c r="A522" s="12"/>
+      <c r="B522" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="C522" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D522" s="47"/>
       <c r="E522" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CreditExpert</v>
+        <f t="shared" si="10"/>
+        <v>CreditExpertID</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="3"/>
       <c r="B523" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C523" s="28"/>
+        <v>73</v>
+      </c>
+      <c r="C523" s="27" t="s">
+        <v>92</v>
+      </c>
       <c r="D523" s="47"/>
       <c r="E523" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="10"/>
+        <v>CreditExpert</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="3"/>
       <c r="B524" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C524" s="21"/>
+        <v>74</v>
+      </c>
+      <c r="C524" s="28"/>
       <c r="D524" s="47"/>
       <c r="E524" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="3"/>
       <c r="B525" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C525" s="39"/>
+        <v>75</v>
+      </c>
+      <c r="C525" s="21"/>
       <c r="D525" s="47"/>
       <c r="E525" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="3"/>
       <c r="B526" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C526" s="27" t="s">
-        <v>50</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C526" s="39"/>
       <c r="D526" s="47"/>
       <c r="E526" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CreditID</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="3"/>
-      <c r="B527" s="1" t="s">
-        <v>354</v>
+      <c r="B527" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C527" s="27" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D527" s="47"/>
       <c r="E527" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>DisbursementDate</v>
+        <f t="shared" si="10"/>
+        <v>CreditID</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="3"/>
-      <c r="B528" s="2" t="s">
-        <v>46</v>
+      <c r="B528" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="C528" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D528" s="47"/>
       <c r="E528" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CurrencyID</v>
+        <f t="shared" si="10"/>
+        <v>DisbursementDate</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A529" s="7"/>
-      <c r="B529" s="1" t="s">
-        <v>247</v>
+      <c r="A529" s="3"/>
+      <c r="B529" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="C529" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D529" s="47"/>
       <c r="E529" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CreditAmount</v>
+        <f t="shared" si="10"/>
+        <v>CurrencyID</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A530" s="3"/>
-      <c r="B530" s="2" t="s">
-        <v>62</v>
+      <c r="A530" s="7"/>
+      <c r="B530" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="C530" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D530" s="47"/>
       <c r="E530" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CreditCurrency</v>
+        <f t="shared" si="10"/>
+        <v>CreditAmount</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="3"/>
       <c r="B531" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C531" s="27"/>
+        <v>62</v>
+      </c>
+      <c r="C531" s="27" t="s">
+        <v>68</v>
+      </c>
       <c r="D531" s="47"/>
       <c r="E531" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="10"/>
+        <v>CreditCurrency</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="3"/>
-      <c r="B532" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C532" s="27" t="s">
-        <v>8</v>
-      </c>
+      <c r="B532" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C532" s="27"/>
       <c r="D532" s="47"/>
       <c r="E532" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>ClientID</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="3"/>
-      <c r="B533" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C533" s="27"/>
+      <c r="B533" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C533" s="27" t="s">
+        <v>8</v>
+      </c>
       <c r="D533" s="47"/>
       <c r="E533" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="10"/>
+        <v>ClientID</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="3"/>
       <c r="B534" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C534" s="27" t="s">
-        <v>69</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C534" s="27"/>
       <c r="D534" s="47"/>
       <c r="E534" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>FirstFilialID</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="3"/>
       <c r="B535" s="2" t="s">
-        <v>355</v>
+        <v>72</v>
       </c>
       <c r="C535" s="27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D535" s="47"/>
       <c r="E535" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>FirstExpertID</v>
+        <f t="shared" si="10"/>
+        <v>FirstFilialID</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="3"/>
-      <c r="B536" s="1" t="s">
-        <v>358</v>
+      <c r="B536" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="C536" s="27" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D536" s="47"/>
       <c r="E536" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>IRR</v>
+        <f t="shared" si="10"/>
+        <v>FirstExpertID</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="3"/>
-      <c r="B537" s="2" t="s">
-        <v>359</v>
+      <c r="B537" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="C537" s="27" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="D537" s="47"/>
       <c r="E537" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>IRR_Client</v>
+        <f t="shared" si="10"/>
+        <v>IRR</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="3"/>
       <c r="B538" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C538" s="27"/>
+        <v>359</v>
+      </c>
+      <c r="C538" s="27" t="s">
+        <v>71</v>
+      </c>
       <c r="D538" s="47"/>
       <c r="E538" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="10"/>
+        <v>IRR_Client</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="3"/>
       <c r="B539" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C539" s="27"/>
       <c r="D539" s="47"/>
       <c r="E539" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A540" s="13"/>
-      <c r="B540" s="14"/>
+      <c r="A540" s="3"/>
+      <c r="B540" s="2" t="s">
+        <v>357</v>
+      </c>
       <c r="C540" s="27"/>
       <c r="D540" s="47"/>
       <c r="E540" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A541" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B541" s="17"/>
+      <c r="A541" s="13"/>
+      <c r="B541" s="14"/>
       <c r="C541" s="27"/>
       <c r="D541" s="47"/>
       <c r="E541" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A542" s="12"/>
-      <c r="B542" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="A542" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B542" s="17"/>
       <c r="C542" s="27"/>
       <c r="D542" s="47"/>
       <c r="E542" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A543" s="3"/>
-      <c r="B543" s="2" t="s">
-        <v>58</v>
+      <c r="A543" s="12"/>
+      <c r="B543" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C543" s="27"/>
       <c r="D543" s="47"/>
       <c r="E543" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="3"/>
       <c r="B544" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C544" s="27"/>
       <c r="D544" s="47"/>
       <c r="E544" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="3"/>
       <c r="B545" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C545" s="16"/>
+        <v>59</v>
+      </c>
       <c r="D545" s="47"/>
       <c r="E545" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="3"/>
-      <c r="B546" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C546" s="32"/>
+      <c r="B546" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C546" s="16"/>
       <c r="D546" s="47"/>
       <c r="E546" s="41" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="3"/>
-      <c r="B547" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C547" s="27" t="s">
-        <v>49</v>
-      </c>
+      <c r="B547" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C547" s="32"/>
       <c r="D547" s="47"/>
       <c r="E547" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>SoldDate</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="3"/>
       <c r="B548" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C548" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D548" s="47"/>
       <c r="E548" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>CreditID</v>
+        <f t="shared" si="10"/>
+        <v>SoldDate</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="3"/>
-      <c r="B549" s="1" t="s">
-        <v>35</v>
+      <c r="B549" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C549" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D549" s="47"/>
       <c r="E549" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v>SoldAmount</v>
+        <f t="shared" si="10"/>
+        <v>CreditID</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="3"/>
-      <c r="B550" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C550" s="27"/>
+      <c r="B550" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C550" s="27" t="s">
+        <v>51</v>
+      </c>
       <c r="D550" s="47"/>
       <c r="E550" s="41" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="10"/>
+        <v>SoldAmount</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="3"/>
       <c r="B551" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C551" s="27" t="s">
-        <v>52</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="C551" s="27"/>
       <c r="D551" s="47"/>
       <c r="E551" s="41" t="str">
-        <f t="shared" ref="E551:E556" si="10">IF(C551&gt;0,IF(D551&gt;0,D551, C551)," ")</f>
-        <v>IRR</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A552" s="13"/>
-      <c r="B552" s="19"/>
+      <c r="A552" s="3"/>
+      <c r="B552" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="C552" s="27" t="s">
         <v>52</v>
       </c>
       <c r="D552" s="47"/>
       <c r="E552" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="E552:E557" si="11">IF(C552&gt;0,IF(D552&gt;0,D552, C552)," ")</f>
         <v>IRR</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C553" s="27"/>
+      <c r="A553" s="13"/>
+      <c r="B553" s="19"/>
+      <c r="C553" s="27" t="s">
+        <v>52</v>
+      </c>
       <c r="D553" s="47"/>
       <c r="E553" s="41" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="11"/>
+        <v>IRR</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C554" s="27" t="s">
-        <v>53</v>
-      </c>
+      <c r="C554" s="27"/>
       <c r="D554" s="47"/>
       <c r="E554" s="41" t="str">
-        <f t="shared" si="10"/>
-        <v>ExpertID</v>
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C555" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D555" s="47"/>
       <c r="E555" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
+        <v>ExpertID</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C556" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D556" s="47"/>
+      <c r="E556" s="41" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve">BranchID </v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C556" s="28"/>
-      <c r="D556" s="48"/>
-      <c r="E556" s="41" t="str">
-        <f t="shared" si="10"/>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C557" s="28"/>
+      <c r="D557" s="48"/>
+      <c r="E557" s="41" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="E3:E556">
+  <conditionalFormatting sqref="E3:E557">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$D3&gt;0</formula>
     </cfRule>

--- a/data/glossary/ATK_mis.Gold_tables_v1.xlsx
+++ b/data/glossary/ATK_mis.Gold_tables_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80F654F-B89C-4AEB-8CF4-FDAD67FB2052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8FF929-A07F-4381-A6AB-93D05637B451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27750" yWindow="600" windowWidth="26490" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26550" yWindow="375" windowWidth="26490" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="825">
   <si>
     <t>BranchCode</t>
   </si>
@@ -150,9 +150,6 @@
     <t>[ATK].[dbo].[РегистрыСведений.КредитыВТеневыхФилиалах]</t>
   </si>
   <si>
-    <t>mis.[2tbl_Gold_Fact_Disbursement]</t>
-  </si>
-  <si>
     <t>[Кредиты Владелец]</t>
   </si>
   <si>
@@ -204,9 +201,6 @@
     <t>[ОтветственныеПоКредитамВыданным Филиал ID]</t>
   </si>
   <si>
-    <t>mis.[2tbl_Gold_Fact_Sold]</t>
-  </si>
-  <si>
     <t>Current values</t>
   </si>
   <si>
@@ -234,18 +228,12 @@
     <t>[УстановкаДанныхКредита Внутренняя Норма Доходности Клиент Годовая]</t>
   </si>
   <si>
-    <t>[ДанныеКредитовВыданных Кредит ID]</t>
-  </si>
-  <si>
     <t>[ДанныеКредитовВыданных Дата Выдачи]</t>
   </si>
   <si>
     <t>[ДанныеКредитовВыданных Валюта Кредита ID]</t>
   </si>
   <si>
-    <t>[ДанныеКредитовВыданных Сумма Кредита]</t>
-  </si>
-  <si>
     <t>[ДанныеКредитовВыданных Валюта Кредита]</t>
   </si>
   <si>
@@ -285,12 +273,6 @@
     <t>Branch</t>
   </si>
   <si>
-    <t>CreditExpertID</t>
-  </si>
-  <si>
-    <t>CreditExpert</t>
-  </si>
-  <si>
     <t>ProductID</t>
   </si>
   <si>
@@ -639,15 +621,6 @@
     <t>DealerID</t>
   </si>
   <si>
-    <t>Registrar_Tref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[КредитыВТеневыхФилиалах Регистратор _TRef] </t>
-  </si>
-  <si>
-    <t>[ATK].[mis].[Silver_РегистрыСведений.КредитыВТеневыхФилиалах]</t>
-  </si>
-  <si>
     <t>[СведенияОПользователяхМобильногоПриложения Клиент]</t>
   </si>
   <si>
@@ -711,9 +684,6 @@
     <t>LatestOutstandingAmount</t>
   </si>
   <si>
-    <t>[ATK].[mis].[Silver_РегистрыСведений.ОтветственныеПоКредитамВыданным]</t>
-  </si>
-  <si>
     <t>[Дилеры Представитель Организации]</t>
   </si>
   <si>
@@ -897,12 +867,6 @@
     <t>SigningSource</t>
   </si>
   <si>
-    <t>[ATK].[mis].[Silver_РегистрыСведений.ДанныеКредитовВыданных]</t>
-  </si>
-  <si>
-    <t>[ATK].[mis].[Silver_Справочники.Кредиты</t>
-  </si>
-  <si>
     <t>[ATK].[mis].[Silver_РегистрыСведений.Валюта]</t>
   </si>
   <si>
@@ -921,9 +885,6 @@
     <t>[Валюта Период]</t>
   </si>
   <si>
-    <t xml:space="preserve">[ЗаявкаНаКредит Причина Отказа] </t>
-  </si>
-  <si>
     <t>FROM Tables/columns</t>
   </si>
   <si>
@@ -2481,64 +2442,76 @@
     <t>[РегистрыСведений.КредитыВТеневыхФилиалах]</t>
   </si>
   <si>
-    <t xml:space="preserve">    Period DATETIME NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ID VARCHAR(32) NOT NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RowNumber INT NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Active VARCHAR(36) NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    CreditID VARCHAR(32) NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Credit NVARCHAR(100) NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    BranchID VARCHAR(32) NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Branch NVARCHAR(100) NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    CreditEmployeeID VARCHAR(32) NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    CreditEmployee NVARCHAR(100) NULL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Период]                 AS Period,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах ID]                     AS ID,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Номер Строки]           AS RowNumber,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Активность]             AS Active,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Кредит ID]              AS CreditID,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Кредит]                 AS Credit,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Филиал ID]              AS BranchID,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Филиал]                 AS Branch,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Кредитный Эксперт ID]   AS CreditEmployeeID,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          rs.[КредитыВТеневыхФилиалах Кредитный Эксперт]      AS CreditEmployee</t>
+    <t>[КредитыВТеневыхФилиалах Период]</t>
+  </si>
+  <si>
+    <t>CreditEmployeeID</t>
+  </si>
+  <si>
+    <t>CreditEmployee</t>
+  </si>
+  <si>
+    <t>mis.Gold_Fact_Disbursement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ДанныеКредитовВыданных Кредит ID] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Кредиты Владелец] </t>
+  </si>
+  <si>
+    <t>[РегистрыСведений.ДанныеКредитовВыданных]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CreditCurrency </t>
+  </si>
+  <si>
+    <t>[Документы.УстановкаДанныхКредита]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FirstFilialID/LastFilialID </t>
+  </si>
+  <si>
+    <t xml:space="preserve">First_BranchID/Last_BranchID </t>
+  </si>
+  <si>
+    <t>First_EmployeeID/Last_EmployeeID</t>
+  </si>
+  <si>
+    <t>V3__inc_Gold_Fact_Restruct_Daily_Sold_Par</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        EmployeeID            VARCHAR(36)   NULL,</t>
+  </si>
+  <si>
+    <t>[СуммыЗадолженностиПоПериодамПросрочки Клиент ID]</t>
+  </si>
+  <si>
+    <t>[СуммыЗадолженностиПоПериодамПросрочки Количество Дней Просрочки Кредит]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[СуммыЗадолженностиПоПериодамПросрочки Фактическое Количество Дней Просрочки Итого] </t>
+  </si>
+  <si>
+    <t>[СуммыЗадолженностиПоПериодамПросрочки Количество Дней Просрочки МСФО]</t>
+  </si>
+  <si>
+    <t>[ОтветственныеПоКредитамВыданным Филиал ID] AS BranchID,</t>
+  </si>
+  <si>
+    <t>[ОтветственныеПоКредитамВыданным Кредитный Эксперт ID] AS EmployeeID,</t>
+  </si>
+  <si>
+    <t>Balance_Total</t>
+  </si>
+  <si>
+    <t>DaysBucket_Credit</t>
+  </si>
+  <si>
+    <t>DaysFact_Total</t>
+  </si>
+  <si>
+    <t>DaysIFRS</t>
   </si>
 </sst>
 </file>
@@ -2641,7 +2614,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -2967,11 +2940,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3035,6 +3023,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3323,7 +3316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E581"/>
+  <dimension ref="A1:E584"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.140625" customWidth="1"/>
@@ -3339,21 +3332,21 @@
         <v>7</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -3362,7 +3355,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="5" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="43"/>
@@ -3374,10 +3367,10 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D4" s="44"/>
       <c r="E4" s="38" t="str">
@@ -3388,10 +3381,10 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D5" s="44"/>
       <c r="E5" s="38" t="str">
@@ -3402,10 +3395,10 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="38" t="str">
@@ -3416,10 +3409,10 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D7" s="44"/>
       <c r="E7" s="38" t="str">
@@ -3430,10 +3423,10 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>203</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>212</v>
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="38" t="str">
@@ -3453,7 +3446,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="20"/>
@@ -3466,7 +3459,7 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="44"/>
@@ -3478,7 +3471,7 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>10</v>
@@ -3492,7 +3485,7 @@
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>0</v>
@@ -3506,7 +3499,7 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>1</v>
@@ -3520,10 +3513,10 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="38" t="str">
@@ -3534,10 +3527,10 @@
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="38" t="str">
@@ -3548,7 +3541,7 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>2</v>
@@ -3562,10 +3555,10 @@
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D18" s="44"/>
       <c r="E18" s="38" t="str">
@@ -3576,7 +3569,7 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>3</v>
@@ -3590,10 +3583,10 @@
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="38" t="str">
@@ -3604,7 +3597,7 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C21" s="27" t="s">
         <v>4</v>
@@ -3618,10 +3611,10 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D22" s="44"/>
       <c r="E22" s="38" t="str">
@@ -3632,10 +3625,10 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D23" s="44"/>
       <c r="E23" s="38" t="str">
@@ -3656,7 +3649,7 @@
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="1" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="44"/>
@@ -3668,7 +3661,7 @@
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C26" s="27" t="s">
         <v>34</v>
@@ -3682,10 +3675,10 @@
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="2" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="D27" s="44"/>
       <c r="E27" s="38" t="str">
@@ -3696,7 +3689,7 @@
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C28" s="27" t="s">
         <v>6</v>
@@ -3710,10 +3703,10 @@
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="2" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D29" s="44"/>
       <c r="E29" s="38" t="str">
@@ -3733,7 +3726,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -3746,7 +3739,7 @@
     <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="5" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="44"/>
@@ -3758,7 +3751,7 @@
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C33" s="26" t="s">
         <v>8</v>
@@ -3772,7 +3765,7 @@
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C34" s="27" t="s">
         <v>9</v>
@@ -3786,7 +3779,7 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C35" s="27" t="s">
         <v>10</v>
@@ -3800,7 +3793,7 @@
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C36" s="27" t="s">
         <v>11</v>
@@ -3814,7 +3807,7 @@
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C37" s="27" t="s">
         <v>12</v>
@@ -3828,7 +3821,7 @@
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C38" s="27" t="s">
         <v>13</v>
@@ -3842,7 +3835,7 @@
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C39" s="27" t="s">
         <v>14</v>
@@ -3856,7 +3849,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C40" s="27" t="s">
         <v>15</v>
@@ -3870,7 +3863,7 @@
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>16</v>
@@ -3884,7 +3877,7 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C42" s="27" t="s">
         <v>17</v>
@@ -3898,7 +3891,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C43" s="27" t="s">
         <v>5</v>
@@ -3912,7 +3905,7 @@
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C44" s="27" t="s">
         <v>25</v>
@@ -3926,7 +3919,7 @@
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C45" s="27" t="s">
         <v>18</v>
@@ -3940,7 +3933,7 @@
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C46" s="27" t="s">
         <v>19</v>
@@ -3954,7 +3947,7 @@
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C47" s="27" t="s">
         <v>20</v>
@@ -3968,7 +3961,7 @@
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C48" s="27" t="s">
         <v>21</v>
@@ -3982,7 +3975,7 @@
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C49" s="27" t="s">
         <v>22</v>
@@ -3996,7 +3989,7 @@
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C50" s="27" t="s">
         <v>23</v>
@@ -4010,7 +4003,7 @@
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C51" s="27" t="s">
         <v>24</v>
@@ -4024,7 +4017,7 @@
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C52" s="27" t="s">
         <v>26</v>
@@ -4038,7 +4031,7 @@
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C53" s="27" t="s">
         <v>27</v>
@@ -4052,7 +4045,7 @@
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C54" s="27" t="s">
         <v>3</v>
@@ -4066,7 +4059,7 @@
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C55" s="27" t="s">
         <v>28</v>
@@ -4080,7 +4073,7 @@
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C56" s="27" t="s">
         <v>29</v>
@@ -4094,7 +4087,7 @@
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C57" s="27" t="s">
         <v>30</v>
@@ -4108,7 +4101,7 @@
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C58" s="27" t="s">
         <v>31</v>
@@ -4122,7 +4115,7 @@
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C59" s="27" t="s">
         <v>32</v>
@@ -4136,7 +4129,7 @@
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C60" s="27" t="s">
         <v>33</v>
@@ -4150,10 +4143,10 @@
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="2" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="D61" s="44"/>
       <c r="E61" s="38" t="str">
@@ -4174,7 +4167,7 @@
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="1" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C63" s="27"/>
       <c r="D63" s="44"/>
@@ -4186,10 +4179,10 @@
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C64" s="27" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D64" s="44"/>
       <c r="E64" s="38" t="str">
@@ -4210,7 +4203,7 @@
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="1" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C66" s="27"/>
       <c r="D66" s="44"/>
@@ -4222,10 +4215,10 @@
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="2" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="D67" s="44"/>
       <c r="E67" s="38" t="str">
@@ -4246,7 +4239,7 @@
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="1" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="D69" s="44"/>
       <c r="E69" s="38" t="str">
@@ -4257,10 +4250,10 @@
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="2" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="C70" s="27" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="D70" s="44"/>
       <c r="E70" s="38" t="str">
@@ -4271,10 +4264,10 @@
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="2" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="D71" s="44"/>
       <c r="E71" s="38" t="str">
@@ -4285,10 +4278,10 @@
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="2" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C72" s="27" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D72" s="44"/>
       <c r="E72" s="38" t="str">
@@ -4309,7 +4302,7 @@
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="1" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C74" s="27"/>
       <c r="D74" s="44"/>
@@ -4321,10 +4314,10 @@
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="2" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D75" s="44"/>
       <c r="E75" s="38" t="str">
@@ -4335,10 +4328,10 @@
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="2" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="D76" s="44"/>
       <c r="E76" s="38" t="str">
@@ -4358,7 +4351,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -4371,7 +4364,7 @@
     <row r="79" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12"/>
       <c r="B79" s="5" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C79" s="32"/>
       <c r="D79" s="44"/>
@@ -4383,10 +4376,10 @@
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
       <c r="B80" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C80" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D80" s="44"/>
       <c r="E80" s="38" t="str">
@@ -4397,10 +4390,10 @@
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="B81" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D81" s="44"/>
       <c r="E81" s="38" t="str">
@@ -4411,10 +4404,10 @@
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C82" s="27" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D82" s="44"/>
       <c r="E82" s="38" t="str">
@@ -4425,10 +4418,10 @@
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D83" s="44"/>
       <c r="E83" s="38" t="str">
@@ -4439,10 +4432,10 @@
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D84" s="44"/>
       <c r="E84" s="38" t="str">
@@ -4453,10 +4446,10 @@
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D85" s="44"/>
       <c r="E85" s="38" t="str">
@@ -4467,10 +4460,10 @@
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D86" s="44"/>
       <c r="E86" s="38" t="str">
@@ -4481,10 +4474,10 @@
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
       <c r="B87" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="D87" s="44"/>
       <c r="E87" s="38" t="str">
@@ -4495,10 +4488,10 @@
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
       <c r="B88" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D88" s="44"/>
       <c r="E88" s="38" t="str">
@@ -4509,10 +4502,10 @@
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
       <c r="B89" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D89" s="44"/>
       <c r="E89" s="38" t="str">
@@ -4523,10 +4516,10 @@
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C90" s="27" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="D90" s="44"/>
       <c r="E90" s="38" t="str">
@@ -4537,10 +4530,10 @@
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
       <c r="B91" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D91" s="44"/>
       <c r="E91" s="38" t="str">
@@ -4551,10 +4544,10 @@
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
       <c r="B92" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D92" s="44"/>
       <c r="E92" s="38" t="str">
@@ -4565,10 +4558,10 @@
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="B93" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C93" s="27" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D93" s="44"/>
       <c r="E93" s="38" t="str">
@@ -4579,10 +4572,10 @@
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
       <c r="B94" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D94" s="44"/>
       <c r="E94" s="38" t="str">
@@ -4593,10 +4586,10 @@
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="B95" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D95" s="44"/>
       <c r="E95" s="38" t="str">
@@ -4607,10 +4600,10 @@
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="B96" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C96" s="27" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D96" s="44"/>
       <c r="E96" s="38" t="str">
@@ -4621,10 +4614,10 @@
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="B97" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C97" s="27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D97" s="44"/>
       <c r="E97" s="38" t="str">
@@ -4635,10 +4628,10 @@
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C98" s="27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D98" s="44"/>
       <c r="E98" s="38" t="str">
@@ -4649,10 +4642,10 @@
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C99" s="27" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D99" s="44"/>
       <c r="E99" s="38" t="str">
@@ -4663,10 +4656,10 @@
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C100" s="27" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D100" s="44"/>
       <c r="E100" s="38" t="str">
@@ -4677,10 +4670,10 @@
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="B101" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C101" s="27" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D101" s="44"/>
       <c r="E101" s="38" t="str">
@@ -4691,10 +4684,10 @@
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
       <c r="B102" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C102" s="27" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D102" s="44"/>
       <c r="E102" s="38" t="str">
@@ -4705,10 +4698,10 @@
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C103" s="27" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="D103" s="44"/>
       <c r="E103" s="38" t="str">
@@ -4719,10 +4712,10 @@
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C104" s="27" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D104" s="44"/>
       <c r="E104" s="38" t="str">
@@ -4733,10 +4726,10 @@
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="2" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="D105" s="44"/>
       <c r="E105" s="38" t="str">
@@ -4757,7 +4750,7 @@
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
       <c r="B107" s="1" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C107" s="27"/>
       <c r="D107" s="44"/>
@@ -4769,10 +4762,10 @@
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="B108" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C108" s="27" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D108" s="44"/>
       <c r="E108" s="38" t="str">
@@ -4793,7 +4786,7 @@
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
       <c r="B110" s="1" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="C110" s="27"/>
       <c r="D110" s="44"/>
@@ -4805,10 +4798,10 @@
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="B111" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C111" s="27" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D111" s="44"/>
       <c r="E111" s="38" t="str">
@@ -4829,7 +4822,7 @@
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="B113" s="1" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C113" s="27"/>
       <c r="D113" s="44"/>
@@ -4841,10 +4834,10 @@
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="B114" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C114" s="27" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D114" s="44"/>
       <c r="E114" s="38" t="str">
@@ -4855,10 +4848,10 @@
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
       <c r="B115" s="2" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="D115" s="44"/>
       <c r="E115" s="38" t="str">
@@ -4879,7 +4872,7 @@
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="B117" s="1" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C117" s="27"/>
       <c r="D117" s="44"/>
@@ -4891,10 +4884,10 @@
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C118" s="27" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="D118" s="44"/>
       <c r="E118" s="38" t="str">
@@ -4905,10 +4898,10 @@
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
       <c r="B119" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C119" s="27" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="D119" s="44"/>
       <c r="E119" s="38" t="str">
@@ -4929,7 +4922,7 @@
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="B121" s="1" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C121" s="27"/>
       <c r="D121" s="44"/>
@@ -4941,10 +4934,10 @@
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C122" s="27" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D122" s="44"/>
       <c r="E122" s="38" t="str">
@@ -4975,7 +4968,7 @@
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
       <c r="B125" s="1" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="C125" s="27"/>
       <c r="D125" s="44"/>
@@ -4987,10 +4980,10 @@
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
       <c r="B126" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C126" s="27" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D126" s="44"/>
       <c r="E126" s="38" t="str">
@@ -5001,10 +4994,10 @@
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
       <c r="B127" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C127" s="27" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="D127" s="44"/>
       <c r="E127" s="38" t="str">
@@ -5025,7 +5018,7 @@
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
       <c r="B129" s="1" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C129" s="27"/>
       <c r="D129" s="44"/>
@@ -5037,10 +5030,10 @@
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
       <c r="B130" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C130" s="27" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D130" s="44"/>
       <c r="E130" s="38" t="str">
@@ -5061,7 +5054,7 @@
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="B132" s="1" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C132" s="27"/>
       <c r="D132" s="44"/>
@@ -5073,10 +5066,10 @@
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
       <c r="B133" s="2" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C133" s="27" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="D133" s="44"/>
       <c r="E133" s="38" t="str">
@@ -5097,7 +5090,7 @@
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="13"/>
       <c r="B135" s="19" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="C135" s="27"/>
       <c r="D135" s="44"/>
@@ -5109,10 +5102,10 @@
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="13"/>
       <c r="B136" s="15" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="C136" s="27" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="D136" s="44"/>
       <c r="E136" s="38" t="str">
@@ -5123,10 +5116,10 @@
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="13"/>
       <c r="B137" s="15" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="C137" s="27" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D137" s="44"/>
       <c r="E137" s="38" t="str">
@@ -5137,10 +5130,10 @@
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="13"/>
       <c r="B138" s="15" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C138" s="27" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="D138" s="44"/>
       <c r="E138" s="38" t="str">
@@ -5161,7 +5154,7 @@
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="13"/>
       <c r="B140" s="19" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="C140" s="27"/>
       <c r="D140" s="44"/>
@@ -5173,10 +5166,10 @@
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="13"/>
       <c r="B141" s="15" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C141" s="27" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="D141" s="44"/>
       <c r="E141" s="38" t="str">
@@ -5187,10 +5180,10 @@
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="13"/>
       <c r="B142" s="15" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="C142" s="27" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D142" s="44"/>
       <c r="E142" s="38" t="str">
@@ -5200,7 +5193,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="22" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="16"/>
@@ -5213,7 +5206,7 @@
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="13"/>
       <c r="B144" s="19" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C144" s="33"/>
       <c r="D144" s="44"/>
@@ -5225,10 +5218,10 @@
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="13"/>
       <c r="B145" s="15" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C145" s="27" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="D145" s="44"/>
       <c r="E145" s="38" t="str">
@@ -5239,10 +5232,10 @@
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="13"/>
       <c r="B146" s="15" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C146" s="27" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D146" s="44"/>
       <c r="E146" s="38" t="str">
@@ -5262,7 +5255,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="22" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B148" s="20"/>
       <c r="C148" s="16"/>
@@ -5275,7 +5268,7 @@
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="13"/>
       <c r="B149" s="19" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C149" s="33"/>
       <c r="D149" s="44"/>
@@ -5287,10 +5280,10 @@
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="13"/>
       <c r="B150" s="15" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C150" s="27" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="D150" s="44"/>
       <c r="E150" s="38" t="str">
@@ -5301,7 +5294,7 @@
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="13"/>
       <c r="B151" s="15" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="C151" s="27" t="s">
         <v>10</v>
@@ -5315,10 +5308,10 @@
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="13"/>
       <c r="B152" s="15" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C152" s="27" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="D152" s="44"/>
       <c r="E152" s="38" t="str">
@@ -5329,10 +5322,10 @@
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="13"/>
       <c r="B153" s="15" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C153" s="27" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="D153" s="44"/>
       <c r="E153" s="38" t="str">
@@ -5343,10 +5336,10 @@
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="13"/>
       <c r="B154" s="15" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="C154" s="27" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="D154" s="44"/>
       <c r="E154" s="38" t="str">
@@ -5357,10 +5350,10 @@
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="13"/>
       <c r="B155" s="15" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C155" s="27" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D155" s="44"/>
       <c r="E155" s="38" t="str">
@@ -5371,10 +5364,10 @@
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="13"/>
       <c r="B156" s="15" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C156" s="27" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="D156" s="44"/>
       <c r="E156" s="38" t="str">
@@ -5385,10 +5378,10 @@
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="13"/>
       <c r="B157" s="15" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C157" s="27" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D157" s="44"/>
       <c r="E157" s="38" t="str">
@@ -5399,10 +5392,10 @@
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="13"/>
       <c r="B158" s="15" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D158" s="44"/>
       <c r="E158" s="38" t="str">
@@ -5413,10 +5406,10 @@
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="13"/>
       <c r="B159" s="15" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C159" s="27" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D159" s="44"/>
       <c r="E159" s="38" t="str">
@@ -5427,10 +5420,10 @@
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="13"/>
       <c r="B160" s="15" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="C160" s="27" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="D160" s="44"/>
       <c r="E160" s="38" t="str">
@@ -5440,7 +5433,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="22" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B161" s="20"/>
       <c r="C161" s="34"/>
@@ -5453,7 +5446,7 @@
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="23"/>
       <c r="B162" s="24" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C162" s="26"/>
       <c r="D162" s="44"/>
@@ -5465,10 +5458,10 @@
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="13"/>
       <c r="B163" s="15" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="C163" s="27" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D163" s="44"/>
       <c r="E163" s="38" t="str">
@@ -5479,10 +5472,10 @@
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="13"/>
       <c r="B164" s="15" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="C164" s="27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D164" s="44"/>
       <c r="E164" s="38" t="str">
@@ -5493,10 +5486,10 @@
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="13"/>
       <c r="B165" s="15" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C165" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D165" s="44"/>
       <c r="E165" s="38" t="str">
@@ -5507,10 +5500,10 @@
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="13"/>
       <c r="B166" s="15" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C166" s="27" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D166" s="44"/>
       <c r="E166" s="38" t="str">
@@ -5521,10 +5514,10 @@
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="13"/>
       <c r="B167" s="15" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C167" s="27" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D167" s="44"/>
       <c r="E167" s="38" t="str">
@@ -5535,10 +5528,10 @@
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="13"/>
       <c r="B168" s="15" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C168" s="27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D168" s="44"/>
       <c r="E168" s="38" t="str">
@@ -5549,10 +5542,10 @@
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="13"/>
       <c r="B169" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C169" s="27" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D169" s="44"/>
       <c r="E169" s="38" t="str">
@@ -5563,10 +5556,10 @@
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="13"/>
       <c r="B170" s="15" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C170" s="27" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D170" s="44"/>
       <c r="E170" s="38" t="str">
@@ -5577,10 +5570,10 @@
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="13"/>
       <c r="B171" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C171" s="27" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D171" s="44"/>
       <c r="E171" s="38" t="str">
@@ -5591,10 +5584,10 @@
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="13"/>
       <c r="B172" s="15" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="C172" s="27" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D172" s="44"/>
       <c r="E172" s="38" t="str">
@@ -5604,7 +5597,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="22" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="B173" s="20"/>
       <c r="C173" s="34"/>
@@ -5617,7 +5610,7 @@
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="13"/>
       <c r="B174" s="19" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C174" s="39"/>
       <c r="D174" s="44"/>
@@ -5629,10 +5622,10 @@
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="13"/>
       <c r="B175" s="15" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C175" s="27" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="D175" s="44"/>
       <c r="E175" s="38" t="str">
@@ -5643,10 +5636,10 @@
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="13"/>
       <c r="B176" s="15" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="C176" s="27" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="D176" s="44"/>
       <c r="E176" s="38" t="str">
@@ -5657,10 +5650,10 @@
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="13"/>
       <c r="B177" s="15" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="C177" s="27" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="D177" s="44"/>
       <c r="E177" s="38" t="str">
@@ -5671,10 +5664,10 @@
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="13"/>
       <c r="B178" s="15" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C178" s="27" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="D178" s="44"/>
       <c r="E178" s="38" t="str">
@@ -5685,10 +5678,10 @@
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="15" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C179" s="27" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="D179" s="44"/>
       <c r="E179" s="38" t="str">
@@ -5699,10 +5692,10 @@
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="13"/>
       <c r="B180" s="15" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="C180" s="27" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="D180" s="44"/>
       <c r="E180" s="38" t="str">
@@ -5713,10 +5706,10 @@
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="13"/>
       <c r="B181" s="15" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="C181" s="27" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="D181" s="44"/>
       <c r="E181" s="38" t="str">
@@ -5727,10 +5720,10 @@
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="13"/>
       <c r="B182" s="15" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="C182" s="27" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="D182" s="44"/>
       <c r="E182" s="38" t="str">
@@ -5741,10 +5734,10 @@
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="13"/>
       <c r="B183" s="15" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="C183" s="27" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D183" s="44"/>
       <c r="E183" s="38" t="str">
@@ -5755,10 +5748,10 @@
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="13"/>
       <c r="B184" s="15" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C184" s="27" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D184" s="44"/>
       <c r="E184" s="38" t="str">
@@ -5769,10 +5762,10 @@
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="13"/>
       <c r="B185" s="15" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="C185" s="27" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="D185" s="44"/>
       <c r="E185" s="38" t="str">
@@ -5783,10 +5776,10 @@
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="13"/>
       <c r="B186" s="15" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="C186" s="27" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="D186" s="44"/>
       <c r="E186" s="38" t="str">
@@ -5797,10 +5790,10 @@
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="13"/>
       <c r="B187" s="15" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C187" s="27" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="D187" s="44"/>
       <c r="E187" s="38" t="str">
@@ -5811,10 +5804,10 @@
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="13"/>
       <c r="B188" s="15" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="C188" s="27" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="D188" s="44"/>
       <c r="E188" s="38" t="str">
@@ -5825,10 +5818,10 @@
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="13"/>
       <c r="B189" s="15" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C189" s="27" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D189" s="44"/>
       <c r="E189" s="38" t="str">
@@ -5839,10 +5832,10 @@
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="13"/>
       <c r="B190" s="15" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C190" s="27" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="D190" s="44"/>
       <c r="E190" s="38" t="str">
@@ -5862,7 +5855,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="22" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="B192" s="20"/>
       <c r="C192" s="34"/>
@@ -5875,7 +5868,7 @@
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="13"/>
       <c r="B193" s="19" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="C193" s="39"/>
       <c r="D193" s="44"/>
@@ -5887,10 +5880,10 @@
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="13"/>
       <c r="B194" s="15" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="C194" s="27" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="D194" s="44"/>
       <c r="E194" s="38" t="str">
@@ -5901,10 +5894,10 @@
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="13"/>
       <c r="B195" s="15" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="C195" s="27" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="D195" s="44"/>
       <c r="E195" s="38" t="str">
@@ -5915,10 +5908,10 @@
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="13"/>
       <c r="B196" s="15" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="C196" s="27" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="D196" s="44"/>
       <c r="E196" s="38" t="str">
@@ -5929,10 +5922,10 @@
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="13"/>
       <c r="B197" s="15" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="C197" s="27" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="D197" s="44"/>
       <c r="E197" s="38" t="str">
@@ -5943,10 +5936,10 @@
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="13"/>
       <c r="B198" s="15" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="C198" s="27" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="D198" s="44"/>
       <c r="E198" s="38" t="str">
@@ -5957,10 +5950,10 @@
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="13"/>
       <c r="B199" s="15" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="C199" s="27" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="D199" s="44"/>
       <c r="E199" s="38" t="str">
@@ -5971,10 +5964,10 @@
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="13"/>
       <c r="B200" s="15" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C200" s="27" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="D200" s="44"/>
       <c r="E200" s="38" t="str">
@@ -5995,7 +5988,7 @@
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="13"/>
       <c r="B202" s="19" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C202" s="27"/>
       <c r="D202" s="44"/>
@@ -6007,10 +6000,10 @@
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="13"/>
       <c r="B203" s="15" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="C203" s="27" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="D203" s="44"/>
       <c r="E203" s="38" t="str">
@@ -6021,10 +6014,10 @@
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="13"/>
       <c r="B204" s="15" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C204" s="27" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="D204" s="44"/>
       <c r="E204" s="38" t="str">
@@ -6035,10 +6028,10 @@
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="13"/>
       <c r="B205" s="15" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="C205" s="27" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D205" s="44"/>
       <c r="E205" s="38" t="str">
@@ -6049,10 +6042,10 @@
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="13"/>
       <c r="B206" s="15" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="C206" s="27" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="D206" s="44"/>
       <c r="E206" s="38" t="str">
@@ -6072,7 +6065,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="22" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="B208" s="17"/>
       <c r="C208" s="21"/>
@@ -6085,7 +6078,7 @@
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="12"/>
       <c r="B209" s="5" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C209" s="26"/>
       <c r="D209" s="44"/>
@@ -6097,10 +6090,10 @@
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
       <c r="B210" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C210" s="27" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="D210" s="44"/>
       <c r="E210" s="38" t="str">
@@ -6111,10 +6104,10 @@
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
       <c r="B211" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C211" s="27" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="D211" s="44"/>
       <c r="E211" s="38" t="str">
@@ -6125,10 +6118,10 @@
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="3"/>
       <c r="B212" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C212" s="27" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="D212" s="44"/>
       <c r="E212" s="38" t="str">
@@ -6139,10 +6132,10 @@
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="3"/>
       <c r="B213" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C213" s="27" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="D213" s="44"/>
       <c r="E213" s="38" t="str">
@@ -6153,10 +6146,10 @@
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="3"/>
       <c r="B214" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C214" s="27" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="D214" s="44"/>
       <c r="E214" s="38" t="str">
@@ -6167,10 +6160,10 @@
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="3"/>
       <c r="B215" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C215" s="27" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="D215" s="44"/>
       <c r="E215" s="38" t="str">
@@ -6191,7 +6184,7 @@
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="3"/>
       <c r="B217" s="5" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C217" s="27"/>
       <c r="D217" s="44"/>
@@ -6203,10 +6196,10 @@
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="3"/>
       <c r="B218" s="11" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C218" s="27" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="D218" s="44"/>
       <c r="E218" s="38" t="str">
@@ -6226,7 +6219,7 @@
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="3"/>
       <c r="B220" s="1" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="C220" s="27"/>
       <c r="D220" s="44"/>
@@ -6238,10 +6231,10 @@
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="3"/>
       <c r="B221" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C221" s="27" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D221" s="44"/>
       <c r="E221" s="38" t="str">
@@ -6252,10 +6245,10 @@
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="3"/>
       <c r="B222" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C222" s="27" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="D222" s="44"/>
       <c r="E222" s="38" t="str">
@@ -6266,10 +6259,10 @@
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="3"/>
       <c r="B223" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C223" s="27" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="D223" s="44"/>
       <c r="E223" s="38" t="str">
@@ -6280,10 +6273,10 @@
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="3"/>
       <c r="B224" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C224" s="27" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="D224" s="44"/>
       <c r="E224" s="38" t="str">
@@ -6294,10 +6287,10 @@
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="3"/>
       <c r="B225" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C225" s="27" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="D225" s="44"/>
       <c r="E225" s="38" t="str">
@@ -6308,10 +6301,10 @@
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="3"/>
       <c r="B226" s="2" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C226" s="27" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="D226" s="44"/>
       <c r="E226" s="38" t="str">
@@ -6322,10 +6315,10 @@
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="3"/>
       <c r="B227" s="2" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C227" s="27" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="D227" s="44"/>
       <c r="E227" s="38" t="str">
@@ -6336,10 +6329,10 @@
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="3"/>
       <c r="B228" s="2" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="C228" s="27" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="D228" s="44"/>
       <c r="E228" s="38" t="str">
@@ -6359,7 +6352,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="22" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="B230" s="20"/>
       <c r="C230" s="16"/>
@@ -6372,7 +6365,7 @@
     <row r="231" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="12"/>
       <c r="B231" s="5" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="C231" s="35"/>
       <c r="D231" s="44"/>
@@ -6384,10 +6377,10 @@
     <row r="232" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12"/>
       <c r="B232" s="11" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="C232" s="27" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="D232" s="44"/>
       <c r="E232" s="38" t="str">
@@ -6398,10 +6391,10 @@
     <row r="233" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="12"/>
       <c r="B233" s="11" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="C233" s="27" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="D233" s="44"/>
       <c r="E233" s="38" t="str">
@@ -6412,10 +6405,10 @@
     <row r="234" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12"/>
       <c r="B234" s="11" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="C234" s="27" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="D234" s="44"/>
       <c r="E234" s="38" t="str">
@@ -6426,10 +6419,10 @@
     <row r="235" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="12"/>
       <c r="B235" s="11" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="C235" s="27" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="D235" s="44"/>
       <c r="E235" s="38" t="str">
@@ -6440,10 +6433,10 @@
     <row r="236" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12"/>
       <c r="B236" s="11" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="C236" s="27" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="D236" s="44"/>
       <c r="E236" s="38" t="str">
@@ -6454,10 +6447,10 @@
     <row r="237" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="12"/>
       <c r="B237" s="11" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="C237" s="27" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="D237" s="44"/>
       <c r="E237" s="38" t="str">
@@ -6468,10 +6461,10 @@
     <row r="238" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12"/>
       <c r="B238" s="11" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C238" s="27" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="D238" s="44"/>
       <c r="E238" s="38" t="str">
@@ -6482,10 +6475,10 @@
     <row r="239" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="12"/>
       <c r="B239" s="11" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="D239" s="44"/>
       <c r="E239" s="38" t="str">
@@ -6496,10 +6489,10 @@
     <row r="240" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12"/>
       <c r="B240" s="11" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="C240" s="27" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="D240" s="44"/>
       <c r="E240" s="38" t="str">
@@ -6510,10 +6503,10 @@
     <row r="241" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12"/>
       <c r="B241" s="11" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="C241" s="27" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="D241" s="44"/>
       <c r="E241" s="38" t="str">
@@ -6524,10 +6517,10 @@
     <row r="242" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12"/>
       <c r="B242" s="11" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="C242" s="27" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="D242" s="44"/>
       <c r="E242" s="38" t="str">
@@ -6538,10 +6531,10 @@
     <row r="243" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="12"/>
       <c r="B243" s="11" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="C243" s="27" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="D243" s="44"/>
       <c r="E243" s="38" t="str">
@@ -6552,10 +6545,10 @@
     <row r="244" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12"/>
       <c r="B244" s="11" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="C244" s="27" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="D244" s="44"/>
       <c r="E244" s="38" t="str">
@@ -6566,10 +6559,10 @@
     <row r="245" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="12"/>
       <c r="B245" s="11" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="C245" s="27" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="D245" s="44"/>
       <c r="E245" s="38" t="str">
@@ -6580,10 +6573,10 @@
     <row r="246" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12"/>
       <c r="B246" s="11" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="C246" s="27" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="D246" s="44"/>
       <c r="E246" s="38" t="str">
@@ -6594,10 +6587,10 @@
     <row r="247" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="12"/>
       <c r="B247" s="11" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="C247" s="27" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="D247" s="44"/>
       <c r="E247" s="38" t="str">
@@ -6608,10 +6601,10 @@
     <row r="248" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12"/>
       <c r="B248" s="11" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="C248" s="27" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="D248" s="44"/>
       <c r="E248" s="38" t="str">
@@ -6622,10 +6615,10 @@
     <row r="249" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="12"/>
       <c r="B249" s="11" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="C249" s="27" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="D249" s="44"/>
       <c r="E249" s="38" t="str">
@@ -6636,10 +6629,10 @@
     <row r="250" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12"/>
       <c r="B250" s="11" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="C250" s="27" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D250" s="44"/>
       <c r="E250" s="38" t="str">
@@ -6650,10 +6643,10 @@
     <row r="251" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="12"/>
       <c r="B251" s="11" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="C251" s="27" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="D251" s="44"/>
       <c r="E251" s="38" t="str">
@@ -6664,10 +6657,10 @@
     <row r="252" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12"/>
       <c r="B252" s="11" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="C252" s="27" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D252" s="44"/>
       <c r="E252" s="38" t="str">
@@ -6678,10 +6671,10 @@
     <row r="253" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="12"/>
       <c r="B253" s="11" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="C253" s="27" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="D253" s="44"/>
       <c r="E253" s="38" t="str">
@@ -6692,10 +6685,10 @@
     <row r="254" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12"/>
       <c r="B254" s="11" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="C254" s="27" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="D254" s="44"/>
       <c r="E254" s="38" t="str">
@@ -6706,10 +6699,10 @@
     <row r="255" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="12"/>
       <c r="B255" s="11" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="C255" s="27" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D255" s="44"/>
       <c r="E255" s="38" t="str">
@@ -6720,10 +6713,10 @@
     <row r="256" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12"/>
       <c r="B256" s="11" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="C256" s="27" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="D256" s="44"/>
       <c r="E256" s="38" t="str">
@@ -6734,10 +6727,10 @@
     <row r="257" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="12"/>
       <c r="B257" s="11" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="C257" s="27" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="D257" s="44"/>
       <c r="E257" s="38" t="str">
@@ -6748,10 +6741,10 @@
     <row r="258" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12"/>
       <c r="B258" s="11" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="C258" s="27" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D258" s="44"/>
       <c r="E258" s="38" t="str">
@@ -6762,10 +6755,10 @@
     <row r="259" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="12"/>
       <c r="B259" s="11" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C259" s="27" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="D259" s="44"/>
       <c r="E259" s="38" t="str">
@@ -6776,10 +6769,10 @@
     <row r="260" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
       <c r="B260" s="11" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="C260" s="27" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="D260" s="44"/>
       <c r="E260" s="38" t="str">
@@ -6790,10 +6783,10 @@
     <row r="261" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="12"/>
       <c r="B261" s="11" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="C261" s="27" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="D261" s="44"/>
       <c r="E261" s="38" t="str">
@@ -6804,10 +6797,10 @@
     <row r="262" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12"/>
       <c r="B262" s="11" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="C262" s="27" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="D262" s="44"/>
       <c r="E262" s="38" t="str">
@@ -6818,10 +6811,10 @@
     <row r="263" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12"/>
       <c r="B263" s="11" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="C263" s="27" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="D263" s="44"/>
       <c r="E263" s="38" t="str">
@@ -6832,10 +6825,10 @@
     <row r="264" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12"/>
       <c r="B264" s="11" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C264" s="27" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="D264" s="44"/>
       <c r="E264" s="38" t="str">
@@ -6846,10 +6839,10 @@
     <row r="265" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12"/>
       <c r="B265" s="11" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="C265" s="27" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D265" s="44"/>
       <c r="E265" s="38" t="str">
@@ -6860,10 +6853,10 @@
     <row r="266" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12"/>
       <c r="B266" s="11" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="C266" s="27" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="D266" s="44"/>
       <c r="E266" s="38" t="str">
@@ -6874,10 +6867,10 @@
     <row r="267" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12"/>
       <c r="B267" s="11" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C267" s="27" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="D267" s="44"/>
       <c r="E267" s="38" t="str">
@@ -6888,10 +6881,10 @@
     <row r="268" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12"/>
       <c r="B268" s="11" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="C268" s="27" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D268" s="44"/>
       <c r="E268" s="38" t="str">
@@ -6902,10 +6895,10 @@
     <row r="269" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="12"/>
       <c r="B269" s="11" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="C269" s="27" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="D269" s="44"/>
       <c r="E269" s="38" t="str">
@@ -6916,10 +6909,10 @@
     <row r="270" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12"/>
       <c r="B270" s="11" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="C270" s="27" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="D270" s="44"/>
       <c r="E270" s="38" t="str">
@@ -6930,10 +6923,10 @@
     <row r="271" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="12"/>
       <c r="B271" s="11" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="C271" s="27" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="D271" s="44"/>
       <c r="E271" s="38" t="str">
@@ -6944,10 +6937,10 @@
     <row r="272" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12"/>
       <c r="B272" s="11" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="C272" s="27" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D272" s="44"/>
       <c r="E272" s="38" t="str">
@@ -6968,7 +6961,7 @@
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="12"/>
       <c r="B274" s="5" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="C274" s="27"/>
       <c r="D274" s="46"/>
@@ -6980,10 +6973,10 @@
     <row r="275" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="12"/>
       <c r="B275" s="11" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="C275" s="27" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="D275" s="44"/>
       <c r="E275" s="38" t="str">
@@ -6994,10 +6987,10 @@
     <row r="276" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12"/>
       <c r="B276" s="11" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="C276" s="27" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="D276" s="44"/>
       <c r="E276" s="38" t="str">
@@ -7008,10 +7001,10 @@
     <row r="277" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="12"/>
       <c r="B277" s="11" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="C277" s="27" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="D277" s="44"/>
       <c r="E277" s="38" t="str">
@@ -7022,10 +7015,10 @@
     <row r="278" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12"/>
       <c r="B278" s="11" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="D278" s="44"/>
       <c r="E278" s="38" t="str">
@@ -7036,10 +7029,10 @@
     <row r="279" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="12"/>
       <c r="B279" s="11" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C279" s="27" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="D279" s="44"/>
       <c r="E279" s="38" t="str">
@@ -7050,10 +7043,10 @@
     <row r="280" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12"/>
       <c r="B280" s="11" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C280" s="27" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="D280" s="44"/>
       <c r="E280" s="38" t="str">
@@ -7064,10 +7057,10 @@
     <row r="281" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="12"/>
       <c r="B281" s="11" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C281" s="27" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="D281" s="44"/>
       <c r="E281" s="38" t="str">
@@ -7078,10 +7071,10 @@
     <row r="282" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12"/>
       <c r="B282" s="11" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C282" s="27" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="D282" s="44"/>
       <c r="E282" s="38" t="str">
@@ -7092,10 +7085,10 @@
     <row r="283" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="12"/>
       <c r="B283" s="11" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="C283" s="27" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D283" s="44"/>
       <c r="E283" s="38" t="str">
@@ -7106,10 +7099,10 @@
     <row r="284" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12"/>
       <c r="B284" s="11" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="C284" s="27" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="D284" s="44"/>
       <c r="E284" s="38" t="str">
@@ -7120,10 +7113,10 @@
     <row r="285" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="12"/>
       <c r="B285" s="11" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="C285" s="27" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="D285" s="44"/>
       <c r="E285" s="38" t="str">
@@ -7134,10 +7127,10 @@
     <row r="286" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12"/>
       <c r="B286" s="11" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="C286" s="27" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D286" s="44"/>
       <c r="E286" s="38" t="str">
@@ -7158,7 +7151,7 @@
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="12"/>
       <c r="B288" s="5" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="C288" s="27"/>
       <c r="D288" s="46"/>
@@ -7170,10 +7163,10 @@
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="12"/>
       <c r="B289" s="11" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="C289" s="35" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="D289" s="46"/>
       <c r="E289" s="38" t="str">
@@ -7184,10 +7177,10 @@
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="12"/>
       <c r="B290" s="11" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="C290" s="35" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="D290" s="46"/>
       <c r="E290" s="38" t="str">
@@ -7198,10 +7191,10 @@
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="12"/>
       <c r="B291" s="11" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C291" s="35" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="D291" s="46"/>
       <c r="E291" s="38" t="str">
@@ -7212,10 +7205,10 @@
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="12"/>
       <c r="B292" s="11" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="C292" s="35" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="D292" s="46"/>
       <c r="E292" s="38" t="str">
@@ -7226,10 +7219,10 @@
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="12"/>
       <c r="B293" s="11" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="C293" s="35" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="D293" s="46"/>
       <c r="E293" s="38" t="str">
@@ -7240,10 +7233,10 @@
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="12"/>
       <c r="B294" s="11" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="C294" s="35" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="D294" s="46"/>
       <c r="E294" s="38" t="str">
@@ -7254,10 +7247,10 @@
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="12"/>
       <c r="B295" s="11" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="C295" s="35" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="D295" s="46"/>
       <c r="E295" s="38" t="str">
@@ -7268,10 +7261,10 @@
     <row r="296" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12"/>
       <c r="B296" s="11" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="C296" s="35" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="D296" s="44"/>
       <c r="E296" s="38" t="str">
@@ -7282,10 +7275,10 @@
     <row r="297" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="12"/>
       <c r="B297" s="11" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C297" s="35" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="D297" s="44"/>
       <c r="E297" s="38" t="str">
@@ -7296,10 +7289,10 @@
     <row r="298" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12"/>
       <c r="B298" s="11" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="C298" s="35" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="D298" s="44"/>
       <c r="E298" s="38" t="str">
@@ -7320,7 +7313,7 @@
     <row r="300" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12"/>
       <c r="B300" s="5" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C300" s="35"/>
       <c r="D300" s="44"/>
@@ -7332,10 +7325,10 @@
     <row r="301" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12"/>
       <c r="B301" s="11" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="C301" s="35" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D301" s="44"/>
       <c r="E301" s="38" t="str">
@@ -7346,10 +7339,10 @@
     <row r="302" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="12"/>
       <c r="B302" s="11" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="C302" s="35" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="D302" s="44"/>
       <c r="E302" s="38" t="str">
@@ -7369,7 +7362,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="22" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="B304" s="20"/>
       <c r="C304" s="16"/>
@@ -7382,7 +7375,7 @@
     <row r="305" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12"/>
       <c r="B305" s="5" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C305" s="35"/>
       <c r="D305" s="44"/>
@@ -7394,10 +7387,10 @@
     <row r="306" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="12"/>
       <c r="B306" s="2" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C306" s="35" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="D306" s="44"/>
       <c r="E306" s="38" t="str">
@@ -7408,10 +7401,10 @@
     <row r="307" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12"/>
       <c r="B307" s="2" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="C307" s="35" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="D307" s="44"/>
       <c r="E307" s="38" t="str">
@@ -7422,10 +7415,10 @@
     <row r="308" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="12"/>
       <c r="B308" s="2" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C308" s="35" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="D308" s="44"/>
       <c r="E308" s="38" t="str">
@@ -7436,10 +7429,10 @@
     <row r="309" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12"/>
       <c r="B309" s="2" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="C309" s="35" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="D309" s="44"/>
       <c r="E309" s="38" t="str">
@@ -7450,10 +7443,10 @@
     <row r="310" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="12"/>
       <c r="B310" s="2" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="C310" s="35" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D310" s="44"/>
       <c r="E310" s="38" t="str">
@@ -7464,10 +7457,10 @@
     <row r="311" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12"/>
       <c r="B311" s="2" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="D311" s="44"/>
       <c r="E311" s="38" t="str">
@@ -7478,10 +7471,10 @@
     <row r="312" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="12"/>
       <c r="B312" s="2" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="C312" s="35" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="D312" s="44"/>
       <c r="E312" s="38" t="str">
@@ -7492,10 +7485,10 @@
     <row r="313" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="12"/>
       <c r="B313" s="2" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="C313" s="35" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="D313" s="44"/>
       <c r="E313" s="38" t="str">
@@ -7506,10 +7499,10 @@
     <row r="314" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="12"/>
       <c r="B314" s="2" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="C314" s="35" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="D314" s="44"/>
       <c r="E314" s="38" t="str">
@@ -7520,10 +7513,10 @@
     <row r="315" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="12"/>
       <c r="B315" s="2" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="C315" s="35" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="D315" s="44"/>
       <c r="E315" s="38" t="str">
@@ -7534,10 +7527,10 @@
     <row r="316" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="12"/>
       <c r="B316" s="2" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C316" s="35" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="D316" s="44"/>
       <c r="E316" s="38" t="str">
@@ -7548,10 +7541,10 @@
     <row r="317" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="12"/>
       <c r="B317" s="2" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C317" s="35" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="D317" s="44"/>
       <c r="E317" s="38" t="str">
@@ -7562,10 +7555,10 @@
     <row r="318" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="12"/>
       <c r="B318" s="2" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="C318" s="35" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="D318" s="44"/>
       <c r="E318" s="38" t="str">
@@ -7576,10 +7569,10 @@
     <row r="319" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="12"/>
       <c r="B319" s="2" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="C319" s="35" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="D319" s="44"/>
       <c r="E319" s="38" t="str">
@@ -7590,10 +7583,10 @@
     <row r="320" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="12"/>
       <c r="B320" s="2" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="C320" s="35" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="D320" s="44"/>
       <c r="E320" s="38" t="str">
@@ -7604,10 +7597,10 @@
     <row r="321" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="12"/>
       <c r="B321" s="2" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="C321" s="35" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="D321" s="44"/>
       <c r="E321" s="38" t="str">
@@ -7618,10 +7611,10 @@
     <row r="322" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="12"/>
       <c r="B322" s="2" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="C322" s="35" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="D322" s="44"/>
       <c r="E322" s="38" t="str">
@@ -7632,10 +7625,10 @@
     <row r="323" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="12"/>
       <c r="B323" s="2" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C323" s="35" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="D323" s="44"/>
       <c r="E323" s="38" t="str">
@@ -7646,10 +7639,10 @@
     <row r="324" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="12"/>
       <c r="B324" s="2" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C324" s="35" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="D324" s="44"/>
       <c r="E324" s="38" t="str">
@@ -7660,10 +7653,10 @@
     <row r="325" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="12"/>
       <c r="B325" s="2" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C325" s="35" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="D325" s="44"/>
       <c r="E325" s="38" t="str">
@@ -7674,10 +7667,10 @@
     <row r="326" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="12"/>
       <c r="B326" s="2" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C326" s="35" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D326" s="44"/>
       <c r="E326" s="38" t="str">
@@ -7688,10 +7681,10 @@
     <row r="327" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="12"/>
       <c r="B327" s="2" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="C327" s="35" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="D327" s="44"/>
       <c r="E327" s="38" t="str">
@@ -7702,10 +7695,10 @@
     <row r="328" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="12"/>
       <c r="B328" s="2" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="C328" s="35" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="D328" s="44"/>
       <c r="E328" s="38" t="str">
@@ -7716,10 +7709,10 @@
     <row r="329" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="12"/>
       <c r="B329" s="2" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="C329" s="35" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="D329" s="44"/>
       <c r="E329" s="38" t="str">
@@ -7730,10 +7723,10 @@
     <row r="330" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="12"/>
       <c r="B330" s="2" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="C330" s="35" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="D330" s="44"/>
       <c r="E330" s="38" t="str">
@@ -7744,10 +7737,10 @@
     <row r="331" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="12"/>
       <c r="B331" s="2" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="C331" s="35" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="D331" s="44"/>
       <c r="E331" s="38" t="str">
@@ -7758,10 +7751,10 @@
     <row r="332" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="12"/>
       <c r="B332" s="2" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="C332" s="35" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="D332" s="44"/>
       <c r="E332" s="38" t="str">
@@ -7772,10 +7765,10 @@
     <row r="333" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="12"/>
       <c r="B333" s="2" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="C333" s="35" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="D333" s="44"/>
       <c r="E333" s="38" t="str">
@@ -7796,7 +7789,7 @@
     <row r="335" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="12"/>
       <c r="B335" s="5" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C335" s="35"/>
       <c r="D335" s="44"/>
@@ -7808,10 +7801,10 @@
     <row r="336" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="12"/>
       <c r="B336" s="2" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C336" s="35" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D336" s="44"/>
       <c r="E336" s="38" t="str">
@@ -7822,10 +7815,10 @@
     <row r="337" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="12"/>
       <c r="B337" s="2" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="C337" s="35" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="D337" s="44"/>
       <c r="E337" s="38" t="str">
@@ -7836,10 +7829,10 @@
     <row r="338" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="12"/>
       <c r="B338" s="2" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="C338" s="35" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="D338" s="44"/>
       <c r="E338" s="38" t="str">
@@ -7850,10 +7843,10 @@
     <row r="339" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="12"/>
       <c r="B339" s="2" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="C339" s="35" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="D339" s="44"/>
       <c r="E339" s="38" t="str">
@@ -7864,10 +7857,10 @@
     <row r="340" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="12"/>
       <c r="B340" s="2" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="C340" s="35" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="D340" s="44"/>
       <c r="E340" s="38" t="str">
@@ -7878,10 +7871,10 @@
     <row r="341" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="12"/>
       <c r="B341" s="2" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="C341" s="35" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D341" s="44"/>
       <c r="E341" s="38" t="str">
@@ -7892,10 +7885,10 @@
     <row r="342" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="12"/>
       <c r="B342" s="2" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="C342" s="35" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="D342" s="44"/>
       <c r="E342" s="38" t="str">
@@ -7906,10 +7899,10 @@
     <row r="343" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="12"/>
       <c r="B343" s="2" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="C343" s="35" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="D343" s="44"/>
       <c r="E343" s="38" t="str">
@@ -7920,10 +7913,10 @@
     <row r="344" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="12"/>
       <c r="B344" s="2" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="C344" s="35" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="D344" s="44"/>
       <c r="E344" s="38" t="str">
@@ -7934,10 +7927,10 @@
     <row r="345" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="12"/>
       <c r="B345" s="2" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="C345" s="35" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="D345" s="44"/>
       <c r="E345" s="38" t="str">
@@ -7948,10 +7941,10 @@
     <row r="346" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="12"/>
       <c r="B346" s="2" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="C346" s="35" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="D346" s="44"/>
       <c r="E346" s="38" t="str">
@@ -7962,10 +7955,10 @@
     <row r="347" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="12"/>
       <c r="B347" s="2" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="C347" s="35" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="D347" s="44"/>
       <c r="E347" s="38" t="str">
@@ -7976,10 +7969,10 @@
     <row r="348" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="12"/>
       <c r="B348" s="2" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="C348" s="35" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="D348" s="44"/>
       <c r="E348" s="38" t="str">
@@ -7990,10 +7983,10 @@
     <row r="349" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="12"/>
       <c r="B349" s="2" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="C349" s="35" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="D349" s="44"/>
       <c r="E349" s="38" t="str">
@@ -8004,10 +7997,10 @@
     <row r="350" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="12"/>
       <c r="B350" s="2" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="C350" s="35" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="D350" s="44"/>
       <c r="E350" s="38" t="str">
@@ -8018,10 +8011,10 @@
     <row r="351" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="12"/>
       <c r="B351" s="2" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="C351" s="35" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="D351" s="44"/>
       <c r="E351" s="38" t="str">
@@ -8032,10 +8025,10 @@
     <row r="352" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="12"/>
       <c r="B352" s="2" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="C352" s="35" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="D352" s="44"/>
       <c r="E352" s="38" t="str">
@@ -8046,10 +8039,10 @@
     <row r="353" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="12"/>
       <c r="B353" s="2" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="C353" s="35" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="D353" s="44"/>
       <c r="E353" s="38" t="str">
@@ -8060,10 +8053,10 @@
     <row r="354" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="12"/>
       <c r="B354" s="2" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="C354" s="35" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="D354" s="44"/>
       <c r="E354" s="38" t="str">
@@ -8074,10 +8067,10 @@
     <row r="355" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="12"/>
       <c r="B355" s="2" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="C355" s="35" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="D355" s="44"/>
       <c r="E355" s="38" t="str">
@@ -8088,10 +8081,10 @@
     <row r="356" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="12"/>
       <c r="B356" s="2" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="C356" s="35" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="D356" s="44"/>
       <c r="E356" s="38" t="str">
@@ -8111,7 +8104,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="22" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="B358" s="20"/>
       <c r="C358" s="16"/>
@@ -8124,7 +8117,7 @@
     <row r="359" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="3"/>
       <c r="B359" s="1" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="C359" s="35"/>
       <c r="D359" s="44"/>
@@ -8136,10 +8129,10 @@
     <row r="360" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="3"/>
       <c r="B360" s="2" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="D360" s="44"/>
       <c r="E360" s="38" t="str">
@@ -8150,10 +8143,10 @@
     <row r="361" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="3"/>
       <c r="B361" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D361" s="44"/>
       <c r="E361" s="38" t="str">
@@ -8164,10 +8157,10 @@
     <row r="362" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="3"/>
       <c r="B362" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="D362" s="44"/>
       <c r="E362" s="38" t="str">
@@ -8178,10 +8171,10 @@
     <row r="363" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="3"/>
       <c r="B363" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="D363" s="44"/>
       <c r="E363" s="38" t="str">
@@ -8192,10 +8185,10 @@
     <row r="364" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="3"/>
       <c r="B364" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="D364" s="44"/>
       <c r="E364" s="38" t="str">
@@ -8206,10 +8199,10 @@
     <row r="365" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="3"/>
       <c r="B365" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="D365" s="44"/>
       <c r="E365" s="38" t="str">
@@ -8220,10 +8213,10 @@
     <row r="366" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="3"/>
       <c r="B366" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="D366" s="44"/>
       <c r="E366" s="38" t="str">
@@ -8234,10 +8227,10 @@
     <row r="367" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="3"/>
       <c r="B367" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="D367" s="44"/>
       <c r="E367" s="38" t="str">
@@ -8248,10 +8241,10 @@
     <row r="368" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="B368" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="D368" s="44"/>
       <c r="E368" s="38" t="str">
@@ -8262,10 +8255,10 @@
     <row r="369" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="B369" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="D369" s="44"/>
       <c r="E369" s="38" t="str">
@@ -8286,7 +8279,7 @@
     <row r="371" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="3"/>
       <c r="B371" s="1" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="C371" s="35"/>
       <c r="D371" s="44"/>
@@ -8298,10 +8291,10 @@
     <row r="372" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="3"/>
       <c r="B372" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="D372" s="44"/>
       <c r="E372" s="38" t="str">
@@ -8312,10 +8305,10 @@
     <row r="373" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="3"/>
       <c r="B373" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="D373" s="44"/>
       <c r="E373" s="38" t="str">
@@ -8326,10 +8319,10 @@
     <row r="374" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="3"/>
       <c r="B374" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="D374" s="44"/>
       <c r="E374" s="38" t="str">
@@ -8340,10 +8333,10 @@
     <row r="375" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="3"/>
       <c r="B375" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="D375" s="44"/>
       <c r="E375" s="38" t="str">
@@ -8354,10 +8347,10 @@
     <row r="376" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="3"/>
       <c r="B376" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="D376" s="44"/>
       <c r="E376" s="38" t="str">
@@ -8368,7 +8361,7 @@
     <row r="377" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="3"/>
       <c r="B377" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>10</v>
@@ -8382,7 +8375,7 @@
     <row r="378" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="3"/>
       <c r="B378" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>1</v>
@@ -8396,10 +8389,10 @@
     <row r="379" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="3"/>
       <c r="B379" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="D379" s="44"/>
       <c r="E379" s="38" t="str">
@@ -8410,10 +8403,10 @@
     <row r="380" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="3"/>
       <c r="B380" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="D380" s="44"/>
       <c r="E380" s="38" t="str">
@@ -8424,10 +8417,10 @@
     <row r="381" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="3"/>
       <c r="B381" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="D381" s="44"/>
       <c r="E381" s="38" t="str">
@@ -8438,10 +8431,10 @@
     <row r="382" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="3"/>
       <c r="B382" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="D382" s="44"/>
       <c r="E382" s="38" t="str">
@@ -8452,10 +8445,10 @@
     <row r="383" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="3"/>
       <c r="B383" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="D383" s="44"/>
       <c r="E383" s="38" t="str">
@@ -8466,10 +8459,10 @@
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="3"/>
       <c r="B384" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="D384" s="44"/>
       <c r="E384" s="38" t="str">
@@ -8489,7 +8482,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="22" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B386" s="20"/>
       <c r="C386" s="48"/>
@@ -8502,7 +8495,7 @@
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="12"/>
       <c r="B387" s="1" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C387" s="35"/>
       <c r="D387" s="44"/>
@@ -8514,10 +8507,10 @@
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="3"/>
       <c r="B388" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C388" s="27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D388" s="44"/>
       <c r="E388" s="38" t="str">
@@ -8528,10 +8521,10 @@
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="3"/>
       <c r="B389" s="2" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C389" s="27" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="D389" s="44"/>
       <c r="E389" s="38" t="str">
@@ -8542,10 +8535,10 @@
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="3"/>
       <c r="B390" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C390" s="27" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="D390" s="44"/>
       <c r="E390" s="38" t="str">
@@ -8556,10 +8549,10 @@
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="3"/>
       <c r="B391" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C391" s="27" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="D391" s="44"/>
       <c r="E391" s="38" t="str">
@@ -8570,10 +8563,10 @@
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="3"/>
       <c r="B392" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C392" s="27" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="D392" s="44"/>
       <c r="E392" s="38" t="str">
@@ -8584,10 +8577,10 @@
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="3"/>
       <c r="B393" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C393" s="27" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="D393" s="44"/>
       <c r="E393" s="38" t="str">
@@ -8598,10 +8591,10 @@
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="3"/>
       <c r="B394" s="2" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C394" s="27" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="D394" s="44"/>
       <c r="E394" s="38" t="str">
@@ -8612,10 +8605,10 @@
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="3"/>
       <c r="B395" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C395" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D395" s="44"/>
       <c r="E395" s="38" t="str">
@@ -8626,10 +8619,10 @@
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="3"/>
       <c r="B396" s="2" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="C396" s="27" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="D396" s="44"/>
       <c r="E396" s="38" t="str">
@@ -8640,10 +8633,10 @@
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="3"/>
       <c r="B397" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C397" s="27" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="D397" s="44"/>
       <c r="E397" s="38" t="str">
@@ -8654,10 +8647,10 @@
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="13"/>
       <c r="B398" s="2" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C398" s="27" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D398" s="44"/>
       <c r="E398" s="38" t="str">
@@ -8668,10 +8661,10 @@
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="13"/>
       <c r="B399" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C399" s="27" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="D399" s="44"/>
       <c r="E399" s="38" t="str">
@@ -8682,7 +8675,7 @@
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="13"/>
       <c r="B400" s="2" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C400" s="27" t="s">
         <v>8</v>
@@ -8696,10 +8689,10 @@
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="13"/>
       <c r="B401" s="2" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C401" s="27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D401" s="44"/>
       <c r="E401" s="38" t="str">
@@ -8710,10 +8703,10 @@
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="13"/>
       <c r="B402" s="15" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C402" s="27" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="D402" s="44"/>
       <c r="E402" s="38" t="str">
@@ -8724,10 +8717,10 @@
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="3"/>
       <c r="B403" s="2" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C403" s="27" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="D403" s="44"/>
       <c r="E403" s="38" t="str">
@@ -8738,10 +8731,10 @@
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="3"/>
       <c r="B404" s="15" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C404" s="27" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="D404" s="44"/>
       <c r="E404" s="38" t="str">
@@ -8752,10 +8745,10 @@
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="3"/>
       <c r="B405" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C405" s="27" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D405" s="44"/>
       <c r="E405" s="38" t="str">
@@ -8766,10 +8759,10 @@
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="3"/>
       <c r="B406" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C406" s="27" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="D406" s="44"/>
       <c r="E406" s="38" t="str">
@@ -8780,10 +8773,10 @@
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="3"/>
       <c r="B407" s="2" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C407" s="27" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="D407" s="44"/>
       <c r="E407" s="38" t="str">
@@ -8794,10 +8787,10 @@
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="3"/>
       <c r="B408" s="2" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C408" s="27" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="D408" s="44"/>
       <c r="E408" s="38" t="str">
@@ -8808,7 +8801,7 @@
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="3"/>
       <c r="B409" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C409" s="27" t="s">
         <v>10</v>
@@ -8822,10 +8815,10 @@
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="3"/>
       <c r="B410" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C410" s="27" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="D410" s="44"/>
       <c r="E410" s="38" t="str">
@@ -8836,10 +8829,10 @@
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="3"/>
       <c r="B411" s="2" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="C411" s="27" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="D411" s="44"/>
       <c r="E411" s="38" t="str">
@@ -8860,7 +8853,7 @@
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="3"/>
       <c r="B413" s="1" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="C413" s="27"/>
       <c r="D413" s="44"/>
@@ -8872,10 +8865,10 @@
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="3"/>
       <c r="B414" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C414" s="27" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="D414" s="44"/>
       <c r="E414" s="38" t="str">
@@ -8886,10 +8879,10 @@
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="3"/>
       <c r="B415" s="2" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C415" s="27" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="D415" s="44"/>
       <c r="E415" s="38" t="str">
@@ -8900,10 +8893,10 @@
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="3"/>
       <c r="B416" s="2" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C416" s="27" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="D416" s="44"/>
       <c r="E416" s="38" t="str">
@@ -8914,10 +8907,10 @@
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="3"/>
       <c r="B417" s="2" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C417" s="27" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="D417" s="44"/>
       <c r="E417" s="38" t="str">
@@ -8928,10 +8921,10 @@
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="3"/>
       <c r="B418" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C418" s="27" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="D418" s="44"/>
       <c r="E418" s="38" t="str">
@@ -8942,10 +8935,10 @@
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="3"/>
       <c r="B419" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C419" s="27" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="D419" s="44"/>
       <c r="E419" s="38" t="str">
@@ -8956,10 +8949,10 @@
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="3"/>
       <c r="B420" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C420" s="27" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="D420" s="44"/>
       <c r="E420" s="38" t="str">
@@ -8970,10 +8963,10 @@
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="3"/>
       <c r="B421" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C421" s="27" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="D421" s="44"/>
       <c r="E421" s="38" t="str">
@@ -8984,10 +8977,10 @@
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="3"/>
       <c r="B422" s="2" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C422" s="27" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="D422" s="44"/>
       <c r="E422" s="38" t="str">
@@ -8998,10 +8991,10 @@
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="3"/>
       <c r="B423" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C423" s="27" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="D423" s="44"/>
       <c r="E423" s="38" t="str">
@@ -9012,10 +9005,10 @@
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="3"/>
       <c r="B424" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C424" s="27" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="D424" s="44"/>
       <c r="E424" s="38" t="str">
@@ -9026,10 +9019,10 @@
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="3"/>
       <c r="B425" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C425" s="27" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="D425" s="44"/>
       <c r="E425" s="38" t="str">
@@ -9040,10 +9033,10 @@
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="3"/>
       <c r="B426" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C426" s="27" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="D426" s="44"/>
       <c r="E426" s="38" t="str">
@@ -9054,10 +9047,10 @@
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="3"/>
       <c r="B427" s="2" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C427" s="27" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="D427" s="44"/>
       <c r="E427" s="38" t="str">
@@ -9068,10 +9061,10 @@
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="3"/>
       <c r="B428" s="2" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C428" s="27" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="D428" s="44"/>
       <c r="E428" s="38" t="str">
@@ -9082,10 +9075,10 @@
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="3"/>
       <c r="B429" s="2" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="C429" s="27" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="D429" s="44"/>
       <c r="E429" s="38" t="str">
@@ -9096,10 +9089,10 @@
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="3"/>
       <c r="B430" s="2" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="C430" s="27" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="D430" s="44"/>
       <c r="E430" s="38" t="str">
@@ -9120,7 +9113,7 @@
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="13"/>
       <c r="B432" s="1" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="C432" s="27"/>
       <c r="D432" s="44"/>
@@ -9132,10 +9125,10 @@
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="13"/>
       <c r="B433" s="2" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="C433" s="27" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="D433" s="44"/>
       <c r="E433" s="38" t="str">
@@ -9146,10 +9139,10 @@
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="13"/>
       <c r="B434" s="15" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="C434" s="27" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="D434" s="44"/>
       <c r="E434" s="38" t="str">
@@ -9161,7 +9154,7 @@
       <c r="A435" s="13"/>
       <c r="B435" s="14"/>
       <c r="C435" s="27" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="D435" s="44"/>
       <c r="E435" s="38" t="str">
@@ -9173,7 +9166,7 @@
       <c r="A436" s="13"/>
       <c r="B436" s="14"/>
       <c r="C436" s="27" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="D436" s="44"/>
       <c r="E436" s="38" t="str">
@@ -9185,7 +9178,7 @@
       <c r="A437" s="13"/>
       <c r="B437" s="14"/>
       <c r="C437" s="27" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D437" s="44"/>
       <c r="E437" s="38" t="str">
@@ -9197,7 +9190,7 @@
       <c r="A438" s="13"/>
       <c r="B438" s="14"/>
       <c r="C438" s="27" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="D438" s="44"/>
       <c r="E438" s="38" t="str">
@@ -9209,7 +9202,7 @@
       <c r="A439" s="13"/>
       <c r="B439" s="14"/>
       <c r="C439" s="27" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="D439" s="44"/>
       <c r="E439" s="38" t="str">
@@ -9221,7 +9214,7 @@
       <c r="A440" s="13"/>
       <c r="B440" s="14"/>
       <c r="C440" s="27" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="D440" s="44"/>
       <c r="E440" s="38" t="str">
@@ -9233,7 +9226,7 @@
       <c r="A441" s="13"/>
       <c r="B441" s="14"/>
       <c r="C441" s="27" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="D441" s="44"/>
       <c r="E441" s="38" t="str">
@@ -9245,7 +9238,7 @@
       <c r="A442" s="13"/>
       <c r="B442" s="14"/>
       <c r="C442" s="27" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="D442" s="44"/>
       <c r="E442" s="38" t="str">
@@ -9257,7 +9250,7 @@
       <c r="A443" s="13"/>
       <c r="B443" s="14"/>
       <c r="C443" s="27" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="D443" s="44"/>
       <c r="E443" s="38" t="str">
@@ -9269,7 +9262,7 @@
       <c r="A444" s="13"/>
       <c r="B444" s="14"/>
       <c r="C444" s="27" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="D444" s="44"/>
       <c r="E444" s="38" t="str">
@@ -9281,7 +9274,7 @@
       <c r="A445" s="13"/>
       <c r="B445" s="14"/>
       <c r="C445" s="27" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="D445" s="44"/>
       <c r="E445" s="38" t="str">
@@ -9293,7 +9286,7 @@
       <c r="A446" s="13"/>
       <c r="B446" s="14"/>
       <c r="C446" s="27" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="D446" s="44"/>
       <c r="E446" s="38" t="str">
@@ -9305,7 +9298,7 @@
       <c r="A447" s="13"/>
       <c r="B447" s="14"/>
       <c r="C447" s="27" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="D447" s="44"/>
       <c r="E447" s="38" t="str">
@@ -9317,7 +9310,7 @@
       <c r="A448" s="13"/>
       <c r="B448" s="14"/>
       <c r="C448" s="27" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="D448" s="44"/>
       <c r="E448" s="38" t="str">
@@ -9329,7 +9322,7 @@
       <c r="A449" s="13"/>
       <c r="B449" s="14"/>
       <c r="C449" s="27" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D449" s="44"/>
       <c r="E449" s="38" t="str">
@@ -9341,7 +9334,7 @@
       <c r="A450" s="13"/>
       <c r="B450" s="14"/>
       <c r="C450" s="27" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="D450" s="44"/>
       <c r="E450" s="38" t="str">
@@ -9353,7 +9346,7 @@
       <c r="A451" s="13"/>
       <c r="B451" s="14"/>
       <c r="C451" s="27" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="D451" s="44"/>
       <c r="E451" s="38" t="str">
@@ -9365,7 +9358,7 @@
       <c r="A452" s="13"/>
       <c r="B452" s="14"/>
       <c r="C452" s="27" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="D452" s="44"/>
       <c r="E452" s="38" t="str">
@@ -9377,7 +9370,7 @@
       <c r="A453" s="13"/>
       <c r="B453" s="14"/>
       <c r="C453" s="27" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="D453" s="44"/>
       <c r="E453" s="38" t="str">
@@ -9389,7 +9382,7 @@
       <c r="A454" s="13"/>
       <c r="B454" s="14"/>
       <c r="C454" s="27" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="D454" s="44"/>
       <c r="E454" s="38" t="str">
@@ -9401,7 +9394,7 @@
       <c r="A455" s="13"/>
       <c r="B455" s="14"/>
       <c r="C455" s="27" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="D455" s="44"/>
       <c r="E455" s="38" t="str">
@@ -9413,7 +9406,7 @@
       <c r="A456" s="13"/>
       <c r="B456" s="14"/>
       <c r="C456" s="27" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="D456" s="44"/>
       <c r="E456" s="38" t="str">
@@ -9425,7 +9418,7 @@
       <c r="A457" s="13"/>
       <c r="B457" s="14"/>
       <c r="C457" s="27" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="D457" s="44"/>
       <c r="E457" s="38" t="str">
@@ -9437,7 +9430,7 @@
       <c r="A458" s="13"/>
       <c r="B458" s="2"/>
       <c r="C458" s="27" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="D458" s="44"/>
       <c r="E458" s="38" t="str">
@@ -9457,7 +9450,7 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="22" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="B460" s="17"/>
       <c r="C460" s="50"/>
@@ -9470,7 +9463,7 @@
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="12"/>
       <c r="B461" s="5" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C461" s="26"/>
       <c r="D461" s="44"/>
@@ -9482,10 +9475,10 @@
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="3"/>
       <c r="B462" s="2" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C462" s="27" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="D462" s="44"/>
       <c r="E462" s="38" t="str">
@@ -9496,10 +9489,10 @@
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="3"/>
       <c r="B463" s="2" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="C463" s="27" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="D463" s="44"/>
       <c r="E463" s="38" t="str">
@@ -9519,7 +9512,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="22" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="B465" s="17"/>
       <c r="C465" s="50"/>
@@ -9532,7 +9525,7 @@
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="3"/>
       <c r="B466" s="1" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="C466" s="27"/>
       <c r="D466" s="44"/>
@@ -9544,10 +9537,10 @@
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="3"/>
       <c r="B467" s="2" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="C467" s="27" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="D467" s="44"/>
       <c r="E467" s="38" t="str">
@@ -9558,10 +9551,10 @@
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="3"/>
       <c r="B468" s="2" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="C468" s="27" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D468" s="44"/>
       <c r="E468" s="38" t="str">
@@ -9572,10 +9565,10 @@
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="3"/>
       <c r="B469" s="2" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="C469" s="27" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="D469" s="44"/>
       <c r="E469" s="38" t="str">
@@ -9586,10 +9579,10 @@
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="3"/>
       <c r="B470" s="2" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="C470" s="27" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="D470" s="44"/>
       <c r="E470" s="38" t="str">
@@ -9600,10 +9593,10 @@
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="3"/>
       <c r="B471" s="2" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="C471" s="27" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="D471" s="44"/>
       <c r="E471" s="38" t="str">
@@ -9614,10 +9607,10 @@
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="3"/>
       <c r="B472" s="2" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="C472" s="27" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="D472" s="44"/>
       <c r="E472" s="38" t="str">
@@ -9628,10 +9621,10 @@
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="3"/>
       <c r="B473" s="2" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="C473" s="27" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="D473" s="44"/>
       <c r="E473" s="38" t="str">
@@ -9642,10 +9635,10 @@
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="3"/>
       <c r="B474" s="2" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="C474" s="27" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="D474" s="44"/>
       <c r="E474" s="38" t="str">
@@ -9656,10 +9649,10 @@
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="3"/>
       <c r="B475" s="2" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="C475" s="27" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="D475" s="44"/>
       <c r="E475" s="38" t="str">
@@ -9670,10 +9663,10 @@
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="3"/>
       <c r="B476" s="2" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C476" s="27" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="D476" s="44"/>
       <c r="E476" s="38" t="str">
@@ -9684,10 +9677,10 @@
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="3"/>
       <c r="B477" s="2" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="C477" s="27" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="D477" s="44"/>
       <c r="E477" s="38" t="str">
@@ -9698,10 +9691,10 @@
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="3"/>
       <c r="B478" s="2" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C478" s="27" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="D478" s="44"/>
       <c r="E478" s="38" t="str">
@@ -9712,10 +9705,10 @@
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="3"/>
       <c r="B479" s="2" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="C479" s="27" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="D479" s="44"/>
       <c r="E479" s="38" t="str">
@@ -9726,10 +9719,10 @@
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="3"/>
       <c r="B480" s="2" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="C480" s="27" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="D480" s="44"/>
       <c r="E480" s="38" t="str">
@@ -9740,10 +9733,10 @@
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="3"/>
       <c r="B481" s="2" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="C481" s="27" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="D481" s="44"/>
       <c r="E481" s="38" t="str">
@@ -9754,10 +9747,10 @@
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="3"/>
       <c r="B482" s="2" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="C482" s="27" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="D482" s="44"/>
       <c r="E482" s="38" t="str">
@@ -9768,10 +9761,10 @@
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="3"/>
       <c r="B483" s="2" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="C483" s="27" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="D483" s="44"/>
       <c r="E483" s="38" t="str">
@@ -9782,10 +9775,10 @@
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="3"/>
       <c r="B484" s="2" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="C484" s="27" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="D484" s="44"/>
       <c r="E484" s="38" t="str">
@@ -9796,10 +9789,10 @@
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="3"/>
       <c r="B485" s="2" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="C485" s="27" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="D485" s="44"/>
       <c r="E485" s="38" t="str">
@@ -9810,10 +9803,10 @@
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="3"/>
       <c r="B486" s="2" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="C486" s="27" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="D486" s="44"/>
       <c r="E486" s="38" t="str">
@@ -9824,10 +9817,10 @@
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="3"/>
       <c r="B487" s="2" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="C487" s="27" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="E487" s="38" t="str">
         <f t="shared" si="7"/>
@@ -9837,10 +9830,10 @@
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="3"/>
       <c r="B488" s="2" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="C488" s="27" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="D488" s="44"/>
       <c r="E488" s="38" t="str">
@@ -9851,10 +9844,10 @@
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="3"/>
       <c r="B489" s="2" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="C489" s="27" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="D489" s="44"/>
       <c r="E489" s="38" t="str">
@@ -9865,10 +9858,10 @@
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="3"/>
       <c r="B490" s="2" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="C490" s="27" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="D490" s="44"/>
       <c r="E490" s="38" t="str">
@@ -9879,10 +9872,10 @@
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="3"/>
       <c r="B491" s="2" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="C491" s="27" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="D491" s="44"/>
       <c r="E491" s="38" t="str">
@@ -9893,10 +9886,10 @@
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="3"/>
       <c r="B492" s="2" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="C492" s="27" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="D492" s="44"/>
       <c r="E492" s="38" t="str">
@@ -9907,10 +9900,10 @@
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="3"/>
       <c r="B493" s="2" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="C493" s="27" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="D493" s="44"/>
       <c r="E493" s="38" t="str">
@@ -9921,10 +9914,10 @@
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="3"/>
       <c r="B494" s="2" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C494" s="26" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="D494" s="44"/>
       <c r="E494" s="38" t="str">
@@ -9935,10 +9928,10 @@
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="3"/>
       <c r="B495" s="2" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="C495" s="27" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="D495" s="44"/>
       <c r="E495" s="38" t="str">
@@ -9949,10 +9942,10 @@
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="3"/>
       <c r="B496" s="2" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="C496" s="27" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="D496" s="44"/>
       <c r="E496" s="38" t="str">
@@ -9963,10 +9956,10 @@
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="3"/>
       <c r="B497" s="2" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="C497" s="27" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="D497" s="44"/>
       <c r="E497" s="38" t="str">
@@ -9977,10 +9970,10 @@
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="3"/>
       <c r="B498" s="2" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="C498" s="27" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="D498" s="44"/>
       <c r="E498" s="38" t="str">
@@ -9991,10 +9984,10 @@
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="3"/>
       <c r="B499" s="2" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="C499" s="27" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="D499" s="44"/>
       <c r="E499" s="38" t="str">
@@ -10005,10 +9998,10 @@
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="3"/>
       <c r="B500" s="2" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="C500" s="27" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="D500" s="44"/>
       <c r="E500" s="38" t="str">
@@ -10019,10 +10012,10 @@
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="3"/>
       <c r="B501" s="2" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="C501" s="27" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="D501" s="44"/>
       <c r="E501" s="38" t="str">
@@ -10042,10 +10035,10 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="22" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="C503" s="27"/>
       <c r="D503" s="44"/>
@@ -10057,141 +10050,141 @@
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="3"/>
       <c r="B504" s="2" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
       <c r="C504" s="27" t="s">
-        <v>814</v>
+        <v>161</v>
       </c>
       <c r="D504" s="44"/>
       <c r="E504" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    Period DATETIME NULL,</v>
+        <v>Period</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="3"/>
       <c r="B505" s="2" t="s">
-        <v>825</v>
+        <v>66</v>
       </c>
       <c r="C505" s="27" t="s">
-        <v>815</v>
+        <v>73</v>
       </c>
       <c r="D505" s="44"/>
       <c r="E505" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    ID VARCHAR(32) NOT NULL,</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="3"/>
       <c r="B506" s="2" t="s">
-        <v>826</v>
+        <v>67</v>
       </c>
       <c r="C506" s="27" t="s">
-        <v>816</v>
+        <v>74</v>
       </c>
       <c r="D506" s="44"/>
       <c r="E506" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    RowNumber INT NULL,</v>
+        <v>RowNumber</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="3"/>
       <c r="B507" s="2" t="s">
-        <v>827</v>
+        <v>68</v>
       </c>
       <c r="C507" s="27" t="s">
-        <v>817</v>
+        <v>75</v>
       </c>
       <c r="D507" s="44"/>
       <c r="E507" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    Active VARCHAR(36) NULL,</v>
+        <v>Active</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="3"/>
       <c r="B508" s="2" t="s">
-        <v>828</v>
+        <v>47</v>
       </c>
       <c r="C508" s="27" t="s">
-        <v>818</v>
+        <v>41</v>
       </c>
       <c r="D508" s="44"/>
       <c r="E508" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    CreditID VARCHAR(32) NULL,</v>
+        <v>CreditID</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="3"/>
       <c r="B509" s="2" t="s">
-        <v>829</v>
+        <v>69</v>
       </c>
       <c r="C509" s="27" t="s">
-        <v>819</v>
+        <v>76</v>
       </c>
       <c r="D509" s="44"/>
       <c r="E509" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    Credit NVARCHAR(100) NULL,</v>
+        <v>Credit</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="3"/>
       <c r="B510" s="2" t="s">
-        <v>830</v>
+        <v>70</v>
       </c>
       <c r="C510" s="27" t="s">
-        <v>820</v>
+        <v>10</v>
       </c>
       <c r="D510" s="44"/>
       <c r="E510" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    BranchID VARCHAR(32) NULL,</v>
+        <v>BranchID</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="7"/>
       <c r="B511" s="2" t="s">
-        <v>831</v>
+        <v>46</v>
       </c>
       <c r="C511" s="27" t="s">
-        <v>821</v>
+        <v>77</v>
       </c>
       <c r="D511" s="44"/>
       <c r="E511" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    Branch NVARCHAR(100) NULL,</v>
+        <v>Branch</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="3"/>
       <c r="B512" s="2" t="s">
-        <v>832</v>
+        <v>71</v>
       </c>
       <c r="C512" s="27" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
       <c r="D512" s="44"/>
       <c r="E512" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    CreditEmployeeID VARCHAR(32) NULL,</v>
+        <v>CreditEmployeeID</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="3"/>
       <c r="B513" s="2" t="s">
-        <v>833</v>
+        <v>72</v>
       </c>
       <c r="C513" s="27" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="D513" s="44"/>
       <c r="E513" s="38" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    CreditEmployee NVARCHAR(100) NULL,</v>
+        <v>CreditEmployee</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
@@ -10205,7 +10198,9 @@
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A515" s="3"/>
+      <c r="A515" s="22" t="s">
+        <v>804</v>
+      </c>
       <c r="B515" s="2"/>
       <c r="C515" s="27"/>
       <c r="D515" s="44"/>
@@ -10216,7 +10211,9 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="7"/>
-      <c r="B516" s="2"/>
+      <c r="B516" s="1" t="s">
+        <v>807</v>
+      </c>
       <c r="C516" s="27"/>
       <c r="D516" s="44"/>
       <c r="E516" s="38" t="str">
@@ -10226,76 +10223,83 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="3"/>
-      <c r="B517" s="2"/>
-      <c r="C517" s="27"/>
+      <c r="B517" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C517" s="27" t="s">
+        <v>41</v>
+      </c>
       <c r="D517" s="44"/>
       <c r="E517" s="38" t="str">
-        <f t="shared" ref="E517:E580" si="8">IF(C517&gt;0,IF(D517&gt;0,D517, C517)," ")</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" ref="E517:E583" si="8">IF(C517&gt;0,IF(D517&gt;0,D517, C517)," ")</f>
+        <v>CreditID</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="3"/>
-      <c r="B518" s="2"/>
-      <c r="C518" s="27"/>
+      <c r="B518" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C518" s="27" t="s">
+        <v>55</v>
+      </c>
       <c r="D518" s="44"/>
-      <c r="E518" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="E518" s="38"/>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="3"/>
-      <c r="B519" s="2"/>
-      <c r="C519" s="27"/>
+      <c r="B519" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C519" s="27" t="s">
+        <v>56</v>
+      </c>
       <c r="D519" s="44"/>
-      <c r="E519" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="E519" s="38"/>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A520" s="7"/>
-      <c r="B520" s="2"/>
-      <c r="C520" s="30"/>
+      <c r="A520" s="3"/>
+      <c r="B520" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C520" s="27" t="s">
+        <v>808</v>
+      </c>
       <c r="D520" s="44"/>
-      <c r="E520" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="E520" s="38"/>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="3"/>
       <c r="B521" s="2"/>
       <c r="C521" s="27"/>
       <c r="D521" s="44"/>
-      <c r="E521" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="E521" s="38"/>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="3"/>
-      <c r="B522" s="2"/>
+      <c r="B522" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="C522" s="27"/>
       <c r="D522" s="44"/>
-      <c r="E522" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="E522" s="38"/>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="3"/>
-      <c r="B523" s="2"/>
-      <c r="C523" s="27"/>
+      <c r="B523" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C523" s="27" t="s">
+        <v>8</v>
+      </c>
       <c r="D523" s="44"/>
       <c r="E523" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>ClientID</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A524" s="7"/>
+      <c r="A524" s="3"/>
       <c r="B524" s="2"/>
       <c r="C524" s="27"/>
       <c r="D524" s="44"/>
@@ -10305,141 +10309,143 @@
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A525" s="3"/>
-      <c r="B525" s="2"/>
-      <c r="C525" s="27" t="s">
-        <v>239</v>
-      </c>
+      <c r="A525" s="7"/>
+      <c r="B525" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C525" s="30"/>
       <c r="D525" s="44"/>
       <c r="E525" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Бизнес Сектор Экономики]</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="3"/>
-      <c r="B526" s="2"/>
+      <c r="B526" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C526" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="D526" s="44"/>
+        <v>810</v>
+      </c>
+      <c r="D526" s="52" t="s">
+        <v>811</v>
+      </c>
       <c r="E526" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Заявки]</v>
+        <v xml:space="preserve">First_BranchID/Last_BranchID </v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A527" s="13"/>
-      <c r="B527" s="2"/>
+      <c r="A527" s="3"/>
+      <c r="B527" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="C527" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="D527" s="44"/>
+        <v>333</v>
+      </c>
+      <c r="D527" s="52" t="s">
+        <v>812</v>
+      </c>
       <c r="E527" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Вид Кредитной Истории]</v>
+        <v>First_EmployeeID/Last_EmployeeID</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A528" s="13"/>
-      <c r="B528" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C528" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="D528" s="44"/>
-      <c r="E528" s="38" t="str">
+      <c r="A528" s="3"/>
+      <c r="B528" s="2"/>
+      <c r="C528" s="27"/>
+      <c r="D528" s="52"/>
+      <c r="E528" s="38"/>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A529" s="3"/>
+      <c r="B529" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C529" s="27"/>
+      <c r="D529" s="44"/>
+      <c r="E529" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Кредит ID]</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A530" s="12"/>
+      <c r="A530" s="3"/>
       <c r="B530" s="2" t="s">
-        <v>201</v>
+        <v>346</v>
       </c>
       <c r="C530" s="27" t="s">
-        <v>254</v>
+        <v>344</v>
       </c>
       <c r="D530" s="44"/>
       <c r="E530" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Это Зеленый Кредит]</v>
+        <v>EmployeePosition</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="3"/>
       <c r="B531" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C531" s="27" t="s">
-        <v>244</v>
+        <v>345</v>
+      </c>
+      <c r="C531" s="51" t="s">
+        <v>343</v>
       </c>
       <c r="D531" s="44"/>
-      <c r="E531" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Клиент ID]</v>
-      </c>
+      <c r="E531" s="38"/>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="3"/>
-      <c r="B532" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C532" s="27" t="s">
-        <v>250</v>
-      </c>
+      <c r="B532" s="2"/>
+      <c r="C532" s="27"/>
       <c r="D532" s="44"/>
-      <c r="E532" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v>[ЗаявкаНаКредит Сумма Кредита]</v>
-      </c>
+      <c r="E532" s="38"/>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="3"/>
-      <c r="B533" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C533" s="28" t="s">
-        <v>294</v>
-      </c>
+      <c r="B533" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C533" s="27"/>
       <c r="D533" s="44"/>
       <c r="E533" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">[ЗаявкаНаКредит Причина Отказа] </v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="3"/>
-      <c r="B534" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C534" s="28"/>
+      <c r="B534" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C534" s="27" t="s">
+        <v>61</v>
+      </c>
       <c r="D534" s="44"/>
       <c r="E534" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>IRR_Client</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="3"/>
-      <c r="B535" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C535" s="21"/>
-      <c r="D535" s="44"/>
+      <c r="B535" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C535" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="E535" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>IRR</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A536" s="3"/>
-      <c r="B536" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C536" s="36"/>
+      <c r="A536" s="13"/>
+      <c r="B536" s="15"/>
+      <c r="C536" s="28"/>
       <c r="D536" s="44"/>
       <c r="E536" s="38" t="str">
         <f t="shared" si="8"/>
@@ -10447,161 +10453,148 @@
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A537" s="3"/>
-      <c r="B537" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C537" s="27" t="s">
-        <v>167</v>
-      </c>
+      <c r="A537" s="22" t="s">
+        <v>813</v>
+      </c>
+      <c r="B537" s="53"/>
+      <c r="C537" s="50"/>
       <c r="D537" s="44"/>
       <c r="E537" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>Period</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A538" s="3"/>
-      <c r="B538" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C538" s="27" t="s">
-        <v>200</v>
-      </c>
+      <c r="A538" s="12"/>
+      <c r="B538" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C538" s="26"/>
       <c r="D538" s="44"/>
       <c r="E538" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>Registrar_Tref</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="3"/>
       <c r="B539" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C539" s="27" t="s">
-        <v>77</v>
+        <v>49</v>
+      </c>
+      <c r="C539" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="D539" s="44"/>
       <c r="E539" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>ID</v>
+        <v>SoldDate</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="3"/>
-      <c r="B540" s="14"/>
-      <c r="C540" s="27" t="s">
-        <v>78</v>
+      <c r="B540" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C540" s="28" t="s">
+        <v>41</v>
       </c>
       <c r="D540" s="44"/>
       <c r="E540" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>RowNumber</v>
+        <v>CreditID</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
-      <c r="B541" s="17"/>
-      <c r="C541" s="27" t="s">
-        <v>79</v>
+      <c r="B541" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C541" s="28" t="s">
+        <v>8</v>
       </c>
       <c r="D541" s="44"/>
       <c r="E541" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>Active</v>
+        <v>ClientID</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A542" s="13"/>
-      <c r="B542" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C542" s="27" t="s">
-        <v>42</v>
+      <c r="A542" s="3"/>
+      <c r="B542" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C542" s="28" t="s">
+        <v>821</v>
       </c>
       <c r="D542" s="44"/>
       <c r="E542" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>CreditID</v>
+        <v>Balance_Total</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A543" s="22" t="s">
-        <v>37</v>
-      </c>
+      <c r="A543" s="3"/>
       <c r="B543" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C543" s="27" t="s">
-        <v>80</v>
+        <v>816</v>
+      </c>
+      <c r="C543" s="28" t="s">
+        <v>822</v>
       </c>
       <c r="D543" s="44"/>
       <c r="E543" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>Credit</v>
+        <v>DaysBucket_Credit</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A544" s="12"/>
+      <c r="A544" s="3"/>
       <c r="B544" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C544" s="27" t="s">
-        <v>10</v>
+        <v>817</v>
+      </c>
+      <c r="C544" s="28" t="s">
+        <v>823</v>
       </c>
       <c r="D544" s="44"/>
       <c r="E544" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>BranchID</v>
+        <v>DaysFact_Total</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="3"/>
       <c r="B545" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C545" s="27" t="s">
-        <v>81</v>
+        <v>818</v>
+      </c>
+      <c r="C545" s="28" t="s">
+        <v>824</v>
       </c>
       <c r="D545" s="44"/>
       <c r="E545" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>Branch</v>
+        <v>DaysIFRS</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="3"/>
-      <c r="B546" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C546" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="B546" s="2"/>
+      <c r="C546" s="28"/>
       <c r="D546" s="44"/>
-      <c r="E546" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v>CreditExpertID</v>
-      </c>
+      <c r="E546" s="38"/>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="3"/>
-      <c r="B547" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C547" s="27" t="s">
-        <v>83</v>
-      </c>
+      <c r="B547" s="2"/>
+      <c r="C547" s="28"/>
       <c r="D547" s="44"/>
       <c r="E547" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>CreditExpert</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="3"/>
-      <c r="B548" s="1" t="s">
-        <v>287</v>
+      <c r="B548" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="C548" s="28"/>
       <c r="D548" s="44"/>
@@ -10613,229 +10606,220 @@
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="3"/>
       <c r="B549" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C549" s="21"/>
+        <v>819</v>
+      </c>
+      <c r="C549" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="D549" s="44"/>
       <c r="E549" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v xml:space="preserve">BranchID </v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="3"/>
-      <c r="B550" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C550" s="36"/>
+      <c r="B550" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C550" s="27" t="s">
+        <v>814</v>
+      </c>
       <c r="D550" s="44"/>
       <c r="E550" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v xml:space="preserve">        EmployeeID            VARCHAR(36)   NULL,</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="3"/>
-      <c r="B551" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C551" s="27" t="s">
-        <v>42</v>
-      </c>
+      <c r="C551" s="28"/>
       <c r="D551" s="44"/>
       <c r="E551" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>CreditID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A552" s="7"/>
-      <c r="B552" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C552" s="27" t="s">
-        <v>57</v>
-      </c>
+      <c r="A552" s="3"/>
+      <c r="B552" s="2"/>
+      <c r="C552" s="28"/>
       <c r="D552" s="44"/>
       <c r="E552" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>DisbursementDate</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="3"/>
-      <c r="B553" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C553" s="27" t="s">
-        <v>58</v>
-      </c>
+      <c r="B553" s="1"/>
+      <c r="C553" s="36"/>
       <c r="D553" s="44"/>
       <c r="E553" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>CurrencyID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="3"/>
       <c r="B554" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C554" s="27" t="s">
-        <v>59</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C554" s="27"/>
       <c r="D554" s="44"/>
       <c r="E554" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>CreditAmount</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A555" s="3"/>
+      <c r="A555" s="7"/>
       <c r="B555" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C555" s="27" t="s">
-        <v>60</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C555" s="27"/>
       <c r="D555" s="44"/>
       <c r="E555" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>CreditCurrency</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="3"/>
-      <c r="B556" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C556" s="27"/>
+      <c r="B556" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C556" s="27" t="s">
+        <v>56</v>
+      </c>
       <c r="D556" s="44"/>
       <c r="E556" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>CurrencyID</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="3"/>
-      <c r="B557" s="1" t="s">
-        <v>291</v>
+      <c r="B557" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="C557" s="27" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="D557" s="44"/>
       <c r="E557" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>ClientID</v>
+        <v>CreditAmount</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="3"/>
       <c r="B558" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C558" s="27"/>
+        <v>62</v>
+      </c>
+      <c r="C558" s="27" t="s">
+        <v>58</v>
+      </c>
       <c r="D558" s="44"/>
       <c r="E558" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>CreditCurrency</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="3"/>
       <c r="B559" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C559" s="27" t="s">
-        <v>61</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C559" s="27"/>
       <c r="D559" s="44"/>
       <c r="E559" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>FirstFilialID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="3"/>
-      <c r="B560" s="2" t="s">
-        <v>290</v>
+      <c r="B560" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="C560" s="27" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D560" s="44"/>
       <c r="E560" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>FirstExpertID</v>
+        <v>ClientID</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="3"/>
-      <c r="B561" s="14"/>
-      <c r="C561" s="27" t="s">
-        <v>44</v>
-      </c>
+      <c r="B561" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C561" s="27"/>
       <c r="D561" s="44"/>
       <c r="E561" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>IRR</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="3"/>
-      <c r="B562" s="17"/>
+      <c r="B562" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="C562" s="27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D562" s="44"/>
       <c r="E562" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>IRR_Client</v>
+        <v>FirstFilialID</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A563" s="13"/>
-      <c r="B563" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C563" s="27"/>
+      <c r="A563" s="3"/>
+      <c r="B563" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C563" s="27" t="s">
+        <v>60</v>
+      </c>
       <c r="D563" s="44"/>
       <c r="E563" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>FirstExpertID</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A564" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B564" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C564" s="27"/>
+      <c r="A564" s="3"/>
+      <c r="B564" s="14"/>
+      <c r="C564" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="D564" s="44"/>
       <c r="E564" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>IRR</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A565" s="12"/>
-      <c r="B565" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C565" s="27"/>
+      <c r="A565" s="3"/>
+      <c r="B565" s="17"/>
+      <c r="C565" s="27" t="s">
+        <v>61</v>
+      </c>
       <c r="D565" s="44"/>
       <c r="E565" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>IRR_Client</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A566" s="3"/>
-      <c r="B566" s="2" t="s">
-        <v>52</v>
+      <c r="A566" s="13"/>
+      <c r="B566" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C566" s="27"/>
       <c r="D566" s="44"/>
@@ -10845,9 +10829,8 @@
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A567" s="3"/>
-      <c r="B567" s="1" t="s">
-        <v>289</v>
+      <c r="B567" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C567" s="27"/>
       <c r="D567" s="44"/>
@@ -10857,9 +10840,9 @@
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A568" s="3"/>
+      <c r="A568" s="12"/>
       <c r="B568" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C568" s="27"/>
       <c r="D568" s="44"/>
@@ -10871,8 +10854,9 @@
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="3"/>
       <c r="B569" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C569" s="27"/>
       <c r="D569" s="44"/>
       <c r="E569" s="38" t="str">
         <f t="shared" si="8"/>
@@ -10882,9 +10866,9 @@
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="3"/>
       <c r="B570" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C570" s="16"/>
+        <v>277</v>
+      </c>
+      <c r="C570" s="27"/>
       <c r="D570" s="44"/>
       <c r="E570" s="38" t="str">
         <f t="shared" si="8"/>
@@ -10894,9 +10878,9 @@
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="3"/>
       <c r="B571" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C571" s="32"/>
+        <v>48</v>
+      </c>
+      <c r="C571" s="27"/>
       <c r="D571" s="44"/>
       <c r="E571" s="38" t="str">
         <f t="shared" si="8"/>
@@ -10906,70 +10890,77 @@
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="3"/>
       <c r="B572" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C572" s="27" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D572" s="44"/>
       <c r="E572" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>SoldDate</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="3"/>
-      <c r="B573" s="19"/>
-      <c r="C573" s="27" t="s">
-        <v>42</v>
-      </c>
+      <c r="B573" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C573" s="16"/>
       <c r="D573" s="44"/>
       <c r="E573" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>CreditID</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="3"/>
-      <c r="C574" s="27" t="s">
-        <v>43</v>
-      </c>
+      <c r="B574" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C574" s="32"/>
       <c r="D574" s="44"/>
       <c r="E574" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>SoldAmount</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A575" s="13"/>
-      <c r="C575" s="27"/>
+      <c r="A575" s="3"/>
+      <c r="B575" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C575" s="27" t="s">
+        <v>40</v>
+      </c>
       <c r="D575" s="44"/>
       <c r="E575" s="38" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>SoldDate</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A576" s="3"/>
+      <c r="B576" s="19"/>
       <c r="C576" s="27" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D576" s="44"/>
       <c r="E576" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>IRR</v>
-      </c>
-    </row>
-    <row r="577" spans="3:5" x14ac:dyDescent="0.25">
+        <v>CreditID</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A577" s="3"/>
       <c r="C577" s="27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D577" s="44"/>
       <c r="E577" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>IRR</v>
-      </c>
-    </row>
-    <row r="578" spans="3:5" x14ac:dyDescent="0.25">
+        <v>SoldAmount</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A578" s="13"/>
       <c r="C578" s="27"/>
       <c r="D578" s="44"/>
       <c r="E578" s="38" t="str">
@@ -10977,35 +10968,63 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="579" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C579" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D579" s="45"/>
+        <v>43</v>
+      </c>
+      <c r="D579" s="44"/>
       <c r="E579" s="38" t="str">
         <f t="shared" si="8"/>
-        <v>ExpertID</v>
-      </c>
-    </row>
-    <row r="580" spans="3:5" x14ac:dyDescent="0.25">
+        <v>IRR</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C580" s="27" t="s">
-        <v>46</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D580" s="44"/>
       <c r="E580" s="38" t="str">
         <f t="shared" si="8"/>
+        <v>IRR</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C581" s="27"/>
+      <c r="D581" s="44"/>
+      <c r="E581" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C582" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D582" s="45"/>
+      <c r="E582" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>ExpertID</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C583" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E583" s="38" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">BranchID </v>
       </c>
     </row>
-    <row r="581" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C581" s="28"/>
-      <c r="E581" s="38" t="str">
-        <f t="shared" ref="E581" si="9">IF(C581&gt;0,IF(D581&gt;0,D581, C581)," ")</f>
+    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C584" s="28"/>
+      <c r="E584" s="38" t="str">
+        <f t="shared" ref="E584" si="9">IF(C584&gt;0,IF(D584&gt;0,D584, C584)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="E530:E581 E3:E528">
+  <conditionalFormatting sqref="E3:E584">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$D3&gt;0</formula>
     </cfRule>
